--- a/Assets/AddressableResource/Data/Excels/LevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/LevelData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\Resources\Data\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE771BD1-1B9B-420B-AF5A-D191211230BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C676FA-075F-4D77-88D9-13649AA31363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42450" yWindow="3750" windowWidth="31935" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -211,9 +211,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -226,8 +223,11 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,7 +534,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:XFA107"/>
+  <dimension ref="A1:XFA305"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.875" style="6" customWidth="1"/>
@@ -558,7 +558,7 @@
       <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="4"/>
@@ -579,7 +579,7 @@
       <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <f>B2</f>
         <v>2</v>
       </c>
@@ -599,11 +599,11 @@
       <c r="C3" s="10">
         <v>0</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <f>E2+B3</f>
         <v>4</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <f>B3-B2</f>
         <v>0</v>
       </c>
@@ -619,11 +619,11 @@
       <c r="C4" s="10">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f t="shared" ref="E4:E67" si="1">E3+B4</f>
         <v>6</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <f t="shared" ref="F4:F67" si="2">B4-B3</f>
         <v>0</v>
       </c>
@@ -639,11 +639,11 @@
       <c r="C5" s="10">
         <v>0</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -660,11 +660,11 @@
       <c r="C6" s="10">
         <v>2</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -685,11 +685,11 @@
       <c r="C7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -707,11 +707,11 @@
       <c r="C8" s="10">
         <v>0</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -728,11 +728,11 @@
       <c r="C9" s="10">
         <v>0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -749,11 +749,11 @@
       <c r="C10" s="10">
         <v>0</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -770,11 +770,11 @@
       <c r="C11" s="10">
         <v>3</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -794,11 +794,11 @@
       <c r="C12" s="10">
         <v>0</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -815,11 +815,11 @@
       <c r="C13" s="10">
         <v>0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -836,11 +836,11 @@
       <c r="C14" s="10">
         <v>0</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -857,11 +857,11 @@
       <c r="C15" s="10">
         <v>4</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -881,11 +881,11 @@
       <c r="C16" s="10">
         <v>0</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -902,11 +902,11 @@
       <c r="C17" s="10">
         <v>0</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -923,11 +923,11 @@
       <c r="C18" s="10">
         <v>0</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f>E17+B18</f>
         <v>55</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -944,11 +944,11 @@
       <c r="C19" s="10">
         <v>0</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <f t="shared" ref="E19:E34" si="4">E18+B18</f>
         <v>60</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -965,11 +965,11 @@
       <c r="C20" s="10">
         <v>0</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -986,11 +986,11 @@
       <c r="C21" s="10">
         <v>5</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1010,11 +1010,11 @@
       <c r="C22" s="10">
         <v>0</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1031,11 +1031,11 @@
       <c r="C23" s="10">
         <v>6</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1055,11 +1055,11 @@
       <c r="C24" s="10">
         <v>0</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1076,11 +1076,11 @@
       <c r="C25" s="10">
         <v>7</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <f t="shared" si="4"/>
         <v>93</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1100,11 +1100,11 @@
       <c r="C26" s="10">
         <v>0</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <f t="shared" si="4"/>
         <v>99</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1121,11 +1121,11 @@
       <c r="C27" s="10">
         <v>8</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <f t="shared" si="4"/>
         <v>105</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1145,11 +1145,11 @@
       <c r="C28" s="10">
         <v>0</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <f t="shared" si="4"/>
         <v>112</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1166,11 +1166,11 @@
       <c r="C29" s="10">
         <v>0</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1187,11 +1187,11 @@
       <c r="C30" s="10">
         <v>0</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <f t="shared" si="4"/>
         <v>126</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1208,11 +1208,11 @@
       <c r="C31" s="10">
         <v>0</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1229,11 +1229,11 @@
       <c r="C32" s="10">
         <v>0</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <f t="shared" si="4"/>
         <v>140</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1250,11 +1250,11 @@
       <c r="C33" s="10">
         <v>0</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <f t="shared" si="4"/>
         <v>148</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1272,11 +1272,11 @@
       <c r="C34" s="10">
         <v>0</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="12">
         <f t="shared" si="4"/>
         <v>156</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1293,11 +1293,11 @@
       <c r="C35" s="10">
         <v>0</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="12">
         <f t="shared" si="1"/>
         <v>164</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1314,11 +1314,11 @@
       <c r="C36" s="10">
         <v>0</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="12">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1335,11 +1335,11 @@
       <c r="C37" s="10">
         <v>0</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="12">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1356,11 +1356,11 @@
       <c r="C38" s="10">
         <v>0</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="12">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1377,11 +1377,11 @@
       <c r="C39" s="10">
         <v>0</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="12">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1398,11 +1398,11 @@
       <c r="C40" s="10">
         <v>0</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="12">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F40" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1419,11 +1419,11 @@
       <c r="C41" s="10">
         <v>0</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="12">
         <f t="shared" si="1"/>
         <v>220</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1440,11 +1440,11 @@
       <c r="C42" s="10">
         <v>0</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="12">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F42" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1461,11 +1461,11 @@
       <c r="C43" s="10">
         <v>0</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="12">
         <f t="shared" si="1"/>
         <v>241</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1482,11 +1482,11 @@
       <c r="C44" s="10">
         <v>0</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="12">
         <f t="shared" si="1"/>
         <v>252</v>
       </c>
-      <c r="F44" s="14">
+      <c r="F44" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1503,11 +1503,11 @@
       <c r="C45" s="10">
         <v>0</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="12">
         <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F45" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1524,11 +1524,11 @@
       <c r="C46" s="10">
         <v>0</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="12">
         <f t="shared" si="1"/>
         <v>275</v>
       </c>
-      <c r="F46" s="14">
+      <c r="F46" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1545,11 +1545,11 @@
       <c r="C47" s="10">
         <v>0</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="12">
         <f t="shared" si="1"/>
         <v>287</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1566,11 +1566,11 @@
       <c r="C48" s="10">
         <v>0</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="12">
         <f t="shared" si="1"/>
         <v>299</v>
       </c>
-      <c r="F48" s="14">
+      <c r="F48" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1587,11 +1587,11 @@
       <c r="C49" s="10">
         <v>0</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="12">
         <f t="shared" si="1"/>
         <v>312</v>
       </c>
-      <c r="F49" s="14">
+      <c r="F49" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1608,11 +1608,11 @@
       <c r="C50" s="10">
         <v>0</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="12">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1629,11 +1629,11 @@
       <c r="C51" s="10">
         <v>0</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="12">
         <f t="shared" si="1"/>
         <v>338</v>
       </c>
-      <c r="F51" s="14">
+      <c r="F51" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1650,11 +1650,11 @@
       <c r="C52" s="10">
         <v>0</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="12">
         <f t="shared" si="1"/>
         <v>352</v>
       </c>
-      <c r="F52" s="14">
+      <c r="F52" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1671,11 +1671,11 @@
       <c r="C53" s="10">
         <v>0</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="12">
         <f t="shared" si="1"/>
         <v>366</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1692,11 +1692,11 @@
       <c r="C54" s="10">
         <v>0</v>
       </c>
-      <c r="E54" s="13">
+      <c r="E54" s="12">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="F54" s="14">
+      <c r="F54" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1713,11 +1713,11 @@
       <c r="C55" s="10">
         <v>0</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="12">
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="F55" s="14">
+      <c r="F55" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1734,11 +1734,11 @@
       <c r="C56" s="10">
         <v>0</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="12">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="F56" s="14">
+      <c r="F56" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1755,11 +1755,11 @@
       <c r="C57" s="10">
         <v>0</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="12">
         <f t="shared" si="1"/>
         <v>425</v>
       </c>
-      <c r="F57" s="14">
+      <c r="F57" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1776,11 +1776,11 @@
       <c r="C58" s="10">
         <v>0</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="12">
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="F58" s="14">
+      <c r="F58" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1797,11 +1797,11 @@
       <c r="C59" s="10">
         <v>0</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="12">
         <f t="shared" si="1"/>
         <v>457</v>
       </c>
-      <c r="F59" s="14">
+      <c r="F59" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1818,11 +1818,11 @@
       <c r="C60" s="10">
         <v>0</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="12">
         <f t="shared" si="1"/>
         <v>474</v>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1839,11 +1839,11 @@
       <c r="C61" s="10">
         <v>0</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="12">
         <f t="shared" si="1"/>
         <v>491</v>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1860,11 +1860,11 @@
       <c r="C62" s="10">
         <v>0</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="12">
         <f t="shared" si="1"/>
         <v>509</v>
       </c>
-      <c r="F62" s="14">
+      <c r="F62" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1881,11 +1881,11 @@
       <c r="C63" s="10">
         <v>0</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="12">
         <f t="shared" si="1"/>
         <v>527</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1902,11 +1902,11 @@
       <c r="C64" s="10">
         <v>0</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="12">
         <f t="shared" si="1"/>
         <v>546</v>
       </c>
-      <c r="F64" s="14">
+      <c r="F64" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1923,11 +1923,11 @@
       <c r="C65" s="10">
         <v>0</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="12">
         <f t="shared" si="1"/>
         <v>565</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1944,11 +1944,11 @@
       <c r="C66" s="10">
         <v>0</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="12">
         <f t="shared" si="1"/>
         <v>585</v>
       </c>
-      <c r="F66" s="14">
+      <c r="F66" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1965,11 +1965,11 @@
       <c r="C67" s="10">
         <v>0</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="12">
         <f t="shared" si="1"/>
         <v>606</v>
       </c>
-      <c r="F67" s="14">
+      <c r="F67" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1986,11 +1986,11 @@
       <c r="C68" s="10">
         <v>0</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="12">
         <f t="shared" ref="E68:E100" si="9">E67+B68</f>
         <v>628</v>
       </c>
-      <c r="F68" s="14">
+      <c r="F68" s="13">
         <f t="shared" ref="F68:F100" si="10">B68-B67</f>
         <v>1</v>
       </c>
@@ -2007,11 +2007,11 @@
       <c r="C69" s="10">
         <v>0</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="12">
         <f t="shared" si="9"/>
         <v>651</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2028,11 +2028,11 @@
       <c r="C70" s="10">
         <v>0</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="12">
         <f t="shared" si="9"/>
         <v>675</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2049,11 +2049,11 @@
       <c r="C71" s="10">
         <v>0</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="12">
         <f t="shared" si="9"/>
         <v>700</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2070,11 +2070,11 @@
       <c r="C72" s="10">
         <v>0</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="12">
         <f t="shared" si="9"/>
         <v>726</v>
       </c>
-      <c r="F72" s="14">
+      <c r="F72" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2091,11 +2091,11 @@
       <c r="C73" s="10">
         <v>0</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="12">
         <f t="shared" si="9"/>
         <v>753</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2112,11 +2112,11 @@
       <c r="C74" s="10">
         <v>0</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="12">
         <f t="shared" si="9"/>
         <v>781</v>
       </c>
-      <c r="F74" s="14">
+      <c r="F74" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2133,11 +2133,11 @@
       <c r="C75" s="10">
         <v>0</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="12">
         <f t="shared" si="9"/>
         <v>810</v>
       </c>
-      <c r="F75" s="14">
+      <c r="F75" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2154,11 +2154,11 @@
       <c r="C76" s="10">
         <v>0</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="12">
         <f t="shared" si="9"/>
         <v>840</v>
       </c>
-      <c r="F76" s="14">
+      <c r="F76" s="13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
@@ -2175,11 +2175,11 @@
       <c r="C77" s="10">
         <v>0</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="12">
         <f t="shared" si="9"/>
         <v>872</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2196,11 +2196,11 @@
       <c r="C78" s="10">
         <v>0</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="12">
         <f t="shared" si="9"/>
         <v>906</v>
       </c>
-      <c r="F78" s="14">
+      <c r="F78" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2217,11 +2217,11 @@
       <c r="C79" s="10">
         <v>0</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="12">
         <f t="shared" si="9"/>
         <v>942</v>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2238,11 +2238,11 @@
       <c r="C80" s="10">
         <v>0</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="12">
         <f t="shared" si="9"/>
         <v>980</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2259,11 +2259,11 @@
       <c r="C81" s="10">
         <v>0</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="12">
         <f t="shared" si="9"/>
         <v>1020</v>
       </c>
-      <c r="F81" s="14">
+      <c r="F81" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2280,11 +2280,11 @@
       <c r="C82" s="10">
         <v>0</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="12">
         <f t="shared" si="9"/>
         <v>1062</v>
       </c>
-      <c r="F82" s="14">
+      <c r="F82" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2301,11 +2301,11 @@
       <c r="C83" s="10">
         <v>0</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="12">
         <f t="shared" si="9"/>
         <v>1106</v>
       </c>
-      <c r="F83" s="14">
+      <c r="F83" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2322,11 +2322,11 @@
       <c r="C84" s="10">
         <v>0</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="12">
         <f t="shared" si="9"/>
         <v>1152</v>
       </c>
-      <c r="F84" s="14">
+      <c r="F84" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2343,11 +2343,11 @@
       <c r="C85" s="10">
         <v>0</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="12">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="F85" s="14">
+      <c r="F85" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2364,11 +2364,11 @@
       <c r="C86" s="10">
         <v>0</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="12">
         <f t="shared" si="9"/>
         <v>1250</v>
       </c>
-      <c r="F86" s="14">
+      <c r="F86" s="13">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -2385,11 +2385,11 @@
       <c r="C87" s="10">
         <v>0</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="12">
         <f t="shared" si="9"/>
         <v>1303</v>
       </c>
-      <c r="F87" s="14">
+      <c r="F87" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2406,11 +2406,11 @@
       <c r="C88" s="10">
         <v>0</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="12">
         <f t="shared" si="9"/>
         <v>1359</v>
       </c>
-      <c r="F88" s="14">
+      <c r="F88" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2427,11 +2427,11 @@
       <c r="C89" s="10">
         <v>0</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="12">
         <f t="shared" si="9"/>
         <v>1418</v>
       </c>
-      <c r="F89" s="14">
+      <c r="F89" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2448,11 +2448,11 @@
       <c r="C90" s="10">
         <v>0</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="12">
         <f t="shared" si="9"/>
         <v>1480</v>
       </c>
-      <c r="F90" s="14">
+      <c r="F90" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2469,11 +2469,11 @@
       <c r="C91" s="10">
         <v>0</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="12">
         <f t="shared" si="9"/>
         <v>1545</v>
       </c>
-      <c r="F91" s="14">
+      <c r="F91" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2490,11 +2490,11 @@
       <c r="C92" s="10">
         <v>0</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="12">
         <f t="shared" si="9"/>
         <v>1613</v>
       </c>
-      <c r="F92" s="14">
+      <c r="F92" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2511,18 +2511,18 @@
       <c r="C93" s="10">
         <v>0</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="12">
         <f t="shared" si="9"/>
         <v>1684</v>
       </c>
-      <c r="F93" s="14">
+      <c r="F93" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
-        <f t="shared" ref="A94:A101" si="14">A93+1</f>
+        <f t="shared" ref="A94:A157" si="14">A93+1</f>
         <v>93</v>
       </c>
       <c r="B94" s="10">
@@ -2532,11 +2532,11 @@
       <c r="C94" s="10">
         <v>0</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="12">
         <f t="shared" si="9"/>
         <v>1758</v>
       </c>
-      <c r="F94" s="14">
+      <c r="F94" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2553,11 +2553,11 @@
       <c r="C95" s="10">
         <v>0</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="12">
         <f t="shared" si="9"/>
         <v>1835</v>
       </c>
-      <c r="F95" s="14">
+      <c r="F95" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2574,11 +2574,11 @@
       <c r="C96" s="10">
         <v>0</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="12">
         <f t="shared" si="9"/>
         <v>1915</v>
       </c>
-      <c r="F96" s="14">
+      <c r="F96" s="13">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
@@ -2595,11 +2595,11 @@
       <c r="C97" s="10">
         <v>0</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="12">
         <f t="shared" si="9"/>
         <v>1999</v>
       </c>
-      <c r="F97" s="14">
+      <c r="F97" s="13">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -2610,17 +2610,17 @@
         <v>97</v>
       </c>
       <c r="B98" s="10">
-        <f t="shared" ref="B98:B100" si="15">B97+4</f>
+        <f t="shared" ref="B98:B161" si="15">B97+4</f>
         <v>88</v>
       </c>
       <c r="C98" s="10">
         <v>0</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="12">
         <f t="shared" si="9"/>
         <v>2087</v>
       </c>
-      <c r="F98" s="14">
+      <c r="F98" s="13">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -2637,11 +2637,11 @@
       <c r="C99" s="10">
         <v>0</v>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="12">
         <f t="shared" si="9"/>
         <v>2179</v>
       </c>
-      <c r="F99" s="14">
+      <c r="F99" s="13">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -2658,11 +2658,11 @@
       <c r="C100" s="10">
         <v>0</v>
       </c>
-      <c r="E100" s="13">
+      <c r="E100" s="12">
         <f t="shared" si="9"/>
         <v>2275</v>
       </c>
-      <c r="F100" s="14">
+      <c r="F100" s="13">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -2672,31 +2672,4040 @@
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="10">
+        <v>100</v>
+      </c>
+      <c r="C101" s="10">
+        <v>0</v>
+      </c>
+      <c r="E101" s="12">
+        <f t="shared" ref="E101:E164" si="16">E100+B101</f>
+        <v>2375</v>
+      </c>
+      <c r="F101" s="13">
+        <f t="shared" ref="F101:F164" si="17">B101-B100</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="5">
+        <f t="shared" si="14"/>
+        <v>101</v>
+      </c>
+      <c r="B102" s="10">
+        <v>100</v>
+      </c>
+      <c r="C102" s="10">
+        <v>0</v>
+      </c>
+      <c r="E102" s="12">
+        <f t="shared" si="16"/>
+        <v>2475</v>
+      </c>
+      <c r="F102" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="5">
+        <f t="shared" si="14"/>
+        <v>102</v>
+      </c>
+      <c r="B103" s="10">
+        <v>100</v>
+      </c>
+      <c r="C103" s="10">
+        <v>0</v>
+      </c>
+      <c r="E103" s="12">
+        <f t="shared" si="16"/>
+        <v>2575</v>
+      </c>
+      <c r="F103" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="5">
+        <f t="shared" si="14"/>
+        <v>103</v>
+      </c>
+      <c r="B104" s="10">
+        <v>100</v>
+      </c>
+      <c r="C104" s="10">
+        <v>0</v>
+      </c>
+      <c r="E104" s="12">
+        <f t="shared" si="16"/>
+        <v>2675</v>
+      </c>
+      <c r="F104" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="5">
+        <f t="shared" si="14"/>
+        <v>104</v>
+      </c>
+      <c r="B105" s="10">
+        <v>100</v>
+      </c>
+      <c r="C105" s="10">
+        <v>0</v>
+      </c>
+      <c r="E105" s="12">
+        <f t="shared" si="16"/>
+        <v>2775</v>
+      </c>
+      <c r="F105" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="5">
+        <f t="shared" si="14"/>
+        <v>105</v>
+      </c>
+      <c r="B106" s="10">
+        <v>100</v>
+      </c>
+      <c r="C106" s="10">
+        <v>0</v>
+      </c>
+      <c r="E106" s="12">
+        <f t="shared" si="16"/>
+        <v>2875</v>
+      </c>
+      <c r="F106" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="5">
+        <f t="shared" si="14"/>
+        <v>106</v>
+      </c>
+      <c r="B107" s="10">
+        <v>100</v>
+      </c>
+      <c r="C107" s="10">
+        <v>0</v>
+      </c>
+      <c r="E107" s="12">
+        <f t="shared" si="16"/>
+        <v>2975</v>
+      </c>
+      <c r="F107" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="5">
+        <f t="shared" si="14"/>
+        <v>107</v>
+      </c>
+      <c r="B108" s="10">
+        <v>100</v>
+      </c>
+      <c r="C108" s="10">
+        <v>0</v>
+      </c>
+      <c r="E108" s="12">
+        <f t="shared" si="16"/>
+        <v>3075</v>
+      </c>
+      <c r="F108" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="5">
+        <f t="shared" si="14"/>
+        <v>108</v>
+      </c>
+      <c r="B109" s="10">
+        <v>100</v>
+      </c>
+      <c r="C109" s="10">
+        <v>0</v>
+      </c>
+      <c r="E109" s="12">
+        <f t="shared" si="16"/>
+        <v>3175</v>
+      </c>
+      <c r="F109" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="5">
+        <f t="shared" si="14"/>
+        <v>109</v>
+      </c>
+      <c r="B110" s="10">
+        <v>100</v>
+      </c>
+      <c r="C110" s="10">
+        <v>0</v>
+      </c>
+      <c r="E110" s="12">
+        <f t="shared" si="16"/>
+        <v>3275</v>
+      </c>
+      <c r="F110" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="5">
+        <f t="shared" si="14"/>
+        <v>110</v>
+      </c>
+      <c r="B111" s="10">
+        <v>100</v>
+      </c>
+      <c r="C111" s="10">
+        <v>0</v>
+      </c>
+      <c r="E111" s="12">
+        <f t="shared" si="16"/>
+        <v>3375</v>
+      </c>
+      <c r="F111" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="5">
+        <f t="shared" si="14"/>
+        <v>111</v>
+      </c>
+      <c r="B112" s="10">
+        <v>100</v>
+      </c>
+      <c r="C112" s="10">
+        <v>0</v>
+      </c>
+      <c r="E112" s="12">
+        <f t="shared" si="16"/>
+        <v>3475</v>
+      </c>
+      <c r="F112" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="5">
+        <f t="shared" si="14"/>
+        <v>112</v>
+      </c>
+      <c r="B113" s="10">
+        <v>100</v>
+      </c>
+      <c r="C113" s="10">
+        <v>0</v>
+      </c>
+      <c r="E113" s="12">
+        <f t="shared" si="16"/>
+        <v>3575</v>
+      </c>
+      <c r="F113" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="5">
+        <f t="shared" si="14"/>
+        <v>113</v>
+      </c>
+      <c r="B114" s="10">
+        <v>100</v>
+      </c>
+      <c r="C114" s="10">
+        <v>0</v>
+      </c>
+      <c r="E114" s="12">
+        <f t="shared" si="16"/>
+        <v>3675</v>
+      </c>
+      <c r="F114" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="5">
+        <f t="shared" si="14"/>
+        <v>114</v>
+      </c>
+      <c r="B115" s="10">
+        <v>100</v>
+      </c>
+      <c r="C115" s="10">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12">
+        <f t="shared" si="16"/>
+        <v>3775</v>
+      </c>
+      <c r="F115" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="5">
+        <f t="shared" si="14"/>
+        <v>115</v>
+      </c>
+      <c r="B116" s="10">
+        <v>100</v>
+      </c>
+      <c r="C116" s="10">
+        <v>0</v>
+      </c>
+      <c r="E116" s="12">
+        <f t="shared" si="16"/>
+        <v>3875</v>
+      </c>
+      <c r="F116" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="5">
+        <f t="shared" si="14"/>
+        <v>116</v>
+      </c>
+      <c r="B117" s="10">
+        <v>100</v>
+      </c>
+      <c r="C117" s="10">
+        <v>0</v>
+      </c>
+      <c r="E117" s="12">
+        <f t="shared" si="16"/>
+        <v>3975</v>
+      </c>
+      <c r="F117" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="5">
+        <f t="shared" si="14"/>
+        <v>117</v>
+      </c>
+      <c r="B118" s="10">
+        <v>100</v>
+      </c>
+      <c r="C118" s="10">
+        <v>0</v>
+      </c>
+      <c r="E118" s="12">
+        <f t="shared" si="16"/>
+        <v>4075</v>
+      </c>
+      <c r="F118" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="5">
+        <f t="shared" si="14"/>
+        <v>118</v>
+      </c>
+      <c r="B119" s="10">
+        <v>100</v>
+      </c>
+      <c r="C119" s="10">
+        <v>0</v>
+      </c>
+      <c r="E119" s="12">
+        <f t="shared" si="16"/>
+        <v>4175</v>
+      </c>
+      <c r="F119" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="5">
+        <f t="shared" si="14"/>
+        <v>119</v>
+      </c>
+      <c r="B120" s="10">
+        <v>100</v>
+      </c>
+      <c r="C120" s="10">
+        <v>0</v>
+      </c>
+      <c r="E120" s="12">
+        <f t="shared" si="16"/>
+        <v>4275</v>
+      </c>
+      <c r="F120" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="5">
+        <f t="shared" si="14"/>
+        <v>120</v>
+      </c>
+      <c r="B121" s="10">
+        <v>100</v>
+      </c>
+      <c r="C121" s="10">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12">
+        <f t="shared" si="16"/>
+        <v>4375</v>
+      </c>
+      <c r="F121" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="5">
+        <f t="shared" si="14"/>
+        <v>121</v>
+      </c>
+      <c r="B122" s="10">
+        <v>100</v>
+      </c>
+      <c r="C122" s="10">
+        <v>0</v>
+      </c>
+      <c r="E122" s="12">
+        <f t="shared" si="16"/>
+        <v>4475</v>
+      </c>
+      <c r="F122" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="5">
+        <f t="shared" si="14"/>
+        <v>122</v>
+      </c>
+      <c r="B123" s="10">
+        <v>100</v>
+      </c>
+      <c r="C123" s="10">
+        <v>0</v>
+      </c>
+      <c r="E123" s="12">
+        <f t="shared" si="16"/>
+        <v>4575</v>
+      </c>
+      <c r="F123" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="5">
+        <f t="shared" si="14"/>
+        <v>123</v>
+      </c>
+      <c r="B124" s="10">
+        <v>100</v>
+      </c>
+      <c r="C124" s="10">
+        <v>0</v>
+      </c>
+      <c r="E124" s="12">
+        <f t="shared" si="16"/>
+        <v>4675</v>
+      </c>
+      <c r="F124" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="5">
+        <f t="shared" si="14"/>
+        <v>124</v>
+      </c>
+      <c r="B125" s="10">
+        <v>100</v>
+      </c>
+      <c r="C125" s="10">
+        <v>0</v>
+      </c>
+      <c r="E125" s="12">
+        <f t="shared" si="16"/>
+        <v>4775</v>
+      </c>
+      <c r="F125" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="5">
+        <f t="shared" si="14"/>
+        <v>125</v>
+      </c>
+      <c r="B126" s="10">
+        <v>100</v>
+      </c>
+      <c r="C126" s="10">
+        <v>0</v>
+      </c>
+      <c r="E126" s="12">
+        <f t="shared" si="16"/>
+        <v>4875</v>
+      </c>
+      <c r="F126" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="5">
+        <f t="shared" si="14"/>
+        <v>126</v>
+      </c>
+      <c r="B127" s="10">
+        <v>100</v>
+      </c>
+      <c r="C127" s="10">
+        <v>0</v>
+      </c>
+      <c r="E127" s="12">
+        <f t="shared" si="16"/>
+        <v>4975</v>
+      </c>
+      <c r="F127" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="5">
+        <f t="shared" si="14"/>
+        <v>127</v>
+      </c>
+      <c r="B128" s="10">
+        <v>100</v>
+      </c>
+      <c r="C128" s="10">
+        <v>0</v>
+      </c>
+      <c r="E128" s="12">
+        <f t="shared" si="16"/>
+        <v>5075</v>
+      </c>
+      <c r="F128" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="5">
+        <f t="shared" si="14"/>
+        <v>128</v>
+      </c>
+      <c r="B129" s="10">
+        <v>100</v>
+      </c>
+      <c r="C129" s="10">
+        <v>0</v>
+      </c>
+      <c r="E129" s="12">
+        <f t="shared" si="16"/>
+        <v>5175</v>
+      </c>
+      <c r="F129" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="5">
+        <f t="shared" si="14"/>
+        <v>129</v>
+      </c>
+      <c r="B130" s="10">
+        <v>100</v>
+      </c>
+      <c r="C130" s="10">
+        <v>0</v>
+      </c>
+      <c r="E130" s="12">
+        <f t="shared" si="16"/>
+        <v>5275</v>
+      </c>
+      <c r="F130" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="5">
+        <f t="shared" si="14"/>
+        <v>130</v>
+      </c>
+      <c r="B131" s="10">
+        <v>100</v>
+      </c>
+      <c r="C131" s="10">
+        <v>0</v>
+      </c>
+      <c r="E131" s="12">
+        <f t="shared" si="16"/>
+        <v>5375</v>
+      </c>
+      <c r="F131" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="5">
+        <f t="shared" si="14"/>
+        <v>131</v>
+      </c>
+      <c r="B132" s="10">
+        <v>100</v>
+      </c>
+      <c r="C132" s="10">
+        <v>0</v>
+      </c>
+      <c r="E132" s="12">
+        <f t="shared" si="16"/>
+        <v>5475</v>
+      </c>
+      <c r="F132" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="5">
+        <f t="shared" si="14"/>
+        <v>132</v>
+      </c>
+      <c r="B133" s="10">
+        <v>100</v>
+      </c>
+      <c r="C133" s="10">
+        <v>0</v>
+      </c>
+      <c r="E133" s="12">
+        <f t="shared" si="16"/>
+        <v>5575</v>
+      </c>
+      <c r="F133" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="5">
+        <f t="shared" si="14"/>
+        <v>133</v>
+      </c>
+      <c r="B134" s="10">
+        <v>100</v>
+      </c>
+      <c r="C134" s="10">
+        <v>0</v>
+      </c>
+      <c r="E134" s="12">
+        <f t="shared" si="16"/>
+        <v>5675</v>
+      </c>
+      <c r="F134" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="5">
+        <f t="shared" si="14"/>
+        <v>134</v>
+      </c>
+      <c r="B135" s="10">
+        <v>100</v>
+      </c>
+      <c r="C135" s="10">
+        <v>0</v>
+      </c>
+      <c r="E135" s="12">
+        <f t="shared" si="16"/>
+        <v>5775</v>
+      </c>
+      <c r="F135" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="5">
+        <f t="shared" si="14"/>
+        <v>135</v>
+      </c>
+      <c r="B136" s="10">
+        <v>100</v>
+      </c>
+      <c r="C136" s="10">
+        <v>0</v>
+      </c>
+      <c r="E136" s="12">
+        <f t="shared" si="16"/>
+        <v>5875</v>
+      </c>
+      <c r="F136" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="5">
+        <f t="shared" si="14"/>
+        <v>136</v>
+      </c>
+      <c r="B137" s="10">
+        <v>100</v>
+      </c>
+      <c r="C137" s="10">
+        <v>0</v>
+      </c>
+      <c r="E137" s="12">
+        <f t="shared" si="16"/>
+        <v>5975</v>
+      </c>
+      <c r="F137" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="5">
+        <f t="shared" si="14"/>
+        <v>137</v>
+      </c>
+      <c r="B138" s="10">
+        <v>100</v>
+      </c>
+      <c r="C138" s="10">
+        <v>0</v>
+      </c>
+      <c r="E138" s="12">
+        <f t="shared" si="16"/>
+        <v>6075</v>
+      </c>
+      <c r="F138" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="5">
+        <f t="shared" si="14"/>
+        <v>138</v>
+      </c>
+      <c r="B139" s="10">
+        <v>100</v>
+      </c>
+      <c r="C139" s="10">
+        <v>0</v>
+      </c>
+      <c r="E139" s="12">
+        <f t="shared" si="16"/>
+        <v>6175</v>
+      </c>
+      <c r="F139" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="5">
+        <f t="shared" si="14"/>
+        <v>139</v>
+      </c>
+      <c r="B140" s="10">
+        <v>100</v>
+      </c>
+      <c r="C140" s="10">
+        <v>0</v>
+      </c>
+      <c r="E140" s="12">
+        <f t="shared" si="16"/>
+        <v>6275</v>
+      </c>
+      <c r="F140" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="5">
+        <f t="shared" si="14"/>
+        <v>140</v>
+      </c>
+      <c r="B141" s="10">
+        <v>100</v>
+      </c>
+      <c r="C141" s="10">
+        <v>0</v>
+      </c>
+      <c r="E141" s="12">
+        <f t="shared" si="16"/>
+        <v>6375</v>
+      </c>
+      <c r="F141" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="5">
+        <f t="shared" si="14"/>
+        <v>141</v>
+      </c>
+      <c r="B142" s="10">
+        <v>100</v>
+      </c>
+      <c r="C142" s="10">
+        <v>0</v>
+      </c>
+      <c r="E142" s="12">
+        <f t="shared" si="16"/>
+        <v>6475</v>
+      </c>
+      <c r="F142" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="5">
+        <f t="shared" si="14"/>
+        <v>142</v>
+      </c>
+      <c r="B143" s="10">
+        <v>100</v>
+      </c>
+      <c r="C143" s="10">
+        <v>0</v>
+      </c>
+      <c r="E143" s="12">
+        <f t="shared" si="16"/>
+        <v>6575</v>
+      </c>
+      <c r="F143" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="5">
+        <f t="shared" si="14"/>
+        <v>143</v>
+      </c>
+      <c r="B144" s="10">
+        <v>100</v>
+      </c>
+      <c r="C144" s="10">
+        <v>0</v>
+      </c>
+      <c r="E144" s="12">
+        <f t="shared" si="16"/>
+        <v>6675</v>
+      </c>
+      <c r="F144" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="5">
+        <f t="shared" si="14"/>
+        <v>144</v>
+      </c>
+      <c r="B145" s="10">
+        <v>100</v>
+      </c>
+      <c r="C145" s="10">
+        <v>0</v>
+      </c>
+      <c r="E145" s="12">
+        <f t="shared" si="16"/>
+        <v>6775</v>
+      </c>
+      <c r="F145" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="5">
+        <f t="shared" si="14"/>
+        <v>145</v>
+      </c>
+      <c r="B146" s="10">
+        <v>100</v>
+      </c>
+      <c r="C146" s="10">
+        <v>0</v>
+      </c>
+      <c r="E146" s="12">
+        <f t="shared" si="16"/>
+        <v>6875</v>
+      </c>
+      <c r="F146" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="5">
+        <f t="shared" si="14"/>
+        <v>146</v>
+      </c>
+      <c r="B147" s="10">
+        <v>100</v>
+      </c>
+      <c r="C147" s="10">
+        <v>0</v>
+      </c>
+      <c r="E147" s="12">
+        <f t="shared" si="16"/>
+        <v>6975</v>
+      </c>
+      <c r="F147" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="5">
+        <f t="shared" si="14"/>
+        <v>147</v>
+      </c>
+      <c r="B148" s="10">
+        <v>100</v>
+      </c>
+      <c r="C148" s="10">
+        <v>0</v>
+      </c>
+      <c r="E148" s="12">
+        <f t="shared" si="16"/>
+        <v>7075</v>
+      </c>
+      <c r="F148" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="5">
+        <f t="shared" si="14"/>
+        <v>148</v>
+      </c>
+      <c r="B149" s="10">
+        <v>100</v>
+      </c>
+      <c r="C149" s="10">
+        <v>0</v>
+      </c>
+      <c r="E149" s="12">
+        <f t="shared" si="16"/>
+        <v>7175</v>
+      </c>
+      <c r="F149" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="5">
+        <f t="shared" si="14"/>
+        <v>149</v>
+      </c>
+      <c r="B150" s="10">
+        <v>100</v>
+      </c>
+      <c r="C150" s="10">
+        <v>0</v>
+      </c>
+      <c r="E150" s="12">
+        <f t="shared" si="16"/>
+        <v>7275</v>
+      </c>
+      <c r="F150" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="5">
+        <f t="shared" si="14"/>
+        <v>150</v>
+      </c>
+      <c r="B151" s="10">
+        <v>100</v>
+      </c>
+      <c r="C151" s="10">
+        <v>0</v>
+      </c>
+      <c r="E151" s="12">
+        <f t="shared" si="16"/>
+        <v>7375</v>
+      </c>
+      <c r="F151" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="5">
+        <f t="shared" si="14"/>
+        <v>151</v>
+      </c>
+      <c r="B152" s="10">
+        <v>100</v>
+      </c>
+      <c r="C152" s="10">
+        <v>0</v>
+      </c>
+      <c r="E152" s="12">
+        <f t="shared" si="16"/>
+        <v>7475</v>
+      </c>
+      <c r="F152" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="5">
+        <f t="shared" si="14"/>
+        <v>152</v>
+      </c>
+      <c r="B153" s="10">
+        <v>100</v>
+      </c>
+      <c r="C153" s="10">
+        <v>0</v>
+      </c>
+      <c r="E153" s="12">
+        <f t="shared" si="16"/>
+        <v>7575</v>
+      </c>
+      <c r="F153" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="5">
+        <f t="shared" si="14"/>
+        <v>153</v>
+      </c>
+      <c r="B154" s="10">
+        <v>100</v>
+      </c>
+      <c r="C154" s="10">
+        <v>0</v>
+      </c>
+      <c r="E154" s="12">
+        <f t="shared" si="16"/>
+        <v>7675</v>
+      </c>
+      <c r="F154" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="5">
+        <f t="shared" si="14"/>
+        <v>154</v>
+      </c>
+      <c r="B155" s="10">
+        <v>100</v>
+      </c>
+      <c r="C155" s="10">
+        <v>0</v>
+      </c>
+      <c r="E155" s="12">
+        <f t="shared" si="16"/>
+        <v>7775</v>
+      </c>
+      <c r="F155" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="5">
+        <f t="shared" si="14"/>
+        <v>155</v>
+      </c>
+      <c r="B156" s="10">
+        <v>100</v>
+      </c>
+      <c r="C156" s="10">
+        <v>0</v>
+      </c>
+      <c r="E156" s="12">
+        <f t="shared" si="16"/>
+        <v>7875</v>
+      </c>
+      <c r="F156" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="5">
+        <f t="shared" si="14"/>
+        <v>156</v>
+      </c>
+      <c r="B157" s="10">
+        <v>100</v>
+      </c>
+      <c r="C157" s="10">
+        <v>0</v>
+      </c>
+      <c r="E157" s="12">
+        <f t="shared" si="16"/>
+        <v>7975</v>
+      </c>
+      <c r="F157" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="5">
+        <f t="shared" ref="A158:A221" si="18">A157+1</f>
+        <v>157</v>
+      </c>
+      <c r="B158" s="10">
+        <v>100</v>
+      </c>
+      <c r="C158" s="10">
+        <v>0</v>
+      </c>
+      <c r="E158" s="12">
+        <f t="shared" si="16"/>
+        <v>8075</v>
+      </c>
+      <c r="F158" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="5">
+        <f t="shared" si="18"/>
+        <v>158</v>
+      </c>
+      <c r="B159" s="10">
+        <v>100</v>
+      </c>
+      <c r="C159" s="10">
+        <v>0</v>
+      </c>
+      <c r="E159" s="12">
+        <f t="shared" si="16"/>
+        <v>8175</v>
+      </c>
+      <c r="F159" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="5">
+        <f t="shared" si="18"/>
+        <v>159</v>
+      </c>
+      <c r="B160" s="10">
+        <v>100</v>
+      </c>
+      <c r="C160" s="10">
+        <v>0</v>
+      </c>
+      <c r="E160" s="12">
+        <f t="shared" si="16"/>
+        <v>8275</v>
+      </c>
+      <c r="F160" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="5">
+        <f t="shared" si="18"/>
+        <v>160</v>
+      </c>
+      <c r="B161" s="10">
+        <v>100</v>
+      </c>
+      <c r="C161" s="10">
+        <v>0</v>
+      </c>
+      <c r="E161" s="12">
+        <f t="shared" si="16"/>
+        <v>8375</v>
+      </c>
+      <c r="F161" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="5">
+        <f t="shared" si="18"/>
+        <v>161</v>
+      </c>
+      <c r="B162" s="10">
+        <v>100</v>
+      </c>
+      <c r="C162" s="10">
+        <v>0</v>
+      </c>
+      <c r="E162" s="12">
+        <f t="shared" si="16"/>
+        <v>8475</v>
+      </c>
+      <c r="F162" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="5">
+        <f t="shared" si="18"/>
+        <v>162</v>
+      </c>
+      <c r="B163" s="10">
+        <v>100</v>
+      </c>
+      <c r="C163" s="10">
+        <v>0</v>
+      </c>
+      <c r="E163" s="12">
+        <f t="shared" si="16"/>
+        <v>8575</v>
+      </c>
+      <c r="F163" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="5">
+        <f t="shared" si="18"/>
+        <v>163</v>
+      </c>
+      <c r="B164" s="10">
+        <v>100</v>
+      </c>
+      <c r="C164" s="10">
+        <v>0</v>
+      </c>
+      <c r="E164" s="12">
+        <f t="shared" si="16"/>
+        <v>8675</v>
+      </c>
+      <c r="F164" s="13">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="5">
+        <f t="shared" si="18"/>
+        <v>164</v>
+      </c>
+      <c r="B165" s="10">
+        <v>100</v>
+      </c>
+      <c r="C165" s="10">
+        <v>0</v>
+      </c>
+      <c r="E165" s="12">
+        <f t="shared" ref="E165:E228" si="19">E164+B165</f>
+        <v>8775</v>
+      </c>
+      <c r="F165" s="13">
+        <f t="shared" ref="F165:F228" si="20">B165-B164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="5">
+        <f t="shared" si="18"/>
+        <v>165</v>
+      </c>
+      <c r="B166" s="10">
+        <v>100</v>
+      </c>
+      <c r="C166" s="10">
+        <v>0</v>
+      </c>
+      <c r="E166" s="12">
+        <f t="shared" si="19"/>
+        <v>8875</v>
+      </c>
+      <c r="F166" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="5">
+        <f t="shared" si="18"/>
+        <v>166</v>
+      </c>
+      <c r="B167" s="10">
+        <v>100</v>
+      </c>
+      <c r="C167" s="10">
+        <v>0</v>
+      </c>
+      <c r="E167" s="12">
+        <f t="shared" si="19"/>
+        <v>8975</v>
+      </c>
+      <c r="F167" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="5">
+        <f t="shared" si="18"/>
+        <v>167</v>
+      </c>
+      <c r="B168" s="10">
+        <v>100</v>
+      </c>
+      <c r="C168" s="10">
+        <v>0</v>
+      </c>
+      <c r="E168" s="12">
+        <f t="shared" si="19"/>
+        <v>9075</v>
+      </c>
+      <c r="F168" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="5">
+        <f t="shared" si="18"/>
+        <v>168</v>
+      </c>
+      <c r="B169" s="10">
+        <v>100</v>
+      </c>
+      <c r="C169" s="10">
+        <v>0</v>
+      </c>
+      <c r="E169" s="12">
+        <f t="shared" si="19"/>
+        <v>9175</v>
+      </c>
+      <c r="F169" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="5">
+        <f t="shared" si="18"/>
+        <v>169</v>
+      </c>
+      <c r="B170" s="10">
+        <v>100</v>
+      </c>
+      <c r="C170" s="10">
+        <v>0</v>
+      </c>
+      <c r="E170" s="12">
+        <f t="shared" si="19"/>
+        <v>9275</v>
+      </c>
+      <c r="F170" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="5">
+        <f t="shared" si="18"/>
+        <v>170</v>
+      </c>
+      <c r="B171" s="10">
+        <v>100</v>
+      </c>
+      <c r="C171" s="10">
+        <v>0</v>
+      </c>
+      <c r="E171" s="12">
+        <f t="shared" si="19"/>
+        <v>9375</v>
+      </c>
+      <c r="F171" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="5">
+        <f t="shared" si="18"/>
+        <v>171</v>
+      </c>
+      <c r="B172" s="10">
+        <v>100</v>
+      </c>
+      <c r="C172" s="10">
+        <v>0</v>
+      </c>
+      <c r="E172" s="12">
+        <f t="shared" si="19"/>
+        <v>9475</v>
+      </c>
+      <c r="F172" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="5">
+        <f t="shared" si="18"/>
+        <v>172</v>
+      </c>
+      <c r="B173" s="10">
+        <v>100</v>
+      </c>
+      <c r="C173" s="10">
+        <v>0</v>
+      </c>
+      <c r="E173" s="12">
+        <f t="shared" si="19"/>
+        <v>9575</v>
+      </c>
+      <c r="F173" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="5">
+        <f t="shared" si="18"/>
+        <v>173</v>
+      </c>
+      <c r="B174" s="10">
+        <v>100</v>
+      </c>
+      <c r="C174" s="10">
+        <v>0</v>
+      </c>
+      <c r="E174" s="12">
+        <f t="shared" si="19"/>
+        <v>9675</v>
+      </c>
+      <c r="F174" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="5">
+        <f t="shared" si="18"/>
+        <v>174</v>
+      </c>
+      <c r="B175" s="10">
+        <v>100</v>
+      </c>
+      <c r="C175" s="10">
+        <v>0</v>
+      </c>
+      <c r="E175" s="12">
+        <f t="shared" si="19"/>
+        <v>9775</v>
+      </c>
+      <c r="F175" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="5">
+        <f t="shared" si="18"/>
+        <v>175</v>
+      </c>
+      <c r="B176" s="10">
+        <v>100</v>
+      </c>
+      <c r="C176" s="10">
+        <v>0</v>
+      </c>
+      <c r="E176" s="12">
+        <f t="shared" si="19"/>
+        <v>9875</v>
+      </c>
+      <c r="F176" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="5">
+        <f t="shared" si="18"/>
+        <v>176</v>
+      </c>
+      <c r="B177" s="10">
+        <v>100</v>
+      </c>
+      <c r="C177" s="10">
+        <v>0</v>
+      </c>
+      <c r="E177" s="12">
+        <f t="shared" si="19"/>
+        <v>9975</v>
+      </c>
+      <c r="F177" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="5">
+        <f t="shared" si="18"/>
+        <v>177</v>
+      </c>
+      <c r="B178" s="10">
+        <v>100</v>
+      </c>
+      <c r="C178" s="10">
+        <v>0</v>
+      </c>
+      <c r="E178" s="12">
+        <f t="shared" si="19"/>
+        <v>10075</v>
+      </c>
+      <c r="F178" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="5">
+        <f t="shared" si="18"/>
+        <v>178</v>
+      </c>
+      <c r="B179" s="10">
+        <v>100</v>
+      </c>
+      <c r="C179" s="10">
+        <v>0</v>
+      </c>
+      <c r="E179" s="12">
+        <f t="shared" si="19"/>
+        <v>10175</v>
+      </c>
+      <c r="F179" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="5">
+        <f t="shared" si="18"/>
+        <v>179</v>
+      </c>
+      <c r="B180" s="10">
+        <v>100</v>
+      </c>
+      <c r="C180" s="10">
+        <v>0</v>
+      </c>
+      <c r="E180" s="12">
+        <f t="shared" si="19"/>
+        <v>10275</v>
+      </c>
+      <c r="F180" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="5">
+        <f t="shared" si="18"/>
+        <v>180</v>
+      </c>
+      <c r="B181" s="10">
+        <v>100</v>
+      </c>
+      <c r="C181" s="10">
+        <v>0</v>
+      </c>
+      <c r="E181" s="12">
+        <f t="shared" si="19"/>
+        <v>10375</v>
+      </c>
+      <c r="F181" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="5">
+        <f t="shared" si="18"/>
+        <v>181</v>
+      </c>
+      <c r="B182" s="10">
+        <v>100</v>
+      </c>
+      <c r="C182" s="10">
+        <v>0</v>
+      </c>
+      <c r="E182" s="12">
+        <f t="shared" si="19"/>
+        <v>10475</v>
+      </c>
+      <c r="F182" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="5">
+        <f t="shared" si="18"/>
+        <v>182</v>
+      </c>
+      <c r="B183" s="10">
+        <v>100</v>
+      </c>
+      <c r="C183" s="10">
+        <v>0</v>
+      </c>
+      <c r="E183" s="12">
+        <f t="shared" si="19"/>
+        <v>10575</v>
+      </c>
+      <c r="F183" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="5">
+        <f t="shared" si="18"/>
+        <v>183</v>
+      </c>
+      <c r="B184" s="10">
+        <v>100</v>
+      </c>
+      <c r="C184" s="10">
+        <v>0</v>
+      </c>
+      <c r="E184" s="12">
+        <f t="shared" si="19"/>
+        <v>10675</v>
+      </c>
+      <c r="F184" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="5">
+        <f t="shared" si="18"/>
+        <v>184</v>
+      </c>
+      <c r="B185" s="10">
+        <v>100</v>
+      </c>
+      <c r="C185" s="10">
+        <v>0</v>
+      </c>
+      <c r="E185" s="12">
+        <f t="shared" si="19"/>
+        <v>10775</v>
+      </c>
+      <c r="F185" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="5">
+        <f t="shared" si="18"/>
+        <v>185</v>
+      </c>
+      <c r="B186" s="10">
+        <v>100</v>
+      </c>
+      <c r="C186" s="10">
+        <v>0</v>
+      </c>
+      <c r="E186" s="12">
+        <f t="shared" si="19"/>
+        <v>10875</v>
+      </c>
+      <c r="F186" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="5">
+        <f t="shared" si="18"/>
+        <v>186</v>
+      </c>
+      <c r="B187" s="10">
+        <v>100</v>
+      </c>
+      <c r="C187" s="10">
+        <v>0</v>
+      </c>
+      <c r="E187" s="12">
+        <f t="shared" si="19"/>
+        <v>10975</v>
+      </c>
+      <c r="F187" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="5">
+        <f t="shared" si="18"/>
+        <v>187</v>
+      </c>
+      <c r="B188" s="10">
+        <v>100</v>
+      </c>
+      <c r="C188" s="10">
+        <v>0</v>
+      </c>
+      <c r="E188" s="12">
+        <f t="shared" si="19"/>
+        <v>11075</v>
+      </c>
+      <c r="F188" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="5">
+        <f t="shared" si="18"/>
+        <v>188</v>
+      </c>
+      <c r="B189" s="10">
+        <v>100</v>
+      </c>
+      <c r="C189" s="10">
+        <v>0</v>
+      </c>
+      <c r="E189" s="12">
+        <f t="shared" si="19"/>
+        <v>11175</v>
+      </c>
+      <c r="F189" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="5">
+        <f t="shared" si="18"/>
+        <v>189</v>
+      </c>
+      <c r="B190" s="10">
+        <v>100</v>
+      </c>
+      <c r="C190" s="10">
+        <v>0</v>
+      </c>
+      <c r="E190" s="12">
+        <f t="shared" si="19"/>
+        <v>11275</v>
+      </c>
+      <c r="F190" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="5">
+        <f t="shared" si="18"/>
+        <v>190</v>
+      </c>
+      <c r="B191" s="10">
+        <v>100</v>
+      </c>
+      <c r="C191" s="10">
+        <v>0</v>
+      </c>
+      <c r="E191" s="12">
+        <f t="shared" si="19"/>
+        <v>11375</v>
+      </c>
+      <c r="F191" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="5">
+        <f t="shared" si="18"/>
+        <v>191</v>
+      </c>
+      <c r="B192" s="10">
+        <v>100</v>
+      </c>
+      <c r="C192" s="10">
+        <v>0</v>
+      </c>
+      <c r="E192" s="12">
+        <f t="shared" si="19"/>
+        <v>11475</v>
+      </c>
+      <c r="F192" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="5">
+        <f t="shared" si="18"/>
+        <v>192</v>
+      </c>
+      <c r="B193" s="10">
+        <v>100</v>
+      </c>
+      <c r="C193" s="10">
+        <v>0</v>
+      </c>
+      <c r="E193" s="12">
+        <f t="shared" si="19"/>
+        <v>11575</v>
+      </c>
+      <c r="F193" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="5">
+        <f t="shared" si="18"/>
+        <v>193</v>
+      </c>
+      <c r="B194" s="10">
+        <v>100</v>
+      </c>
+      <c r="C194" s="10">
+        <v>0</v>
+      </c>
+      <c r="E194" s="12">
+        <f t="shared" si="19"/>
+        <v>11675</v>
+      </c>
+      <c r="F194" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="5">
+        <f t="shared" si="18"/>
+        <v>194</v>
+      </c>
+      <c r="B195" s="10">
+        <v>100</v>
+      </c>
+      <c r="C195" s="10">
+        <v>0</v>
+      </c>
+      <c r="E195" s="12">
+        <f t="shared" si="19"/>
+        <v>11775</v>
+      </c>
+      <c r="F195" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="5">
+        <f t="shared" si="18"/>
+        <v>195</v>
+      </c>
+      <c r="B196" s="10">
+        <v>100</v>
+      </c>
+      <c r="C196" s="10">
+        <v>0</v>
+      </c>
+      <c r="E196" s="12">
+        <f t="shared" si="19"/>
+        <v>11875</v>
+      </c>
+      <c r="F196" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="5">
+        <f t="shared" si="18"/>
+        <v>196</v>
+      </c>
+      <c r="B197" s="10">
+        <v>100</v>
+      </c>
+      <c r="C197" s="10">
+        <v>0</v>
+      </c>
+      <c r="E197" s="12">
+        <f t="shared" si="19"/>
+        <v>11975</v>
+      </c>
+      <c r="F197" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="5">
+        <f t="shared" si="18"/>
+        <v>197</v>
+      </c>
+      <c r="B198" s="10">
+        <v>100</v>
+      </c>
+      <c r="C198" s="10">
+        <v>0</v>
+      </c>
+      <c r="E198" s="12">
+        <f t="shared" si="19"/>
+        <v>12075</v>
+      </c>
+      <c r="F198" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="5">
+        <f t="shared" si="18"/>
+        <v>198</v>
+      </c>
+      <c r="B199" s="10">
+        <v>100</v>
+      </c>
+      <c r="C199" s="10">
+        <v>0</v>
+      </c>
+      <c r="E199" s="12">
+        <f t="shared" si="19"/>
+        <v>12175</v>
+      </c>
+      <c r="F199" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="5">
+        <f t="shared" si="18"/>
+        <v>199</v>
+      </c>
+      <c r="B200" s="10">
+        <v>100</v>
+      </c>
+      <c r="C200" s="10">
+        <v>0</v>
+      </c>
+      <c r="E200" s="12">
+        <f t="shared" si="19"/>
+        <v>12275</v>
+      </c>
+      <c r="F200" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="5">
+        <f t="shared" si="18"/>
+        <v>200</v>
+      </c>
+      <c r="B201" s="10">
+        <v>100</v>
+      </c>
+      <c r="C201" s="10">
+        <v>0</v>
+      </c>
+      <c r="E201" s="12">
+        <f t="shared" si="19"/>
+        <v>12375</v>
+      </c>
+      <c r="F201" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="5">
+        <f t="shared" si="18"/>
+        <v>201</v>
+      </c>
+      <c r="B202" s="10">
+        <v>100</v>
+      </c>
+      <c r="C202" s="10">
+        <v>0</v>
+      </c>
+      <c r="E202" s="12">
+        <f t="shared" si="19"/>
+        <v>12475</v>
+      </c>
+      <c r="F202" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="5">
+        <f t="shared" si="18"/>
+        <v>202</v>
+      </c>
+      <c r="B203" s="10">
+        <v>100</v>
+      </c>
+      <c r="C203" s="10">
+        <v>0</v>
+      </c>
+      <c r="E203" s="12">
+        <f t="shared" si="19"/>
+        <v>12575</v>
+      </c>
+      <c r="F203" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="5">
+        <f t="shared" si="18"/>
+        <v>203</v>
+      </c>
+      <c r="B204" s="10">
+        <v>100</v>
+      </c>
+      <c r="C204" s="10">
+        <v>0</v>
+      </c>
+      <c r="E204" s="12">
+        <f t="shared" si="19"/>
+        <v>12675</v>
+      </c>
+      <c r="F204" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="5">
+        <f t="shared" si="18"/>
+        <v>204</v>
+      </c>
+      <c r="B205" s="10">
+        <v>100</v>
+      </c>
+      <c r="C205" s="10">
+        <v>0</v>
+      </c>
+      <c r="E205" s="12">
+        <f t="shared" si="19"/>
+        <v>12775</v>
+      </c>
+      <c r="F205" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="5">
+        <f t="shared" si="18"/>
+        <v>205</v>
+      </c>
+      <c r="B206" s="10">
+        <v>100</v>
+      </c>
+      <c r="C206" s="10">
+        <v>0</v>
+      </c>
+      <c r="E206" s="12">
+        <f t="shared" si="19"/>
+        <v>12875</v>
+      </c>
+      <c r="F206" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="5">
+        <f t="shared" si="18"/>
+        <v>206</v>
+      </c>
+      <c r="B207" s="10">
+        <v>100</v>
+      </c>
+      <c r="C207" s="10">
+        <v>0</v>
+      </c>
+      <c r="E207" s="12">
+        <f t="shared" si="19"/>
+        <v>12975</v>
+      </c>
+      <c r="F207" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="5">
+        <f t="shared" si="18"/>
+        <v>207</v>
+      </c>
+      <c r="B208" s="10">
+        <v>100</v>
+      </c>
+      <c r="C208" s="10">
+        <v>0</v>
+      </c>
+      <c r="E208" s="12">
+        <f t="shared" si="19"/>
+        <v>13075</v>
+      </c>
+      <c r="F208" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="5">
+        <f t="shared" si="18"/>
+        <v>208</v>
+      </c>
+      <c r="B209" s="10">
+        <v>100</v>
+      </c>
+      <c r="C209" s="10">
+        <v>0</v>
+      </c>
+      <c r="E209" s="12">
+        <f t="shared" si="19"/>
+        <v>13175</v>
+      </c>
+      <c r="F209" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" s="5">
+        <f t="shared" si="18"/>
+        <v>209</v>
+      </c>
+      <c r="B210" s="10">
+        <v>100</v>
+      </c>
+      <c r="C210" s="10">
+        <v>0</v>
+      </c>
+      <c r="E210" s="12">
+        <f t="shared" si="19"/>
+        <v>13275</v>
+      </c>
+      <c r="F210" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" s="5">
+        <f t="shared" si="18"/>
+        <v>210</v>
+      </c>
+      <c r="B211" s="10">
+        <v>100</v>
+      </c>
+      <c r="C211" s="10">
+        <v>0</v>
+      </c>
+      <c r="E211" s="12">
+        <f t="shared" si="19"/>
+        <v>13375</v>
+      </c>
+      <c r="F211" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" s="5">
+        <f t="shared" si="18"/>
+        <v>211</v>
+      </c>
+      <c r="B212" s="10">
+        <v>100</v>
+      </c>
+      <c r="C212" s="10">
+        <v>0</v>
+      </c>
+      <c r="E212" s="12">
+        <f t="shared" si="19"/>
+        <v>13475</v>
+      </c>
+      <c r="F212" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" s="5">
+        <f t="shared" si="18"/>
+        <v>212</v>
+      </c>
+      <c r="B213" s="10">
+        <v>100</v>
+      </c>
+      <c r="C213" s="10">
+        <v>0</v>
+      </c>
+      <c r="E213" s="12">
+        <f t="shared" si="19"/>
+        <v>13575</v>
+      </c>
+      <c r="F213" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="5">
+        <f t="shared" si="18"/>
+        <v>213</v>
+      </c>
+      <c r="B214" s="10">
+        <v>100</v>
+      </c>
+      <c r="C214" s="10">
+        <v>0</v>
+      </c>
+      <c r="E214" s="12">
+        <f t="shared" si="19"/>
+        <v>13675</v>
+      </c>
+      <c r="F214" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="5">
+        <f t="shared" si="18"/>
+        <v>214</v>
+      </c>
+      <c r="B215" s="10">
+        <v>100</v>
+      </c>
+      <c r="C215" s="10">
+        <v>0</v>
+      </c>
+      <c r="E215" s="12">
+        <f t="shared" si="19"/>
+        <v>13775</v>
+      </c>
+      <c r="F215" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="5">
+        <f t="shared" si="18"/>
+        <v>215</v>
+      </c>
+      <c r="B216" s="10">
+        <v>100</v>
+      </c>
+      <c r="C216" s="10">
+        <v>0</v>
+      </c>
+      <c r="E216" s="12">
+        <f t="shared" si="19"/>
+        <v>13875</v>
+      </c>
+      <c r="F216" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" s="5">
+        <f t="shared" si="18"/>
+        <v>216</v>
+      </c>
+      <c r="B217" s="10">
+        <v>100</v>
+      </c>
+      <c r="C217" s="10">
+        <v>0</v>
+      </c>
+      <c r="E217" s="12">
+        <f t="shared" si="19"/>
+        <v>13975</v>
+      </c>
+      <c r="F217" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" s="5">
+        <f t="shared" si="18"/>
+        <v>217</v>
+      </c>
+      <c r="B218" s="10">
+        <v>100</v>
+      </c>
+      <c r="C218" s="10">
+        <v>0</v>
+      </c>
+      <c r="E218" s="12">
+        <f t="shared" si="19"/>
+        <v>14075</v>
+      </c>
+      <c r="F218" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" s="5">
+        <f t="shared" si="18"/>
+        <v>218</v>
+      </c>
+      <c r="B219" s="10">
+        <v>100</v>
+      </c>
+      <c r="C219" s="10">
+        <v>0</v>
+      </c>
+      <c r="E219" s="12">
+        <f t="shared" si="19"/>
+        <v>14175</v>
+      </c>
+      <c r="F219" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="5">
+        <f t="shared" si="18"/>
+        <v>219</v>
+      </c>
+      <c r="B220" s="10">
+        <v>100</v>
+      </c>
+      <c r="C220" s="10">
+        <v>0</v>
+      </c>
+      <c r="E220" s="12">
+        <f t="shared" si="19"/>
+        <v>14275</v>
+      </c>
+      <c r="F220" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" s="5">
+        <f t="shared" si="18"/>
+        <v>220</v>
+      </c>
+      <c r="B221" s="10">
+        <v>100</v>
+      </c>
+      <c r="C221" s="10">
+        <v>0</v>
+      </c>
+      <c r="E221" s="12">
+        <f t="shared" si="19"/>
+        <v>14375</v>
+      </c>
+      <c r="F221" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="5">
+        <f t="shared" ref="A222:A285" si="21">A221+1</f>
+        <v>221</v>
+      </c>
+      <c r="B222" s="10">
+        <v>100</v>
+      </c>
+      <c r="C222" s="10">
+        <v>0</v>
+      </c>
+      <c r="E222" s="12">
+        <f t="shared" si="19"/>
+        <v>14475</v>
+      </c>
+      <c r="F222" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="5">
+        <f t="shared" si="21"/>
+        <v>222</v>
+      </c>
+      <c r="B223" s="10">
+        <v>100</v>
+      </c>
+      <c r="C223" s="10">
+        <v>0</v>
+      </c>
+      <c r="E223" s="12">
+        <f t="shared" si="19"/>
+        <v>14575</v>
+      </c>
+      <c r="F223" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="5">
+        <f t="shared" si="21"/>
+        <v>223</v>
+      </c>
+      <c r="B224" s="10">
+        <v>100</v>
+      </c>
+      <c r="C224" s="10">
+        <v>0</v>
+      </c>
+      <c r="E224" s="12">
+        <f t="shared" si="19"/>
+        <v>14675</v>
+      </c>
+      <c r="F224" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="5">
+        <f t="shared" si="21"/>
+        <v>224</v>
+      </c>
+      <c r="B225" s="10">
+        <v>100</v>
+      </c>
+      <c r="C225" s="10">
+        <v>0</v>
+      </c>
+      <c r="E225" s="12">
+        <f t="shared" si="19"/>
+        <v>14775</v>
+      </c>
+      <c r="F225" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="5">
+        <f t="shared" si="21"/>
+        <v>225</v>
+      </c>
+      <c r="B226" s="10">
+        <v>100</v>
+      </c>
+      <c r="C226" s="10">
+        <v>0</v>
+      </c>
+      <c r="E226" s="12">
+        <f t="shared" si="19"/>
+        <v>14875</v>
+      </c>
+      <c r="F226" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="5">
+        <f t="shared" si="21"/>
+        <v>226</v>
+      </c>
+      <c r="B227" s="10">
+        <v>100</v>
+      </c>
+      <c r="C227" s="10">
+        <v>0</v>
+      </c>
+      <c r="E227" s="12">
+        <f t="shared" si="19"/>
+        <v>14975</v>
+      </c>
+      <c r="F227" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228" s="5">
+        <f t="shared" si="21"/>
+        <v>227</v>
+      </c>
+      <c r="B228" s="10">
+        <v>100</v>
+      </c>
+      <c r="C228" s="10">
+        <v>0</v>
+      </c>
+      <c r="E228" s="12">
+        <f t="shared" si="19"/>
+        <v>15075</v>
+      </c>
+      <c r="F228" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229" s="5">
+        <f t="shared" si="21"/>
+        <v>228</v>
+      </c>
+      <c r="B229" s="10">
+        <v>100</v>
+      </c>
+      <c r="C229" s="10">
+        <v>0</v>
+      </c>
+      <c r="E229" s="12">
+        <f t="shared" ref="E229:E292" si="22">E228+B229</f>
+        <v>15175</v>
+      </c>
+      <c r="F229" s="13">
+        <f t="shared" ref="F229:F292" si="23">B229-B228</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230" s="5">
+        <f t="shared" si="21"/>
+        <v>229</v>
+      </c>
+      <c r="B230" s="10">
+        <v>100</v>
+      </c>
+      <c r="C230" s="10">
+        <v>0</v>
+      </c>
+      <c r="E230" s="12">
+        <f t="shared" si="22"/>
+        <v>15275</v>
+      </c>
+      <c r="F230" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231" s="5">
+        <f t="shared" si="21"/>
+        <v>230</v>
+      </c>
+      <c r="B231" s="10">
+        <v>100</v>
+      </c>
+      <c r="C231" s="10">
+        <v>0</v>
+      </c>
+      <c r="E231" s="12">
+        <f t="shared" si="22"/>
+        <v>15375</v>
+      </c>
+      <c r="F231" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="5">
+        <f t="shared" si="21"/>
+        <v>231</v>
+      </c>
+      <c r="B232" s="10">
+        <v>100</v>
+      </c>
+      <c r="C232" s="10">
+        <v>0</v>
+      </c>
+      <c r="E232" s="12">
+        <f t="shared" si="22"/>
+        <v>15475</v>
+      </c>
+      <c r="F232" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="5">
+        <f t="shared" si="21"/>
+        <v>232</v>
+      </c>
+      <c r="B233" s="10">
+        <v>100</v>
+      </c>
+      <c r="C233" s="10">
+        <v>0</v>
+      </c>
+      <c r="E233" s="12">
+        <f t="shared" si="22"/>
+        <v>15575</v>
+      </c>
+      <c r="F233" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="5">
+        <f t="shared" si="21"/>
+        <v>233</v>
+      </c>
+      <c r="B234" s="10">
+        <v>100</v>
+      </c>
+      <c r="C234" s="10">
+        <v>0</v>
+      </c>
+      <c r="E234" s="12">
+        <f t="shared" si="22"/>
+        <v>15675</v>
+      </c>
+      <c r="F234" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235" s="5">
+        <f t="shared" si="21"/>
+        <v>234</v>
+      </c>
+      <c r="B235" s="10">
+        <v>100</v>
+      </c>
+      <c r="C235" s="10">
+        <v>0</v>
+      </c>
+      <c r="E235" s="12">
+        <f t="shared" si="22"/>
+        <v>15775</v>
+      </c>
+      <c r="F235" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236" s="5">
+        <f t="shared" si="21"/>
+        <v>235</v>
+      </c>
+      <c r="B236" s="10">
+        <v>100</v>
+      </c>
+      <c r="C236" s="10">
+        <v>0</v>
+      </c>
+      <c r="E236" s="12">
+        <f t="shared" si="22"/>
+        <v>15875</v>
+      </c>
+      <c r="F236" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237" s="5">
+        <f t="shared" si="21"/>
+        <v>236</v>
+      </c>
+      <c r="B237" s="10">
+        <v>100</v>
+      </c>
+      <c r="C237" s="10">
+        <v>0</v>
+      </c>
+      <c r="E237" s="12">
+        <f t="shared" si="22"/>
+        <v>15975</v>
+      </c>
+      <c r="F237" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238" s="5">
+        <f t="shared" si="21"/>
+        <v>237</v>
+      </c>
+      <c r="B238" s="10">
+        <v>100</v>
+      </c>
+      <c r="C238" s="10">
+        <v>0</v>
+      </c>
+      <c r="E238" s="12">
+        <f t="shared" si="22"/>
+        <v>16075</v>
+      </c>
+      <c r="F238" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239" s="5">
+        <f t="shared" si="21"/>
+        <v>238</v>
+      </c>
+      <c r="B239" s="10">
+        <v>100</v>
+      </c>
+      <c r="C239" s="10">
+        <v>0</v>
+      </c>
+      <c r="E239" s="12">
+        <f t="shared" si="22"/>
+        <v>16175</v>
+      </c>
+      <c r="F239" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240" s="5">
+        <f t="shared" si="21"/>
+        <v>239</v>
+      </c>
+      <c r="B240" s="10">
+        <v>100</v>
+      </c>
+      <c r="C240" s="10">
+        <v>0</v>
+      </c>
+      <c r="E240" s="12">
+        <f t="shared" si="22"/>
+        <v>16275</v>
+      </c>
+      <c r="F240" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241" s="5">
+        <f t="shared" si="21"/>
+        <v>240</v>
+      </c>
+      <c r="B241" s="10">
+        <v>100</v>
+      </c>
+      <c r="C241" s="10">
+        <v>0</v>
+      </c>
+      <c r="E241" s="12">
+        <f t="shared" si="22"/>
+        <v>16375</v>
+      </c>
+      <c r="F241" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242" s="5">
+        <f t="shared" si="21"/>
+        <v>241</v>
+      </c>
+      <c r="B242" s="10">
+        <v>100</v>
+      </c>
+      <c r="C242" s="10">
+        <v>0</v>
+      </c>
+      <c r="E242" s="12">
+        <f t="shared" si="22"/>
+        <v>16475</v>
+      </c>
+      <c r="F242" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243" s="5">
+        <f t="shared" si="21"/>
+        <v>242</v>
+      </c>
+      <c r="B243" s="10">
+        <v>100</v>
+      </c>
+      <c r="C243" s="10">
+        <v>0</v>
+      </c>
+      <c r="E243" s="12">
+        <f t="shared" si="22"/>
+        <v>16575</v>
+      </c>
+      <c r="F243" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" s="5">
+        <f t="shared" si="21"/>
+        <v>243</v>
+      </c>
+      <c r="B244" s="10">
+        <v>100</v>
+      </c>
+      <c r="C244" s="10">
+        <v>0</v>
+      </c>
+      <c r="E244" s="12">
+        <f t="shared" si="22"/>
+        <v>16675</v>
+      </c>
+      <c r="F244" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245" s="5">
+        <f t="shared" si="21"/>
+        <v>244</v>
+      </c>
+      <c r="B245" s="10">
+        <v>100</v>
+      </c>
+      <c r="C245" s="10">
+        <v>0</v>
+      </c>
+      <c r="E245" s="12">
+        <f t="shared" si="22"/>
+        <v>16775</v>
+      </c>
+      <c r="F245" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246" s="5">
+        <f t="shared" si="21"/>
+        <v>245</v>
+      </c>
+      <c r="B246" s="10">
+        <v>100</v>
+      </c>
+      <c r="C246" s="10">
+        <v>0</v>
+      </c>
+      <c r="E246" s="12">
+        <f t="shared" si="22"/>
+        <v>16875</v>
+      </c>
+      <c r="F246" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247" s="5">
+        <f t="shared" si="21"/>
+        <v>246</v>
+      </c>
+      <c r="B247" s="10">
+        <v>100</v>
+      </c>
+      <c r="C247" s="10">
+        <v>0</v>
+      </c>
+      <c r="E247" s="12">
+        <f t="shared" si="22"/>
+        <v>16975</v>
+      </c>
+      <c r="F247" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" s="5">
+        <f t="shared" si="21"/>
+        <v>247</v>
+      </c>
+      <c r="B248" s="10">
+        <v>100</v>
+      </c>
+      <c r="C248" s="10">
+        <v>0</v>
+      </c>
+      <c r="E248" s="12">
+        <f t="shared" si="22"/>
+        <v>17075</v>
+      </c>
+      <c r="F248" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249" s="5">
+        <f t="shared" si="21"/>
+        <v>248</v>
+      </c>
+      <c r="B249" s="10">
+        <v>100</v>
+      </c>
+      <c r="C249" s="10">
+        <v>0</v>
+      </c>
+      <c r="E249" s="12">
+        <f t="shared" si="22"/>
+        <v>17175</v>
+      </c>
+      <c r="F249" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250" s="5">
+        <f t="shared" si="21"/>
+        <v>249</v>
+      </c>
+      <c r="B250" s="10">
+        <v>100</v>
+      </c>
+      <c r="C250" s="10">
+        <v>0</v>
+      </c>
+      <c r="E250" s="12">
+        <f t="shared" si="22"/>
+        <v>17275</v>
+      </c>
+      <c r="F250" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251" s="5">
+        <f t="shared" si="21"/>
+        <v>250</v>
+      </c>
+      <c r="B251" s="10">
+        <v>100</v>
+      </c>
+      <c r="C251" s="10">
+        <v>0</v>
+      </c>
+      <c r="E251" s="12">
+        <f t="shared" si="22"/>
+        <v>17375</v>
+      </c>
+      <c r="F251" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252" s="5">
+        <f t="shared" si="21"/>
+        <v>251</v>
+      </c>
+      <c r="B252" s="10">
+        <v>100</v>
+      </c>
+      <c r="C252" s="10">
+        <v>0</v>
+      </c>
+      <c r="E252" s="12">
+        <f t="shared" si="22"/>
+        <v>17475</v>
+      </c>
+      <c r="F252" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253" s="5">
+        <f t="shared" si="21"/>
+        <v>252</v>
+      </c>
+      <c r="B253" s="10">
+        <v>100</v>
+      </c>
+      <c r="C253" s="10">
+        <v>0</v>
+      </c>
+      <c r="E253" s="12">
+        <f t="shared" si="22"/>
+        <v>17575</v>
+      </c>
+      <c r="F253" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254" s="5">
+        <f t="shared" si="21"/>
+        <v>253</v>
+      </c>
+      <c r="B254" s="10">
+        <v>100</v>
+      </c>
+      <c r="C254" s="10">
+        <v>0</v>
+      </c>
+      <c r="E254" s="12">
+        <f t="shared" si="22"/>
+        <v>17675</v>
+      </c>
+      <c r="F254" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255" s="5">
+        <f t="shared" si="21"/>
+        <v>254</v>
+      </c>
+      <c r="B255" s="10">
+        <v>100</v>
+      </c>
+      <c r="C255" s="10">
+        <v>0</v>
+      </c>
+      <c r="E255" s="12">
+        <f t="shared" si="22"/>
+        <v>17775</v>
+      </c>
+      <c r="F255" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256" s="5">
+        <f t="shared" si="21"/>
+        <v>255</v>
+      </c>
+      <c r="B256" s="10">
+        <v>100</v>
+      </c>
+      <c r="C256" s="10">
+        <v>0</v>
+      </c>
+      <c r="E256" s="12">
+        <f t="shared" si="22"/>
+        <v>17875</v>
+      </c>
+      <c r="F256" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257" s="5">
+        <f t="shared" si="21"/>
+        <v>256</v>
+      </c>
+      <c r="B257" s="10">
+        <v>100</v>
+      </c>
+      <c r="C257" s="10">
+        <v>0</v>
+      </c>
+      <c r="E257" s="12">
+        <f t="shared" si="22"/>
+        <v>17975</v>
+      </c>
+      <c r="F257" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258" s="5">
+        <f t="shared" si="21"/>
+        <v>257</v>
+      </c>
+      <c r="B258" s="10">
+        <v>100</v>
+      </c>
+      <c r="C258" s="10">
+        <v>0</v>
+      </c>
+      <c r="E258" s="12">
+        <f t="shared" si="22"/>
+        <v>18075</v>
+      </c>
+      <c r="F258" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="5">
+        <f t="shared" si="21"/>
+        <v>258</v>
+      </c>
+      <c r="B259" s="10">
+        <v>100</v>
+      </c>
+      <c r="C259" s="10">
+        <v>0</v>
+      </c>
+      <c r="E259" s="12">
+        <f t="shared" si="22"/>
+        <v>18175</v>
+      </c>
+      <c r="F259" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260" s="5">
+        <f t="shared" si="21"/>
+        <v>259</v>
+      </c>
+      <c r="B260" s="10">
+        <v>100</v>
+      </c>
+      <c r="C260" s="10">
+        <v>0</v>
+      </c>
+      <c r="E260" s="12">
+        <f t="shared" si="22"/>
+        <v>18275</v>
+      </c>
+      <c r="F260" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="5">
+        <f t="shared" si="21"/>
+        <v>260</v>
+      </c>
+      <c r="B261" s="10">
+        <v>100</v>
+      </c>
+      <c r="C261" s="10">
+        <v>0</v>
+      </c>
+      <c r="E261" s="12">
+        <f t="shared" si="22"/>
+        <v>18375</v>
+      </c>
+      <c r="F261" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262" s="5">
+        <f t="shared" si="21"/>
+        <v>261</v>
+      </c>
+      <c r="B262" s="10">
+        <v>100</v>
+      </c>
+      <c r="C262" s="10">
+        <v>0</v>
+      </c>
+      <c r="E262" s="12">
+        <f t="shared" si="22"/>
+        <v>18475</v>
+      </c>
+      <c r="F262" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263" s="5">
+        <f t="shared" si="21"/>
+        <v>262</v>
+      </c>
+      <c r="B263" s="10">
+        <v>100</v>
+      </c>
+      <c r="C263" s="10">
+        <v>0</v>
+      </c>
+      <c r="E263" s="12">
+        <f t="shared" si="22"/>
+        <v>18575</v>
+      </c>
+      <c r="F263" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264" s="5">
+        <f t="shared" si="21"/>
+        <v>263</v>
+      </c>
+      <c r="B264" s="10">
+        <v>100</v>
+      </c>
+      <c r="C264" s="10">
+        <v>0</v>
+      </c>
+      <c r="E264" s="12">
+        <f t="shared" si="22"/>
+        <v>18675</v>
+      </c>
+      <c r="F264" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265" s="5">
+        <f t="shared" si="21"/>
+        <v>264</v>
+      </c>
+      <c r="B265" s="10">
+        <v>100</v>
+      </c>
+      <c r="C265" s="10">
+        <v>0</v>
+      </c>
+      <c r="E265" s="12">
+        <f t="shared" si="22"/>
+        <v>18775</v>
+      </c>
+      <c r="F265" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A266" s="5">
+        <f t="shared" si="21"/>
+        <v>265</v>
+      </c>
+      <c r="B266" s="10">
+        <v>100</v>
+      </c>
+      <c r="C266" s="10">
+        <v>0</v>
+      </c>
+      <c r="E266" s="12">
+        <f t="shared" si="22"/>
+        <v>18875</v>
+      </c>
+      <c r="F266" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A267" s="5">
+        <f t="shared" si="21"/>
+        <v>266</v>
+      </c>
+      <c r="B267" s="10">
+        <v>100</v>
+      </c>
+      <c r="C267" s="10">
+        <v>0</v>
+      </c>
+      <c r="E267" s="12">
+        <f t="shared" si="22"/>
+        <v>18975</v>
+      </c>
+      <c r="F267" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A268" s="5">
+        <f t="shared" si="21"/>
+        <v>267</v>
+      </c>
+      <c r="B268" s="10">
+        <v>100</v>
+      </c>
+      <c r="C268" s="10">
+        <v>0</v>
+      </c>
+      <c r="E268" s="12">
+        <f t="shared" si="22"/>
+        <v>19075</v>
+      </c>
+      <c r="F268" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
+        <f t="shared" si="21"/>
+        <v>268</v>
+      </c>
+      <c r="B269" s="10">
+        <v>100</v>
+      </c>
+      <c r="C269" s="10">
+        <v>0</v>
+      </c>
+      <c r="E269" s="12">
+        <f t="shared" si="22"/>
+        <v>19175</v>
+      </c>
+      <c r="F269" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
+        <f t="shared" si="21"/>
+        <v>269</v>
+      </c>
+      <c r="B270" s="10">
+        <v>100</v>
+      </c>
+      <c r="C270" s="10">
+        <v>0</v>
+      </c>
+      <c r="E270" s="12">
+        <f t="shared" si="22"/>
+        <v>19275</v>
+      </c>
+      <c r="F270" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A271" s="5">
+        <f t="shared" si="21"/>
+        <v>270</v>
+      </c>
+      <c r="B271" s="10">
+        <v>100</v>
+      </c>
+      <c r="C271" s="10">
+        <v>0</v>
+      </c>
+      <c r="E271" s="12">
+        <f t="shared" si="22"/>
+        <v>19375</v>
+      </c>
+      <c r="F271" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A272" s="5">
+        <f t="shared" si="21"/>
+        <v>271</v>
+      </c>
+      <c r="B272" s="10">
+        <v>100</v>
+      </c>
+      <c r="C272" s="10">
+        <v>0</v>
+      </c>
+      <c r="E272" s="12">
+        <f t="shared" si="22"/>
+        <v>19475</v>
+      </c>
+      <c r="F272" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A273" s="5">
+        <f t="shared" si="21"/>
+        <v>272</v>
+      </c>
+      <c r="B273" s="10">
+        <v>100</v>
+      </c>
+      <c r="C273" s="10">
+        <v>0</v>
+      </c>
+      <c r="E273" s="12">
+        <f t="shared" si="22"/>
+        <v>19575</v>
+      </c>
+      <c r="F273" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A274" s="5">
+        <f t="shared" si="21"/>
+        <v>273</v>
+      </c>
+      <c r="B274" s="10">
+        <v>100</v>
+      </c>
+      <c r="C274" s="10">
+        <v>0</v>
+      </c>
+      <c r="E274" s="12">
+        <f t="shared" si="22"/>
+        <v>19675</v>
+      </c>
+      <c r="F274" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A275" s="5">
+        <f t="shared" si="21"/>
+        <v>274</v>
+      </c>
+      <c r="B275" s="10">
+        <v>100</v>
+      </c>
+      <c r="C275" s="10">
+        <v>0</v>
+      </c>
+      <c r="E275" s="12">
+        <f t="shared" si="22"/>
+        <v>19775</v>
+      </c>
+      <c r="F275" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A276" s="5">
+        <f t="shared" si="21"/>
+        <v>275</v>
+      </c>
+      <c r="B276" s="10">
+        <v>100</v>
+      </c>
+      <c r="C276" s="10">
+        <v>0</v>
+      </c>
+      <c r="E276" s="12">
+        <f t="shared" si="22"/>
+        <v>19875</v>
+      </c>
+      <c r="F276" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277" s="5">
+        <f t="shared" si="21"/>
+        <v>276</v>
+      </c>
+      <c r="B277" s="10">
+        <v>100</v>
+      </c>
+      <c r="C277" s="10">
+        <v>0</v>
+      </c>
+      <c r="E277" s="12">
+        <f t="shared" si="22"/>
+        <v>19975</v>
+      </c>
+      <c r="F277" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A278" s="5">
+        <f t="shared" si="21"/>
+        <v>277</v>
+      </c>
+      <c r="B278" s="10">
+        <v>100</v>
+      </c>
+      <c r="C278" s="10">
+        <v>0</v>
+      </c>
+      <c r="E278" s="12">
+        <f t="shared" si="22"/>
+        <v>20075</v>
+      </c>
+      <c r="F278" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A279" s="5">
+        <f t="shared" si="21"/>
+        <v>278</v>
+      </c>
+      <c r="B279" s="10">
+        <v>100</v>
+      </c>
+      <c r="C279" s="10">
+        <v>0</v>
+      </c>
+      <c r="E279" s="12">
+        <f t="shared" si="22"/>
+        <v>20175</v>
+      </c>
+      <c r="F279" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A280" s="5">
+        <f t="shared" si="21"/>
+        <v>279</v>
+      </c>
+      <c r="B280" s="10">
+        <v>100</v>
+      </c>
+      <c r="C280" s="10">
+        <v>0</v>
+      </c>
+      <c r="E280" s="12">
+        <f t="shared" si="22"/>
+        <v>20275</v>
+      </c>
+      <c r="F280" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281" s="5">
+        <f t="shared" si="21"/>
+        <v>280</v>
+      </c>
+      <c r="B281" s="10">
+        <v>100</v>
+      </c>
+      <c r="C281" s="10">
+        <v>0</v>
+      </c>
+      <c r="E281" s="12">
+        <f t="shared" si="22"/>
+        <v>20375</v>
+      </c>
+      <c r="F281" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A282" s="5">
+        <f t="shared" si="21"/>
+        <v>281</v>
+      </c>
+      <c r="B282" s="10">
+        <v>100</v>
+      </c>
+      <c r="C282" s="10">
+        <v>0</v>
+      </c>
+      <c r="E282" s="12">
+        <f t="shared" si="22"/>
+        <v>20475</v>
+      </c>
+      <c r="F282" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A283" s="5">
+        <f t="shared" si="21"/>
+        <v>282</v>
+      </c>
+      <c r="B283" s="10">
+        <v>100</v>
+      </c>
+      <c r="C283" s="10">
+        <v>0</v>
+      </c>
+      <c r="E283" s="12">
+        <f t="shared" si="22"/>
+        <v>20575</v>
+      </c>
+      <c r="F283" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A284" s="5">
+        <f t="shared" si="21"/>
+        <v>283</v>
+      </c>
+      <c r="B284" s="10">
+        <v>100</v>
+      </c>
+      <c r="C284" s="10">
+        <v>0</v>
+      </c>
+      <c r="E284" s="12">
+        <f t="shared" si="22"/>
+        <v>20675</v>
+      </c>
+      <c r="F284" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285" s="5">
+        <f t="shared" si="21"/>
+        <v>284</v>
+      </c>
+      <c r="B285" s="10">
+        <v>100</v>
+      </c>
+      <c r="C285" s="10">
+        <v>0</v>
+      </c>
+      <c r="E285" s="12">
+        <f t="shared" si="22"/>
+        <v>20775</v>
+      </c>
+      <c r="F285" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A286" s="5">
+        <f t="shared" ref="A286:A305" si="24">A285+1</f>
+        <v>285</v>
+      </c>
+      <c r="B286" s="10">
+        <v>100</v>
+      </c>
+      <c r="C286" s="10">
+        <v>0</v>
+      </c>
+      <c r="E286" s="12">
+        <f t="shared" si="22"/>
+        <v>20875</v>
+      </c>
+      <c r="F286" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A287" s="5">
+        <f t="shared" si="24"/>
+        <v>286</v>
+      </c>
+      <c r="B287" s="10">
+        <v>100</v>
+      </c>
+      <c r="C287" s="10">
+        <v>0</v>
+      </c>
+      <c r="E287" s="12">
+        <f t="shared" si="22"/>
+        <v>20975</v>
+      </c>
+      <c r="F287" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A288" s="5">
+        <f t="shared" si="24"/>
+        <v>287</v>
+      </c>
+      <c r="B288" s="10">
+        <v>100</v>
+      </c>
+      <c r="C288" s="10">
+        <v>0</v>
+      </c>
+      <c r="E288" s="12">
+        <f t="shared" si="22"/>
+        <v>21075</v>
+      </c>
+      <c r="F288" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A289" s="5">
+        <f t="shared" si="24"/>
+        <v>288</v>
+      </c>
+      <c r="B289" s="10">
+        <v>100</v>
+      </c>
+      <c r="C289" s="10">
+        <v>0</v>
+      </c>
+      <c r="E289" s="12">
+        <f t="shared" si="22"/>
+        <v>21175</v>
+      </c>
+      <c r="F289" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A290" s="5">
+        <f t="shared" si="24"/>
+        <v>289</v>
+      </c>
+      <c r="B290" s="10">
+        <v>100</v>
+      </c>
+      <c r="C290" s="10">
+        <v>0</v>
+      </c>
+      <c r="E290" s="12">
+        <f t="shared" si="22"/>
+        <v>21275</v>
+      </c>
+      <c r="F290" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A291" s="5">
+        <f t="shared" si="24"/>
+        <v>290</v>
+      </c>
+      <c r="B291" s="10">
+        <v>100</v>
+      </c>
+      <c r="C291" s="10">
+        <v>0</v>
+      </c>
+      <c r="E291" s="12">
+        <f t="shared" si="22"/>
+        <v>21375</v>
+      </c>
+      <c r="F291" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292" s="5">
+        <f t="shared" si="24"/>
+        <v>291</v>
+      </c>
+      <c r="B292" s="10">
+        <v>100</v>
+      </c>
+      <c r="C292" s="10">
+        <v>0</v>
+      </c>
+      <c r="E292" s="12">
+        <f t="shared" si="22"/>
+        <v>21475</v>
+      </c>
+      <c r="F292" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293" s="5">
+        <f t="shared" si="24"/>
+        <v>292</v>
+      </c>
+      <c r="B293" s="10">
+        <v>100</v>
+      </c>
+      <c r="C293" s="10">
+        <v>0</v>
+      </c>
+      <c r="E293" s="12">
+        <f t="shared" ref="E293:E305" si="25">E292+B293</f>
+        <v>21575</v>
+      </c>
+      <c r="F293" s="13">
+        <f t="shared" ref="F293:F305" si="26">B293-B292</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294" s="5">
+        <f t="shared" si="24"/>
+        <v>293</v>
+      </c>
+      <c r="B294" s="10">
+        <v>100</v>
+      </c>
+      <c r="C294" s="10">
+        <v>0</v>
+      </c>
+      <c r="E294" s="12">
+        <f t="shared" si="25"/>
+        <v>21675</v>
+      </c>
+      <c r="F294" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A295" s="5">
+        <f t="shared" si="24"/>
+        <v>294</v>
+      </c>
+      <c r="B295" s="10">
+        <v>100</v>
+      </c>
+      <c r="C295" s="10">
+        <v>0</v>
+      </c>
+      <c r="E295" s="12">
+        <f t="shared" si="25"/>
+        <v>21775</v>
+      </c>
+      <c r="F295" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A296" s="5">
+        <f t="shared" si="24"/>
+        <v>295</v>
+      </c>
+      <c r="B296" s="10">
+        <v>100</v>
+      </c>
+      <c r="C296" s="10">
+        <v>0</v>
+      </c>
+      <c r="E296" s="12">
+        <f t="shared" si="25"/>
+        <v>21875</v>
+      </c>
+      <c r="F296" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A297" s="5">
+        <f t="shared" si="24"/>
+        <v>296</v>
+      </c>
+      <c r="B297" s="10">
+        <v>100</v>
+      </c>
+      <c r="C297" s="10">
+        <v>0</v>
+      </c>
+      <c r="E297" s="12">
+        <f t="shared" si="25"/>
+        <v>21975</v>
+      </c>
+      <c r="F297" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A298" s="5">
+        <f t="shared" si="24"/>
+        <v>297</v>
+      </c>
+      <c r="B298" s="10">
+        <v>100</v>
+      </c>
+      <c r="C298" s="10">
+        <v>0</v>
+      </c>
+      <c r="E298" s="12">
+        <f t="shared" si="25"/>
+        <v>22075</v>
+      </c>
+      <c r="F298" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A299" s="5">
+        <f t="shared" si="24"/>
+        <v>298</v>
+      </c>
+      <c r="B299" s="10">
+        <v>100</v>
+      </c>
+      <c r="C299" s="10">
+        <v>0</v>
+      </c>
+      <c r="E299" s="12">
+        <f t="shared" si="25"/>
+        <v>22175</v>
+      </c>
+      <c r="F299" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A300" s="5">
+        <f t="shared" si="24"/>
+        <v>299</v>
+      </c>
+      <c r="B300" s="10">
+        <v>100</v>
+      </c>
+      <c r="C300" s="10">
+        <v>0</v>
+      </c>
+      <c r="E300" s="12">
+        <f t="shared" si="25"/>
+        <v>22275</v>
+      </c>
+      <c r="F300" s="13">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A301" s="5">
+        <f t="shared" si="24"/>
+        <v>300</v>
+      </c>
+      <c r="B301" s="15">
         <v>-1</v>
       </c>
-      <c r="C101" s="11">
-        <v>0</v>
-      </c>
-      <c r="D101" s="11"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="5"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
+      <c r="C301" s="10">
+        <v>0</v>
+      </c>
+      <c r="E301" s="12">
+        <f t="shared" si="25"/>
+        <v>22274</v>
+      </c>
+      <c r="F301" s="16">
+        <f t="shared" si="26"/>
+        <v>-101</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A302" s="5"/>
+      <c r="E302" s="12"/>
+      <c r="F302" s="13"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A303" s="5"/>
+      <c r="E303" s="12"/>
+      <c r="F303" s="13"/>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A304" s="5"/>
+      <c r="E304" s="12"/>
+      <c r="F304" s="13"/>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A305" s="5"/>
+      <c r="E305" s="12"/>
+      <c r="F305" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/AddressableResource/Data/Excels/LevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/LevelData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C676FA-075F-4D77-88D9-13649AA31363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF238E6-922D-4C43-90FE-F9648A52A5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -222,12 +222,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,7 +604,7 @@
     </row>
     <row r="4" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <f t="shared" ref="A4:B67" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="10">
@@ -1476,7 +1470,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="10">
-        <f t="shared" ref="B44:B59" si="6">B41+1</f>
+        <f t="shared" ref="B44:B107" si="6">B41+1</f>
         <v>11</v>
       </c>
       <c r="C44" s="10">
@@ -1833,7 +1827,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="10">
-        <f t="shared" ref="B61:B66" si="7">B59+1</f>
+        <f t="shared" ref="B61:B124" si="7">B59+1</f>
         <v>17</v>
       </c>
       <c r="C61" s="10">
@@ -1959,19 +1953,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="10">
-        <f>B66+1</f>
-        <v>21</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="C67" s="10">
         <v>0</v>
       </c>
       <c r="E67" s="12">
         <f t="shared" si="1"/>
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F67" s="13">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -1980,15 +1974,15 @@
         <v>67</v>
       </c>
       <c r="B68" s="10">
-        <f t="shared" si="8"/>
-        <v>22</v>
+        <f t="shared" si="7"/>
+        <v>21</v>
       </c>
       <c r="C68" s="10">
         <v>0</v>
       </c>
       <c r="E68" s="12">
         <f t="shared" ref="E68:E100" si="9">E67+B68</f>
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F68" s="13">
         <f t="shared" ref="F68:F100" si="10">B68-B67</f>
@@ -2001,19 +1995,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="10">
-        <f t="shared" si="8"/>
-        <v>23</v>
+        <f t="shared" si="7"/>
+        <v>21</v>
       </c>
       <c r="C69" s="10">
         <v>0</v>
       </c>
       <c r="E69" s="12">
         <f t="shared" si="9"/>
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F69" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2022,15 +2016,15 @@
         <v>69</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" si="8"/>
-        <v>24</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
       </c>
       <c r="E70" s="12">
         <f t="shared" si="9"/>
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F70" s="13">
         <f t="shared" si="10"/>
@@ -2043,19 +2037,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="10">
-        <f t="shared" si="8"/>
-        <v>25</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="C71" s="10">
         <v>0</v>
       </c>
       <c r="E71" s="12">
         <f t="shared" si="9"/>
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="F71" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2064,15 +2058,15 @@
         <v>71</v>
       </c>
       <c r="B72" s="10">
-        <f t="shared" si="8"/>
-        <v>26</v>
+        <f t="shared" si="7"/>
+        <v>23</v>
       </c>
       <c r="C72" s="10">
         <v>0</v>
       </c>
       <c r="E72" s="12">
         <f t="shared" si="9"/>
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="F72" s="13">
         <f t="shared" si="10"/>
@@ -2085,19 +2079,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="10">
-        <f t="shared" si="8"/>
-        <v>27</v>
+        <f t="shared" si="7"/>
+        <v>23</v>
       </c>
       <c r="C73" s="10">
         <v>0</v>
       </c>
       <c r="E73" s="12">
         <f t="shared" si="9"/>
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="F73" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2106,15 +2100,15 @@
         <v>73</v>
       </c>
       <c r="B74" s="10">
-        <f t="shared" si="11"/>
-        <v>28</v>
+        <f t="shared" si="7"/>
+        <v>24</v>
       </c>
       <c r="C74" s="10">
         <v>0</v>
       </c>
       <c r="E74" s="12">
         <f t="shared" si="9"/>
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="F74" s="13">
         <f t="shared" si="10"/>
@@ -2127,19 +2121,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="10">
-        <f t="shared" si="11"/>
-        <v>29</v>
+        <f t="shared" si="7"/>
+        <v>24</v>
       </c>
       <c r="C75" s="10">
         <v>0</v>
       </c>
       <c r="E75" s="12">
         <f t="shared" si="9"/>
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="F75" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2148,15 +2142,15 @@
         <v>75</v>
       </c>
       <c r="B76" s="10">
-        <f t="shared" si="11"/>
-        <v>30</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="C76" s="10">
         <v>0</v>
       </c>
       <c r="E76" s="12">
         <f t="shared" si="9"/>
-        <v>840</v>
+        <v>810</v>
       </c>
       <c r="F76" s="13">
         <f t="shared" si="10"/>
@@ -2169,19 +2163,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="10">
-        <f>B76+2</f>
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="C77" s="10">
         <v>0</v>
       </c>
       <c r="E77" s="12">
         <f t="shared" si="9"/>
-        <v>872</v>
+        <v>835</v>
       </c>
       <c r="F77" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2190,19 +2184,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="10">
-        <f t="shared" ref="B78:B86" si="12">B77+2</f>
-        <v>34</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
       </c>
       <c r="E78" s="12">
         <f t="shared" si="9"/>
-        <v>906</v>
+        <v>861</v>
       </c>
       <c r="F78" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2211,19 +2205,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="10">
-        <f t="shared" si="12"/>
-        <v>36</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="C79" s="10">
         <v>0</v>
       </c>
       <c r="E79" s="12">
         <f t="shared" si="9"/>
-        <v>942</v>
+        <v>887</v>
       </c>
       <c r="F79" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2232,19 +2226,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="10">
-        <f t="shared" si="12"/>
-        <v>38</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="C80" s="10">
         <v>0</v>
       </c>
       <c r="E80" s="12">
         <f t="shared" si="9"/>
-        <v>980</v>
+        <v>914</v>
       </c>
       <c r="F80" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2253,19 +2247,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="10">
-        <f t="shared" si="12"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="C81" s="10">
         <v>0</v>
       </c>
       <c r="E81" s="12">
         <f t="shared" si="9"/>
-        <v>1020</v>
+        <v>941</v>
       </c>
       <c r="F81" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2274,19 +2268,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="10">
-        <f t="shared" si="12"/>
-        <v>42</v>
+        <f t="shared" si="7"/>
+        <v>28</v>
       </c>
       <c r="C82" s="10">
         <v>0</v>
       </c>
       <c r="E82" s="12">
         <f t="shared" si="9"/>
-        <v>1062</v>
+        <v>969</v>
       </c>
       <c r="F82" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2295,19 +2289,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="10">
-        <f t="shared" si="12"/>
-        <v>44</v>
+        <f t="shared" si="7"/>
+        <v>28</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
       </c>
       <c r="E83" s="12">
         <f t="shared" si="9"/>
-        <v>1106</v>
+        <v>997</v>
       </c>
       <c r="F83" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2316,19 +2310,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="10">
-        <f t="shared" si="12"/>
-        <v>46</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="C84" s="10">
         <v>0</v>
       </c>
       <c r="E84" s="12">
         <f t="shared" si="9"/>
-        <v>1152</v>
+        <v>1026</v>
       </c>
       <c r="F84" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2337,19 +2331,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="10">
-        <f t="shared" si="12"/>
-        <v>48</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="C85" s="10">
         <v>0</v>
       </c>
       <c r="E85" s="12">
         <f t="shared" si="9"/>
-        <v>1200</v>
+        <v>1055</v>
       </c>
       <c r="F85" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2358,19 +2352,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="10">
-        <f t="shared" si="12"/>
-        <v>50</v>
+        <f t="shared" si="7"/>
+        <v>30</v>
       </c>
       <c r="C86" s="10">
         <v>0</v>
       </c>
       <c r="E86" s="12">
         <f t="shared" si="9"/>
-        <v>1250</v>
+        <v>1085</v>
       </c>
       <c r="F86" s="13">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2379,19 +2373,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="10">
-        <f>B86+3</f>
-        <v>53</v>
+        <f t="shared" si="7"/>
+        <v>30</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
       </c>
       <c r="E87" s="12">
         <f t="shared" si="9"/>
-        <v>1303</v>
+        <v>1115</v>
       </c>
       <c r="F87" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2400,19 +2394,19 @@
         <v>87</v>
       </c>
       <c r="B88" s="10">
-        <f t="shared" ref="B88:B96" si="13">B87+3</f>
-        <v>56</v>
+        <f t="shared" si="7"/>
+        <v>31</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
       </c>
       <c r="E88" s="12">
         <f t="shared" si="9"/>
-        <v>1359</v>
+        <v>1146</v>
       </c>
       <c r="F88" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2421,19 +2415,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="10">
-        <f t="shared" si="13"/>
-        <v>59</v>
+        <f t="shared" si="7"/>
+        <v>31</v>
       </c>
       <c r="C89" s="10">
         <v>0</v>
       </c>
       <c r="E89" s="12">
         <f t="shared" si="9"/>
-        <v>1418</v>
+        <v>1177</v>
       </c>
       <c r="F89" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2442,19 +2436,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="10">
-        <f t="shared" si="13"/>
-        <v>62</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="C90" s="10">
         <v>0</v>
       </c>
       <c r="E90" s="12">
         <f t="shared" si="9"/>
-        <v>1480</v>
+        <v>1209</v>
       </c>
       <c r="F90" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2463,19 +2457,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="10">
-        <f t="shared" si="13"/>
-        <v>65</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="C91" s="10">
         <v>0</v>
       </c>
       <c r="E91" s="12">
         <f t="shared" si="9"/>
-        <v>1545</v>
+        <v>1241</v>
       </c>
       <c r="F91" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2484,19 +2478,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="10">
-        <f t="shared" si="13"/>
-        <v>68</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="C92" s="10">
         <v>0</v>
       </c>
       <c r="E92" s="12">
         <f t="shared" si="9"/>
-        <v>1613</v>
+        <v>1274</v>
       </c>
       <c r="F92" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2505,2711 +2499,2838 @@
         <v>92</v>
       </c>
       <c r="B93" s="10">
-        <f t="shared" si="13"/>
-        <v>71</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="C93" s="10">
         <v>0</v>
       </c>
       <c r="E93" s="12">
         <f t="shared" si="9"/>
-        <v>1684</v>
+        <v>1307</v>
       </c>
       <c r="F93" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
-        <f t="shared" ref="A94:A157" si="14">A93+1</f>
+        <f t="shared" ref="A94:B157" si="12">A93+1</f>
         <v>93</v>
       </c>
       <c r="B94" s="10">
-        <f t="shared" si="13"/>
-        <v>74</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="C94" s="10">
         <v>0</v>
       </c>
       <c r="E94" s="12">
         <f t="shared" si="9"/>
-        <v>1758</v>
+        <v>1341</v>
       </c>
       <c r="F94" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>94</v>
       </c>
       <c r="B95" s="10">
-        <f t="shared" si="13"/>
-        <v>77</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="C95" s="10">
         <v>0</v>
       </c>
       <c r="E95" s="12">
         <f t="shared" si="9"/>
-        <v>1835</v>
+        <v>1375</v>
       </c>
       <c r="F95" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>95</v>
       </c>
       <c r="B96" s="10">
-        <f t="shared" si="13"/>
-        <v>80</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="C96" s="10">
         <v>0</v>
       </c>
       <c r="E96" s="12">
         <f t="shared" si="9"/>
-        <v>1915</v>
+        <v>1410</v>
       </c>
       <c r="F96" s="13">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>96</v>
       </c>
       <c r="B97" s="10">
-        <f>B96+4</f>
-        <v>84</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="C97" s="10">
         <v>0</v>
       </c>
       <c r="E97" s="12">
         <f t="shared" si="9"/>
-        <v>1999</v>
+        <v>1445</v>
       </c>
       <c r="F97" s="13">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>97</v>
       </c>
       <c r="B98" s="10">
-        <f t="shared" ref="B98:B161" si="15">B97+4</f>
-        <v>88</v>
+        <f t="shared" si="7"/>
+        <v>36</v>
       </c>
       <c r="C98" s="10">
         <v>0</v>
       </c>
       <c r="E98" s="12">
         <f t="shared" si="9"/>
-        <v>2087</v>
+        <v>1481</v>
       </c>
       <c r="F98" s="13">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
       <c r="B99" s="10">
-        <f t="shared" si="15"/>
-        <v>92</v>
+        <f t="shared" si="7"/>
+        <v>36</v>
       </c>
       <c r="C99" s="10">
         <v>0</v>
       </c>
       <c r="E99" s="12">
         <f t="shared" si="9"/>
-        <v>2179</v>
+        <v>1517</v>
       </c>
       <c r="F99" s="13">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>99</v>
       </c>
       <c r="B100" s="10">
-        <f t="shared" si="15"/>
-        <v>96</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="C100" s="10">
         <v>0</v>
       </c>
       <c r="E100" s="12">
         <f t="shared" si="9"/>
-        <v>2275</v>
+        <v>1554</v>
       </c>
       <c r="F100" s="13">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="B101" s="10">
-        <v>100</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="C101" s="10">
         <v>0</v>
       </c>
       <c r="E101" s="12">
-        <f t="shared" ref="E101:E164" si="16">E100+B101</f>
-        <v>2375</v>
+        <f t="shared" ref="E101:E164" si="13">E100+B101</f>
+        <v>1591</v>
       </c>
       <c r="F101" s="13">
-        <f t="shared" ref="F101:F164" si="17">B101-B100</f>
-        <v>4</v>
+        <f t="shared" ref="F101:F164" si="14">B101-B100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
+        <f t="shared" si="12"/>
+        <v>101</v>
+      </c>
+      <c r="B102" s="10">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="C102" s="10">
+        <v>0</v>
+      </c>
+      <c r="E102" s="12">
+        <f t="shared" si="13"/>
+        <v>1629</v>
+      </c>
+      <c r="F102" s="13">
         <f t="shared" si="14"/>
-        <v>101</v>
-      </c>
-      <c r="B102" s="10">
-        <v>100</v>
-      </c>
-      <c r="C102" s="10">
-        <v>0</v>
-      </c>
-      <c r="E102" s="12">
-        <f t="shared" si="16"/>
-        <v>2475</v>
-      </c>
-      <c r="F102" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
+        <f t="shared" si="12"/>
+        <v>102</v>
+      </c>
+      <c r="B103" s="10">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="C103" s="10">
+        <v>0</v>
+      </c>
+      <c r="E103" s="12">
+        <f t="shared" si="13"/>
+        <v>1667</v>
+      </c>
+      <c r="F103" s="13">
         <f t="shared" si="14"/>
-        <v>102</v>
-      </c>
-      <c r="B103" s="10">
-        <v>100</v>
-      </c>
-      <c r="C103" s="10">
-        <v>0</v>
-      </c>
-      <c r="E103" s="12">
-        <f t="shared" si="16"/>
-        <v>2575</v>
-      </c>
-      <c r="F103" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
+        <f t="shared" si="12"/>
+        <v>103</v>
+      </c>
+      <c r="B104" s="10">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="C104" s="10">
+        <v>0</v>
+      </c>
+      <c r="E104" s="12">
+        <f t="shared" si="13"/>
+        <v>1706</v>
+      </c>
+      <c r="F104" s="13">
         <f t="shared" si="14"/>
-        <v>103</v>
-      </c>
-      <c r="B104" s="10">
-        <v>100</v>
-      </c>
-      <c r="C104" s="10">
-        <v>0</v>
-      </c>
-      <c r="E104" s="12">
-        <f t="shared" si="16"/>
-        <v>2675</v>
-      </c>
-      <c r="F104" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
+        <f t="shared" si="12"/>
+        <v>104</v>
+      </c>
+      <c r="B105" s="10">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="C105" s="10">
+        <v>0</v>
+      </c>
+      <c r="E105" s="12">
+        <f t="shared" si="13"/>
+        <v>1745</v>
+      </c>
+      <c r="F105" s="13">
         <f t="shared" si="14"/>
-        <v>104</v>
-      </c>
-      <c r="B105" s="10">
-        <v>100</v>
-      </c>
-      <c r="C105" s="10">
-        <v>0</v>
-      </c>
-      <c r="E105" s="12">
-        <f t="shared" si="16"/>
-        <v>2775</v>
-      </c>
-      <c r="F105" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
+        <f t="shared" si="12"/>
+        <v>105</v>
+      </c>
+      <c r="B106" s="10">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="C106" s="10">
+        <v>0</v>
+      </c>
+      <c r="E106" s="12">
+        <f t="shared" si="13"/>
+        <v>1785</v>
+      </c>
+      <c r="F106" s="13">
         <f t="shared" si="14"/>
-        <v>105</v>
-      </c>
-      <c r="B106" s="10">
-        <v>100</v>
-      </c>
-      <c r="C106" s="10">
-        <v>0</v>
-      </c>
-      <c r="E106" s="12">
-        <f t="shared" si="16"/>
-        <v>2875</v>
-      </c>
-      <c r="F106" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
+        <f t="shared" si="12"/>
+        <v>106</v>
+      </c>
+      <c r="B107" s="10">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="C107" s="10">
+        <v>0</v>
+      </c>
+      <c r="E107" s="12">
+        <f t="shared" si="13"/>
+        <v>1825</v>
+      </c>
+      <c r="F107" s="13">
         <f t="shared" si="14"/>
-        <v>106</v>
-      </c>
-      <c r="B107" s="10">
-        <v>100</v>
-      </c>
-      <c r="C107" s="10">
-        <v>0</v>
-      </c>
-      <c r="E107" s="12">
-        <f t="shared" si="16"/>
-        <v>2975</v>
-      </c>
-      <c r="F107" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
+        <f t="shared" si="12"/>
+        <v>107</v>
+      </c>
+      <c r="B108" s="10">
+        <f t="shared" si="7"/>
+        <v>41</v>
+      </c>
+      <c r="C108" s="10">
+        <v>0</v>
+      </c>
+      <c r="E108" s="12">
+        <f t="shared" si="13"/>
+        <v>1866</v>
+      </c>
+      <c r="F108" s="13">
         <f t="shared" si="14"/>
-        <v>107</v>
-      </c>
-      <c r="B108" s="10">
-        <v>100</v>
-      </c>
-      <c r="C108" s="10">
-        <v>0</v>
-      </c>
-      <c r="E108" s="12">
-        <f t="shared" si="16"/>
-        <v>3075</v>
-      </c>
-      <c r="F108" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
+        <f t="shared" si="12"/>
+        <v>108</v>
+      </c>
+      <c r="B109" s="10">
+        <f t="shared" si="7"/>
+        <v>41</v>
+      </c>
+      <c r="C109" s="10">
+        <v>0</v>
+      </c>
+      <c r="E109" s="12">
+        <f t="shared" si="13"/>
+        <v>1907</v>
+      </c>
+      <c r="F109" s="13">
         <f t="shared" si="14"/>
-        <v>108</v>
-      </c>
-      <c r="B109" s="10">
-        <v>100</v>
-      </c>
-      <c r="C109" s="10">
-        <v>0</v>
-      </c>
-      <c r="E109" s="12">
-        <f t="shared" si="16"/>
-        <v>3175</v>
-      </c>
-      <c r="F109" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
+        <f t="shared" si="12"/>
+        <v>109</v>
+      </c>
+      <c r="B110" s="10">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="C110" s="10">
+        <v>0</v>
+      </c>
+      <c r="E110" s="12">
+        <f t="shared" si="13"/>
+        <v>1949</v>
+      </c>
+      <c r="F110" s="13">
         <f t="shared" si="14"/>
-        <v>109</v>
-      </c>
-      <c r="B110" s="10">
-        <v>100</v>
-      </c>
-      <c r="C110" s="10">
-        <v>0</v>
-      </c>
-      <c r="E110" s="12">
-        <f t="shared" si="16"/>
-        <v>3275</v>
-      </c>
-      <c r="F110" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
+        <f t="shared" si="12"/>
+        <v>110</v>
+      </c>
+      <c r="B111" s="10">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="C111" s="10">
+        <v>0</v>
+      </c>
+      <c r="E111" s="12">
+        <f t="shared" si="13"/>
+        <v>1991</v>
+      </c>
+      <c r="F111" s="13">
         <f t="shared" si="14"/>
-        <v>110</v>
-      </c>
-      <c r="B111" s="10">
-        <v>100</v>
-      </c>
-      <c r="C111" s="10">
-        <v>0</v>
-      </c>
-      <c r="E111" s="12">
-        <f t="shared" si="16"/>
-        <v>3375</v>
-      </c>
-      <c r="F111" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
+        <f t="shared" si="12"/>
+        <v>111</v>
+      </c>
+      <c r="B112" s="10">
+        <f t="shared" si="7"/>
+        <v>43</v>
+      </c>
+      <c r="C112" s="10">
+        <v>0</v>
+      </c>
+      <c r="E112" s="12">
+        <f t="shared" si="13"/>
+        <v>2034</v>
+      </c>
+      <c r="F112" s="13">
         <f t="shared" si="14"/>
-        <v>111</v>
-      </c>
-      <c r="B112" s="10">
-        <v>100</v>
-      </c>
-      <c r="C112" s="10">
-        <v>0</v>
-      </c>
-      <c r="E112" s="12">
-        <f t="shared" si="16"/>
-        <v>3475</v>
-      </c>
-      <c r="F112" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
+        <f t="shared" si="12"/>
+        <v>112</v>
+      </c>
+      <c r="B113" s="10">
+        <f t="shared" si="7"/>
+        <v>43</v>
+      </c>
+      <c r="C113" s="10">
+        <v>0</v>
+      </c>
+      <c r="E113" s="12">
+        <f t="shared" si="13"/>
+        <v>2077</v>
+      </c>
+      <c r="F113" s="13">
         <f t="shared" si="14"/>
-        <v>112</v>
-      </c>
-      <c r="B113" s="10">
-        <v>100</v>
-      </c>
-      <c r="C113" s="10">
-        <v>0</v>
-      </c>
-      <c r="E113" s="12">
-        <f t="shared" si="16"/>
-        <v>3575</v>
-      </c>
-      <c r="F113" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
+        <f t="shared" si="12"/>
+        <v>113</v>
+      </c>
+      <c r="B114" s="10">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="C114" s="10">
+        <v>0</v>
+      </c>
+      <c r="E114" s="12">
+        <f t="shared" si="13"/>
+        <v>2121</v>
+      </c>
+      <c r="F114" s="13">
         <f t="shared" si="14"/>
-        <v>113</v>
-      </c>
-      <c r="B114" s="10">
-        <v>100</v>
-      </c>
-      <c r="C114" s="10">
-        <v>0</v>
-      </c>
-      <c r="E114" s="12">
-        <f t="shared" si="16"/>
-        <v>3675</v>
-      </c>
-      <c r="F114" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
+        <f t="shared" si="12"/>
+        <v>114</v>
+      </c>
+      <c r="B115" s="10">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="C115" s="10">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12">
+        <f t="shared" si="13"/>
+        <v>2165</v>
+      </c>
+      <c r="F115" s="13">
         <f t="shared" si="14"/>
-        <v>114</v>
-      </c>
-      <c r="B115" s="10">
-        <v>100</v>
-      </c>
-      <c r="C115" s="10">
-        <v>0</v>
-      </c>
-      <c r="E115" s="12">
-        <f t="shared" si="16"/>
-        <v>3775</v>
-      </c>
-      <c r="F115" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
+        <f t="shared" si="12"/>
+        <v>115</v>
+      </c>
+      <c r="B116" s="10">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="C116" s="10">
+        <v>0</v>
+      </c>
+      <c r="E116" s="12">
+        <f t="shared" si="13"/>
+        <v>2210</v>
+      </c>
+      <c r="F116" s="13">
         <f t="shared" si="14"/>
-        <v>115</v>
-      </c>
-      <c r="B116" s="10">
-        <v>100</v>
-      </c>
-      <c r="C116" s="10">
-        <v>0</v>
-      </c>
-      <c r="E116" s="12">
-        <f t="shared" si="16"/>
-        <v>3875</v>
-      </c>
-      <c r="F116" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
+        <f t="shared" si="12"/>
+        <v>116</v>
+      </c>
+      <c r="B117" s="10">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="C117" s="10">
+        <v>0</v>
+      </c>
+      <c r="E117" s="12">
+        <f t="shared" si="13"/>
+        <v>2255</v>
+      </c>
+      <c r="F117" s="13">
         <f t="shared" si="14"/>
-        <v>116</v>
-      </c>
-      <c r="B117" s="10">
-        <v>100</v>
-      </c>
-      <c r="C117" s="10">
-        <v>0</v>
-      </c>
-      <c r="E117" s="12">
-        <f t="shared" si="16"/>
-        <v>3975</v>
-      </c>
-      <c r="F117" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
+        <f t="shared" si="12"/>
+        <v>117</v>
+      </c>
+      <c r="B118" s="10">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="C118" s="10">
+        <v>0</v>
+      </c>
+      <c r="E118" s="12">
+        <f t="shared" si="13"/>
+        <v>2301</v>
+      </c>
+      <c r="F118" s="13">
         <f t="shared" si="14"/>
-        <v>117</v>
-      </c>
-      <c r="B118" s="10">
-        <v>100</v>
-      </c>
-      <c r="C118" s="10">
-        <v>0</v>
-      </c>
-      <c r="E118" s="12">
-        <f t="shared" si="16"/>
-        <v>4075</v>
-      </c>
-      <c r="F118" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
+        <f t="shared" si="12"/>
+        <v>118</v>
+      </c>
+      <c r="B119" s="10">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="C119" s="10">
+        <v>0</v>
+      </c>
+      <c r="E119" s="12">
+        <f t="shared" si="13"/>
+        <v>2347</v>
+      </c>
+      <c r="F119" s="13">
         <f t="shared" si="14"/>
-        <v>118</v>
-      </c>
-      <c r="B119" s="10">
-        <v>100</v>
-      </c>
-      <c r="C119" s="10">
-        <v>0</v>
-      </c>
-      <c r="E119" s="12">
-        <f t="shared" si="16"/>
-        <v>4175</v>
-      </c>
-      <c r="F119" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
+        <f t="shared" si="12"/>
+        <v>119</v>
+      </c>
+      <c r="B120" s="10">
+        <f t="shared" si="7"/>
+        <v>47</v>
+      </c>
+      <c r="C120" s="10">
+        <v>0</v>
+      </c>
+      <c r="E120" s="12">
+        <f t="shared" si="13"/>
+        <v>2394</v>
+      </c>
+      <c r="F120" s="13">
         <f t="shared" si="14"/>
-        <v>119</v>
-      </c>
-      <c r="B120" s="10">
-        <v>100</v>
-      </c>
-      <c r="C120" s="10">
-        <v>0</v>
-      </c>
-      <c r="E120" s="12">
-        <f t="shared" si="16"/>
-        <v>4275</v>
-      </c>
-      <c r="F120" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
+        <f t="shared" si="12"/>
+        <v>120</v>
+      </c>
+      <c r="B121" s="10">
+        <f t="shared" si="7"/>
+        <v>47</v>
+      </c>
+      <c r="C121" s="10">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12">
+        <f t="shared" si="13"/>
+        <v>2441</v>
+      </c>
+      <c r="F121" s="13">
         <f t="shared" si="14"/>
-        <v>120</v>
-      </c>
-      <c r="B121" s="10">
-        <v>100</v>
-      </c>
-      <c r="C121" s="10">
-        <v>0</v>
-      </c>
-      <c r="E121" s="12">
-        <f t="shared" si="16"/>
-        <v>4375</v>
-      </c>
-      <c r="F121" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
+        <f t="shared" si="12"/>
+        <v>121</v>
+      </c>
+      <c r="B122" s="10">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="C122" s="10">
+        <v>0</v>
+      </c>
+      <c r="E122" s="12">
+        <f t="shared" si="13"/>
+        <v>2489</v>
+      </c>
+      <c r="F122" s="13">
         <f t="shared" si="14"/>
-        <v>121</v>
-      </c>
-      <c r="B122" s="10">
-        <v>100</v>
-      </c>
-      <c r="C122" s="10">
-        <v>0</v>
-      </c>
-      <c r="E122" s="12">
-        <f t="shared" si="16"/>
-        <v>4475</v>
-      </c>
-      <c r="F122" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
+        <f t="shared" si="12"/>
+        <v>122</v>
+      </c>
+      <c r="B123" s="10">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="C123" s="10">
+        <v>0</v>
+      </c>
+      <c r="E123" s="12">
+        <f t="shared" si="13"/>
+        <v>2537</v>
+      </c>
+      <c r="F123" s="13">
         <f t="shared" si="14"/>
-        <v>122</v>
-      </c>
-      <c r="B123" s="10">
-        <v>100</v>
-      </c>
-      <c r="C123" s="10">
-        <v>0</v>
-      </c>
-      <c r="E123" s="12">
-        <f t="shared" si="16"/>
-        <v>4575</v>
-      </c>
-      <c r="F123" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
+        <f t="shared" si="12"/>
+        <v>123</v>
+      </c>
+      <c r="B124" s="10">
+        <f t="shared" si="7"/>
+        <v>49</v>
+      </c>
+      <c r="C124" s="10">
+        <v>0</v>
+      </c>
+      <c r="E124" s="12">
+        <f t="shared" si="13"/>
+        <v>2586</v>
+      </c>
+      <c r="F124" s="13">
         <f t="shared" si="14"/>
-        <v>123</v>
-      </c>
-      <c r="B124" s="10">
-        <v>100</v>
-      </c>
-      <c r="C124" s="10">
-        <v>0</v>
-      </c>
-      <c r="E124" s="12">
-        <f t="shared" si="16"/>
-        <v>4675</v>
-      </c>
-      <c r="F124" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
+        <f t="shared" si="12"/>
+        <v>124</v>
+      </c>
+      <c r="B125" s="10">
+        <f t="shared" ref="B125:B188" si="15">B123+1</f>
+        <v>49</v>
+      </c>
+      <c r="C125" s="10">
+        <v>0</v>
+      </c>
+      <c r="E125" s="12">
+        <f t="shared" si="13"/>
+        <v>2635</v>
+      </c>
+      <c r="F125" s="13">
         <f t="shared" si="14"/>
-        <v>124</v>
-      </c>
-      <c r="B125" s="10">
-        <v>100</v>
-      </c>
-      <c r="C125" s="10">
-        <v>0</v>
-      </c>
-      <c r="E125" s="12">
-        <f t="shared" si="16"/>
-        <v>4775</v>
-      </c>
-      <c r="F125" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
+        <f t="shared" si="12"/>
+        <v>125</v>
+      </c>
+      <c r="B126" s="10">
+        <f t="shared" si="15"/>
+        <v>50</v>
+      </c>
+      <c r="C126" s="10">
+        <v>0</v>
+      </c>
+      <c r="E126" s="12">
+        <f t="shared" si="13"/>
+        <v>2685</v>
+      </c>
+      <c r="F126" s="13">
         <f t="shared" si="14"/>
-        <v>125</v>
-      </c>
-      <c r="B126" s="10">
-        <v>100</v>
-      </c>
-      <c r="C126" s="10">
-        <v>0</v>
-      </c>
-      <c r="E126" s="12">
-        <f t="shared" si="16"/>
-        <v>4875</v>
-      </c>
-      <c r="F126" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
+        <f t="shared" si="12"/>
+        <v>126</v>
+      </c>
+      <c r="B127" s="10">
+        <f t="shared" si="15"/>
+        <v>50</v>
+      </c>
+      <c r="C127" s="10">
+        <v>0</v>
+      </c>
+      <c r="E127" s="12">
+        <f t="shared" si="13"/>
+        <v>2735</v>
+      </c>
+      <c r="F127" s="13">
         <f t="shared" si="14"/>
-        <v>126</v>
-      </c>
-      <c r="B127" s="10">
-        <v>100</v>
-      </c>
-      <c r="C127" s="10">
-        <v>0</v>
-      </c>
-      <c r="E127" s="12">
-        <f t="shared" si="16"/>
-        <v>4975</v>
-      </c>
-      <c r="F127" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
+        <f t="shared" si="12"/>
+        <v>127</v>
+      </c>
+      <c r="B128" s="10">
+        <f t="shared" si="15"/>
+        <v>51</v>
+      </c>
+      <c r="C128" s="10">
+        <v>0</v>
+      </c>
+      <c r="E128" s="12">
+        <f t="shared" si="13"/>
+        <v>2786</v>
+      </c>
+      <c r="F128" s="13">
         <f t="shared" si="14"/>
-        <v>127</v>
-      </c>
-      <c r="B128" s="10">
-        <v>100</v>
-      </c>
-      <c r="C128" s="10">
-        <v>0</v>
-      </c>
-      <c r="E128" s="12">
-        <f t="shared" si="16"/>
-        <v>5075</v>
-      </c>
-      <c r="F128" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
+        <f t="shared" si="12"/>
+        <v>128</v>
+      </c>
+      <c r="B129" s="10">
+        <f t="shared" si="15"/>
+        <v>51</v>
+      </c>
+      <c r="C129" s="10">
+        <v>0</v>
+      </c>
+      <c r="E129" s="12">
+        <f t="shared" si="13"/>
+        <v>2837</v>
+      </c>
+      <c r="F129" s="13">
         <f t="shared" si="14"/>
-        <v>128</v>
-      </c>
-      <c r="B129" s="10">
-        <v>100</v>
-      </c>
-      <c r="C129" s="10">
-        <v>0</v>
-      </c>
-      <c r="E129" s="12">
-        <f t="shared" si="16"/>
-        <v>5175</v>
-      </c>
-      <c r="F129" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
+        <f t="shared" si="12"/>
+        <v>129</v>
+      </c>
+      <c r="B130" s="10">
+        <f t="shared" si="15"/>
+        <v>52</v>
+      </c>
+      <c r="C130" s="10">
+        <v>0</v>
+      </c>
+      <c r="E130" s="12">
+        <f t="shared" si="13"/>
+        <v>2889</v>
+      </c>
+      <c r="F130" s="13">
         <f t="shared" si="14"/>
-        <v>129</v>
-      </c>
-      <c r="B130" s="10">
-        <v>100</v>
-      </c>
-      <c r="C130" s="10">
-        <v>0</v>
-      </c>
-      <c r="E130" s="12">
-        <f t="shared" si="16"/>
-        <v>5275</v>
-      </c>
-      <c r="F130" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
+        <f t="shared" si="12"/>
+        <v>130</v>
+      </c>
+      <c r="B131" s="10">
+        <f t="shared" si="15"/>
+        <v>52</v>
+      </c>
+      <c r="C131" s="10">
+        <v>0</v>
+      </c>
+      <c r="E131" s="12">
+        <f t="shared" si="13"/>
+        <v>2941</v>
+      </c>
+      <c r="F131" s="13">
         <f t="shared" si="14"/>
-        <v>130</v>
-      </c>
-      <c r="B131" s="10">
-        <v>100</v>
-      </c>
-      <c r="C131" s="10">
-        <v>0</v>
-      </c>
-      <c r="E131" s="12">
-        <f t="shared" si="16"/>
-        <v>5375</v>
-      </c>
-      <c r="F131" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
+        <f t="shared" si="12"/>
+        <v>131</v>
+      </c>
+      <c r="B132" s="10">
+        <f t="shared" si="15"/>
+        <v>53</v>
+      </c>
+      <c r="C132" s="10">
+        <v>0</v>
+      </c>
+      <c r="E132" s="12">
+        <f t="shared" si="13"/>
+        <v>2994</v>
+      </c>
+      <c r="F132" s="13">
         <f t="shared" si="14"/>
-        <v>131</v>
-      </c>
-      <c r="B132" s="10">
-        <v>100</v>
-      </c>
-      <c r="C132" s="10">
-        <v>0</v>
-      </c>
-      <c r="E132" s="12">
-        <f t="shared" si="16"/>
-        <v>5475</v>
-      </c>
-      <c r="F132" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
+        <f t="shared" si="12"/>
+        <v>132</v>
+      </c>
+      <c r="B133" s="10">
+        <f t="shared" si="15"/>
+        <v>53</v>
+      </c>
+      <c r="C133" s="10">
+        <v>0</v>
+      </c>
+      <c r="E133" s="12">
+        <f t="shared" si="13"/>
+        <v>3047</v>
+      </c>
+      <c r="F133" s="13">
         <f t="shared" si="14"/>
-        <v>132</v>
-      </c>
-      <c r="B133" s="10">
-        <v>100</v>
-      </c>
-      <c r="C133" s="10">
-        <v>0</v>
-      </c>
-      <c r="E133" s="12">
-        <f t="shared" si="16"/>
-        <v>5575</v>
-      </c>
-      <c r="F133" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
+        <f t="shared" si="12"/>
+        <v>133</v>
+      </c>
+      <c r="B134" s="10">
+        <f t="shared" si="15"/>
+        <v>54</v>
+      </c>
+      <c r="C134" s="10">
+        <v>0</v>
+      </c>
+      <c r="E134" s="12">
+        <f t="shared" si="13"/>
+        <v>3101</v>
+      </c>
+      <c r="F134" s="13">
         <f t="shared" si="14"/>
-        <v>133</v>
-      </c>
-      <c r="B134" s="10">
-        <v>100</v>
-      </c>
-      <c r="C134" s="10">
-        <v>0</v>
-      </c>
-      <c r="E134" s="12">
-        <f t="shared" si="16"/>
-        <v>5675</v>
-      </c>
-      <c r="F134" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
+        <f t="shared" si="12"/>
+        <v>134</v>
+      </c>
+      <c r="B135" s="10">
+        <f t="shared" si="15"/>
+        <v>54</v>
+      </c>
+      <c r="C135" s="10">
+        <v>0</v>
+      </c>
+      <c r="E135" s="12">
+        <f t="shared" si="13"/>
+        <v>3155</v>
+      </c>
+      <c r="F135" s="13">
         <f t="shared" si="14"/>
-        <v>134</v>
-      </c>
-      <c r="B135" s="10">
-        <v>100</v>
-      </c>
-      <c r="C135" s="10">
-        <v>0</v>
-      </c>
-      <c r="E135" s="12">
-        <f t="shared" si="16"/>
-        <v>5775</v>
-      </c>
-      <c r="F135" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
+        <f t="shared" si="12"/>
+        <v>135</v>
+      </c>
+      <c r="B136" s="10">
+        <f t="shared" si="15"/>
+        <v>55</v>
+      </c>
+      <c r="C136" s="10">
+        <v>0</v>
+      </c>
+      <c r="E136" s="12">
+        <f t="shared" si="13"/>
+        <v>3210</v>
+      </c>
+      <c r="F136" s="13">
         <f t="shared" si="14"/>
-        <v>135</v>
-      </c>
-      <c r="B136" s="10">
-        <v>100</v>
-      </c>
-      <c r="C136" s="10">
-        <v>0</v>
-      </c>
-      <c r="E136" s="12">
-        <f t="shared" si="16"/>
-        <v>5875</v>
-      </c>
-      <c r="F136" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
+        <f t="shared" si="12"/>
+        <v>136</v>
+      </c>
+      <c r="B137" s="10">
+        <f t="shared" si="15"/>
+        <v>55</v>
+      </c>
+      <c r="C137" s="10">
+        <v>0</v>
+      </c>
+      <c r="E137" s="12">
+        <f t="shared" si="13"/>
+        <v>3265</v>
+      </c>
+      <c r="F137" s="13">
         <f t="shared" si="14"/>
-        <v>136</v>
-      </c>
-      <c r="B137" s="10">
-        <v>100</v>
-      </c>
-      <c r="C137" s="10">
-        <v>0</v>
-      </c>
-      <c r="E137" s="12">
-        <f t="shared" si="16"/>
-        <v>5975</v>
-      </c>
-      <c r="F137" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
+        <f t="shared" si="12"/>
+        <v>137</v>
+      </c>
+      <c r="B138" s="10">
+        <f t="shared" si="15"/>
+        <v>56</v>
+      </c>
+      <c r="C138" s="10">
+        <v>0</v>
+      </c>
+      <c r="E138" s="12">
+        <f t="shared" si="13"/>
+        <v>3321</v>
+      </c>
+      <c r="F138" s="13">
         <f t="shared" si="14"/>
-        <v>137</v>
-      </c>
-      <c r="B138" s="10">
-        <v>100</v>
-      </c>
-      <c r="C138" s="10">
-        <v>0</v>
-      </c>
-      <c r="E138" s="12">
-        <f t="shared" si="16"/>
-        <v>6075</v>
-      </c>
-      <c r="F138" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
+        <f t="shared" si="12"/>
+        <v>138</v>
+      </c>
+      <c r="B139" s="10">
+        <f t="shared" si="15"/>
+        <v>56</v>
+      </c>
+      <c r="C139" s="10">
+        <v>0</v>
+      </c>
+      <c r="E139" s="12">
+        <f t="shared" si="13"/>
+        <v>3377</v>
+      </c>
+      <c r="F139" s="13">
         <f t="shared" si="14"/>
-        <v>138</v>
-      </c>
-      <c r="B139" s="10">
-        <v>100</v>
-      </c>
-      <c r="C139" s="10">
-        <v>0</v>
-      </c>
-      <c r="E139" s="12">
-        <f t="shared" si="16"/>
-        <v>6175</v>
-      </c>
-      <c r="F139" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
+        <f t="shared" si="12"/>
+        <v>139</v>
+      </c>
+      <c r="B140" s="10">
+        <f t="shared" si="15"/>
+        <v>57</v>
+      </c>
+      <c r="C140" s="10">
+        <v>0</v>
+      </c>
+      <c r="E140" s="12">
+        <f t="shared" si="13"/>
+        <v>3434</v>
+      </c>
+      <c r="F140" s="13">
         <f t="shared" si="14"/>
-        <v>139</v>
-      </c>
-      <c r="B140" s="10">
-        <v>100</v>
-      </c>
-      <c r="C140" s="10">
-        <v>0</v>
-      </c>
-      <c r="E140" s="12">
-        <f t="shared" si="16"/>
-        <v>6275</v>
-      </c>
-      <c r="F140" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
+        <f t="shared" si="12"/>
+        <v>140</v>
+      </c>
+      <c r="B141" s="10">
+        <f t="shared" si="15"/>
+        <v>57</v>
+      </c>
+      <c r="C141" s="10">
+        <v>0</v>
+      </c>
+      <c r="E141" s="12">
+        <f t="shared" si="13"/>
+        <v>3491</v>
+      </c>
+      <c r="F141" s="13">
         <f t="shared" si="14"/>
-        <v>140</v>
-      </c>
-      <c r="B141" s="10">
-        <v>100</v>
-      </c>
-      <c r="C141" s="10">
-        <v>0</v>
-      </c>
-      <c r="E141" s="12">
-        <f t="shared" si="16"/>
-        <v>6375</v>
-      </c>
-      <c r="F141" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
+        <f t="shared" si="12"/>
+        <v>141</v>
+      </c>
+      <c r="B142" s="10">
+        <f t="shared" si="15"/>
+        <v>58</v>
+      </c>
+      <c r="C142" s="10">
+        <v>0</v>
+      </c>
+      <c r="E142" s="12">
+        <f t="shared" si="13"/>
+        <v>3549</v>
+      </c>
+      <c r="F142" s="13">
         <f t="shared" si="14"/>
-        <v>141</v>
-      </c>
-      <c r="B142" s="10">
-        <v>100</v>
-      </c>
-      <c r="C142" s="10">
-        <v>0</v>
-      </c>
-      <c r="E142" s="12">
-        <f t="shared" si="16"/>
-        <v>6475</v>
-      </c>
-      <c r="F142" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
+        <f t="shared" si="12"/>
+        <v>142</v>
+      </c>
+      <c r="B143" s="10">
+        <f t="shared" si="15"/>
+        <v>58</v>
+      </c>
+      <c r="C143" s="10">
+        <v>0</v>
+      </c>
+      <c r="E143" s="12">
+        <f t="shared" si="13"/>
+        <v>3607</v>
+      </c>
+      <c r="F143" s="13">
         <f t="shared" si="14"/>
-        <v>142</v>
-      </c>
-      <c r="B143" s="10">
-        <v>100</v>
-      </c>
-      <c r="C143" s="10">
-        <v>0</v>
-      </c>
-      <c r="E143" s="12">
-        <f t="shared" si="16"/>
-        <v>6575</v>
-      </c>
-      <c r="F143" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
+        <f t="shared" si="12"/>
+        <v>143</v>
+      </c>
+      <c r="B144" s="10">
+        <f t="shared" si="15"/>
+        <v>59</v>
+      </c>
+      <c r="C144" s="10">
+        <v>0</v>
+      </c>
+      <c r="E144" s="12">
+        <f t="shared" si="13"/>
+        <v>3666</v>
+      </c>
+      <c r="F144" s="13">
         <f t="shared" si="14"/>
-        <v>143</v>
-      </c>
-      <c r="B144" s="10">
-        <v>100</v>
-      </c>
-      <c r="C144" s="10">
-        <v>0</v>
-      </c>
-      <c r="E144" s="12">
-        <f t="shared" si="16"/>
-        <v>6675</v>
-      </c>
-      <c r="F144" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="B145" s="10">
+        <f t="shared" si="15"/>
+        <v>59</v>
+      </c>
+      <c r="C145" s="10">
+        <v>0</v>
+      </c>
+      <c r="E145" s="12">
+        <f t="shared" si="13"/>
+        <v>3725</v>
+      </c>
+      <c r="F145" s="13">
         <f t="shared" si="14"/>
-        <v>144</v>
-      </c>
-      <c r="B145" s="10">
-        <v>100</v>
-      </c>
-      <c r="C145" s="10">
-        <v>0</v>
-      </c>
-      <c r="E145" s="12">
-        <f t="shared" si="16"/>
-        <v>6775</v>
-      </c>
-      <c r="F145" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
+        <f t="shared" si="12"/>
+        <v>145</v>
+      </c>
+      <c r="B146" s="10">
+        <f t="shared" si="15"/>
+        <v>60</v>
+      </c>
+      <c r="C146" s="10">
+        <v>0</v>
+      </c>
+      <c r="E146" s="12">
+        <f t="shared" si="13"/>
+        <v>3785</v>
+      </c>
+      <c r="F146" s="13">
         <f t="shared" si="14"/>
-        <v>145</v>
-      </c>
-      <c r="B146" s="10">
-        <v>100</v>
-      </c>
-      <c r="C146" s="10">
-        <v>0</v>
-      </c>
-      <c r="E146" s="12">
-        <f t="shared" si="16"/>
-        <v>6875</v>
-      </c>
-      <c r="F146" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
+        <f t="shared" si="12"/>
+        <v>146</v>
+      </c>
+      <c r="B147" s="10">
+        <f t="shared" si="15"/>
+        <v>60</v>
+      </c>
+      <c r="C147" s="10">
+        <v>0</v>
+      </c>
+      <c r="E147" s="12">
+        <f t="shared" si="13"/>
+        <v>3845</v>
+      </c>
+      <c r="F147" s="13">
         <f t="shared" si="14"/>
-        <v>146</v>
-      </c>
-      <c r="B147" s="10">
-        <v>100</v>
-      </c>
-      <c r="C147" s="10">
-        <v>0</v>
-      </c>
-      <c r="E147" s="12">
-        <f t="shared" si="16"/>
-        <v>6975</v>
-      </c>
-      <c r="F147" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
+        <f t="shared" si="12"/>
+        <v>147</v>
+      </c>
+      <c r="B148" s="10">
+        <f t="shared" si="15"/>
+        <v>61</v>
+      </c>
+      <c r="C148" s="10">
+        <v>0</v>
+      </c>
+      <c r="E148" s="12">
+        <f t="shared" si="13"/>
+        <v>3906</v>
+      </c>
+      <c r="F148" s="13">
         <f t="shared" si="14"/>
-        <v>147</v>
-      </c>
-      <c r="B148" s="10">
-        <v>100</v>
-      </c>
-      <c r="C148" s="10">
-        <v>0</v>
-      </c>
-      <c r="E148" s="12">
-        <f t="shared" si="16"/>
-        <v>7075</v>
-      </c>
-      <c r="F148" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
+        <f t="shared" si="12"/>
+        <v>148</v>
+      </c>
+      <c r="B149" s="10">
+        <f t="shared" si="15"/>
+        <v>61</v>
+      </c>
+      <c r="C149" s="10">
+        <v>0</v>
+      </c>
+      <c r="E149" s="12">
+        <f t="shared" si="13"/>
+        <v>3967</v>
+      </c>
+      <c r="F149" s="13">
         <f t="shared" si="14"/>
-        <v>148</v>
-      </c>
-      <c r="B149" s="10">
-        <v>100</v>
-      </c>
-      <c r="C149" s="10">
-        <v>0</v>
-      </c>
-      <c r="E149" s="12">
-        <f t="shared" si="16"/>
-        <v>7175</v>
-      </c>
-      <c r="F149" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
+        <f t="shared" si="12"/>
+        <v>149</v>
+      </c>
+      <c r="B150" s="10">
+        <f t="shared" si="15"/>
+        <v>62</v>
+      </c>
+      <c r="C150" s="10">
+        <v>0</v>
+      </c>
+      <c r="E150" s="12">
+        <f t="shared" si="13"/>
+        <v>4029</v>
+      </c>
+      <c r="F150" s="13">
         <f t="shared" si="14"/>
-        <v>149</v>
-      </c>
-      <c r="B150" s="10">
-        <v>100</v>
-      </c>
-      <c r="C150" s="10">
-        <v>0</v>
-      </c>
-      <c r="E150" s="12">
-        <f t="shared" si="16"/>
-        <v>7275</v>
-      </c>
-      <c r="F150" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
+        <f t="shared" si="12"/>
+        <v>150</v>
+      </c>
+      <c r="B151" s="10">
+        <f t="shared" si="15"/>
+        <v>62</v>
+      </c>
+      <c r="C151" s="10">
+        <v>0</v>
+      </c>
+      <c r="E151" s="12">
+        <f t="shared" si="13"/>
+        <v>4091</v>
+      </c>
+      <c r="F151" s="13">
         <f t="shared" si="14"/>
-        <v>150</v>
-      </c>
-      <c r="B151" s="10">
-        <v>100</v>
-      </c>
-      <c r="C151" s="10">
-        <v>0</v>
-      </c>
-      <c r="E151" s="12">
-        <f t="shared" si="16"/>
-        <v>7375</v>
-      </c>
-      <c r="F151" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
+        <f t="shared" si="12"/>
+        <v>151</v>
+      </c>
+      <c r="B152" s="10">
+        <f t="shared" si="15"/>
+        <v>63</v>
+      </c>
+      <c r="C152" s="10">
+        <v>0</v>
+      </c>
+      <c r="E152" s="12">
+        <f t="shared" si="13"/>
+        <v>4154</v>
+      </c>
+      <c r="F152" s="13">
         <f t="shared" si="14"/>
-        <v>151</v>
-      </c>
-      <c r="B152" s="10">
-        <v>100</v>
-      </c>
-      <c r="C152" s="10">
-        <v>0</v>
-      </c>
-      <c r="E152" s="12">
-        <f t="shared" si="16"/>
-        <v>7475</v>
-      </c>
-      <c r="F152" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
+        <f t="shared" si="12"/>
+        <v>152</v>
+      </c>
+      <c r="B153" s="10">
+        <f t="shared" si="15"/>
+        <v>63</v>
+      </c>
+      <c r="C153" s="10">
+        <v>0</v>
+      </c>
+      <c r="E153" s="12">
+        <f t="shared" si="13"/>
+        <v>4217</v>
+      </c>
+      <c r="F153" s="13">
         <f t="shared" si="14"/>
-        <v>152</v>
-      </c>
-      <c r="B153" s="10">
-        <v>100</v>
-      </c>
-      <c r="C153" s="10">
-        <v>0</v>
-      </c>
-      <c r="E153" s="12">
-        <f t="shared" si="16"/>
-        <v>7575</v>
-      </c>
-      <c r="F153" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
+        <f t="shared" si="12"/>
+        <v>153</v>
+      </c>
+      <c r="B154" s="10">
+        <f t="shared" si="15"/>
+        <v>64</v>
+      </c>
+      <c r="C154" s="10">
+        <v>0</v>
+      </c>
+      <c r="E154" s="12">
+        <f t="shared" si="13"/>
+        <v>4281</v>
+      </c>
+      <c r="F154" s="13">
         <f t="shared" si="14"/>
-        <v>153</v>
-      </c>
-      <c r="B154" s="10">
-        <v>100</v>
-      </c>
-      <c r="C154" s="10">
-        <v>0</v>
-      </c>
-      <c r="E154" s="12">
-        <f t="shared" si="16"/>
-        <v>7675</v>
-      </c>
-      <c r="F154" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
+        <f t="shared" si="12"/>
+        <v>154</v>
+      </c>
+      <c r="B155" s="10">
+        <f t="shared" si="15"/>
+        <v>64</v>
+      </c>
+      <c r="C155" s="10">
+        <v>0</v>
+      </c>
+      <c r="E155" s="12">
+        <f t="shared" si="13"/>
+        <v>4345</v>
+      </c>
+      <c r="F155" s="13">
         <f t="shared" si="14"/>
-        <v>154</v>
-      </c>
-      <c r="B155" s="10">
-        <v>100</v>
-      </c>
-      <c r="C155" s="10">
-        <v>0</v>
-      </c>
-      <c r="E155" s="12">
-        <f t="shared" si="16"/>
-        <v>7775</v>
-      </c>
-      <c r="F155" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
+        <f t="shared" si="12"/>
+        <v>155</v>
+      </c>
+      <c r="B156" s="10">
+        <f t="shared" si="15"/>
+        <v>65</v>
+      </c>
+      <c r="C156" s="10">
+        <v>0</v>
+      </c>
+      <c r="E156" s="12">
+        <f t="shared" si="13"/>
+        <v>4410</v>
+      </c>
+      <c r="F156" s="13">
         <f t="shared" si="14"/>
-        <v>155</v>
-      </c>
-      <c r="B156" s="10">
-        <v>100</v>
-      </c>
-      <c r="C156" s="10">
-        <v>0</v>
-      </c>
-      <c r="E156" s="12">
-        <f t="shared" si="16"/>
-        <v>7875</v>
-      </c>
-      <c r="F156" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
+        <f t="shared" si="12"/>
+        <v>156</v>
+      </c>
+      <c r="B157" s="10">
+        <f t="shared" si="15"/>
+        <v>65</v>
+      </c>
+      <c r="C157" s="10">
+        <v>0</v>
+      </c>
+      <c r="E157" s="12">
+        <f t="shared" si="13"/>
+        <v>4475</v>
+      </c>
+      <c r="F157" s="13">
         <f t="shared" si="14"/>
-        <v>156</v>
-      </c>
-      <c r="B157" s="10">
-        <v>100</v>
-      </c>
-      <c r="C157" s="10">
-        <v>0</v>
-      </c>
-      <c r="E157" s="12">
-        <f t="shared" si="16"/>
-        <v>7975</v>
-      </c>
-      <c r="F157" s="13">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
-        <f t="shared" ref="A158:A221" si="18">A157+1</f>
+        <f t="shared" ref="A158:B221" si="16">A157+1</f>
         <v>157</v>
       </c>
       <c r="B158" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>66</v>
       </c>
       <c r="C158" s="10">
         <v>0</v>
       </c>
       <c r="E158" s="12">
-        <f t="shared" si="16"/>
-        <v>8075</v>
+        <f t="shared" si="13"/>
+        <v>4541</v>
       </c>
       <c r="F158" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>158</v>
       </c>
       <c r="B159" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>66</v>
       </c>
       <c r="C159" s="10">
         <v>0</v>
       </c>
       <c r="E159" s="12">
-        <f t="shared" si="16"/>
-        <v>8175</v>
+        <f t="shared" si="13"/>
+        <v>4607</v>
       </c>
       <c r="F159" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>159</v>
       </c>
       <c r="B160" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>67</v>
       </c>
       <c r="C160" s="10">
         <v>0</v>
       </c>
       <c r="E160" s="12">
-        <f t="shared" si="16"/>
-        <v>8275</v>
+        <f t="shared" si="13"/>
+        <v>4674</v>
       </c>
       <c r="F160" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>160</v>
       </c>
       <c r="B161" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>67</v>
       </c>
       <c r="C161" s="10">
         <v>0</v>
       </c>
       <c r="E161" s="12">
-        <f t="shared" si="16"/>
-        <v>8375</v>
+        <f t="shared" si="13"/>
+        <v>4741</v>
       </c>
       <c r="F161" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>161</v>
       </c>
       <c r="B162" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>68</v>
       </c>
       <c r="C162" s="10">
         <v>0</v>
       </c>
       <c r="E162" s="12">
-        <f t="shared" si="16"/>
-        <v>8475</v>
+        <f t="shared" si="13"/>
+        <v>4809</v>
       </c>
       <c r="F162" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>162</v>
       </c>
       <c r="B163" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>68</v>
       </c>
       <c r="C163" s="10">
         <v>0</v>
       </c>
       <c r="E163" s="12">
-        <f t="shared" si="16"/>
-        <v>8575</v>
+        <f t="shared" si="13"/>
+        <v>4877</v>
       </c>
       <c r="F163" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>163</v>
       </c>
       <c r="B164" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>69</v>
       </c>
       <c r="C164" s="10">
         <v>0</v>
       </c>
       <c r="E164" s="12">
-        <f t="shared" si="16"/>
-        <v>8675</v>
+        <f t="shared" si="13"/>
+        <v>4946</v>
       </c>
       <c r="F164" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>164</v>
       </c>
       <c r="B165" s="10">
-        <v>100</v>
+        <f t="shared" si="15"/>
+        <v>69</v>
       </c>
       <c r="C165" s="10">
         <v>0</v>
       </c>
       <c r="E165" s="12">
-        <f t="shared" ref="E165:E228" si="19">E164+B165</f>
-        <v>8775</v>
+        <f t="shared" ref="E165:E228" si="17">E164+B165</f>
+        <v>5015</v>
       </c>
       <c r="F165" s="13">
-        <f t="shared" ref="F165:F228" si="20">B165-B164</f>
+        <f t="shared" ref="F165:F228" si="18">B165-B164</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
+        <f t="shared" si="16"/>
+        <v>165</v>
+      </c>
+      <c r="B166" s="10">
+        <f t="shared" si="15"/>
+        <v>70</v>
+      </c>
+      <c r="C166" s="10">
+        <v>0</v>
+      </c>
+      <c r="E166" s="12">
+        <f t="shared" si="17"/>
+        <v>5085</v>
+      </c>
+      <c r="F166" s="13">
         <f t="shared" si="18"/>
-        <v>165</v>
-      </c>
-      <c r="B166" s="10">
-        <v>100</v>
-      </c>
-      <c r="C166" s="10">
-        <v>0</v>
-      </c>
-      <c r="E166" s="12">
-        <f t="shared" si="19"/>
-        <v>8875</v>
-      </c>
-      <c r="F166" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
+        <f t="shared" si="16"/>
+        <v>166</v>
+      </c>
+      <c r="B167" s="10">
+        <f t="shared" si="15"/>
+        <v>70</v>
+      </c>
+      <c r="C167" s="10">
+        <v>0</v>
+      </c>
+      <c r="E167" s="12">
+        <f t="shared" si="17"/>
+        <v>5155</v>
+      </c>
+      <c r="F167" s="13">
         <f t="shared" si="18"/>
-        <v>166</v>
-      </c>
-      <c r="B167" s="10">
-        <v>100</v>
-      </c>
-      <c r="C167" s="10">
-        <v>0</v>
-      </c>
-      <c r="E167" s="12">
-        <f t="shared" si="19"/>
-        <v>8975</v>
-      </c>
-      <c r="F167" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
+        <f t="shared" si="16"/>
+        <v>167</v>
+      </c>
+      <c r="B168" s="10">
+        <f t="shared" si="15"/>
+        <v>71</v>
+      </c>
+      <c r="C168" s="10">
+        <v>0</v>
+      </c>
+      <c r="E168" s="12">
+        <f t="shared" si="17"/>
+        <v>5226</v>
+      </c>
+      <c r="F168" s="13">
         <f t="shared" si="18"/>
-        <v>167</v>
-      </c>
-      <c r="B168" s="10">
-        <v>100</v>
-      </c>
-      <c r="C168" s="10">
-        <v>0</v>
-      </c>
-      <c r="E168" s="12">
-        <f t="shared" si="19"/>
-        <v>9075</v>
-      </c>
-      <c r="F168" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
+        <f t="shared" si="16"/>
+        <v>168</v>
+      </c>
+      <c r="B169" s="10">
+        <f t="shared" si="15"/>
+        <v>71</v>
+      </c>
+      <c r="C169" s="10">
+        <v>0</v>
+      </c>
+      <c r="E169" s="12">
+        <f t="shared" si="17"/>
+        <v>5297</v>
+      </c>
+      <c r="F169" s="13">
         <f t="shared" si="18"/>
-        <v>168</v>
-      </c>
-      <c r="B169" s="10">
-        <v>100</v>
-      </c>
-      <c r="C169" s="10">
-        <v>0</v>
-      </c>
-      <c r="E169" s="12">
-        <f t="shared" si="19"/>
-        <v>9175</v>
-      </c>
-      <c r="F169" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
+        <f t="shared" si="16"/>
+        <v>169</v>
+      </c>
+      <c r="B170" s="10">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="C170" s="10">
+        <v>0</v>
+      </c>
+      <c r="E170" s="12">
+        <f t="shared" si="17"/>
+        <v>5369</v>
+      </c>
+      <c r="F170" s="13">
         <f t="shared" si="18"/>
-        <v>169</v>
-      </c>
-      <c r="B170" s="10">
-        <v>100</v>
-      </c>
-      <c r="C170" s="10">
-        <v>0</v>
-      </c>
-      <c r="E170" s="12">
-        <f t="shared" si="19"/>
-        <v>9275</v>
-      </c>
-      <c r="F170" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
+        <f t="shared" si="16"/>
+        <v>170</v>
+      </c>
+      <c r="B171" s="10">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="C171" s="10">
+        <v>0</v>
+      </c>
+      <c r="E171" s="12">
+        <f t="shared" si="17"/>
+        <v>5441</v>
+      </c>
+      <c r="F171" s="13">
         <f t="shared" si="18"/>
-        <v>170</v>
-      </c>
-      <c r="B171" s="10">
-        <v>100</v>
-      </c>
-      <c r="C171" s="10">
-        <v>0</v>
-      </c>
-      <c r="E171" s="12">
-        <f t="shared" si="19"/>
-        <v>9375</v>
-      </c>
-      <c r="F171" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
+        <f t="shared" si="16"/>
+        <v>171</v>
+      </c>
+      <c r="B172" s="10">
+        <f t="shared" si="15"/>
+        <v>73</v>
+      </c>
+      <c r="C172" s="10">
+        <v>0</v>
+      </c>
+      <c r="E172" s="12">
+        <f t="shared" si="17"/>
+        <v>5514</v>
+      </c>
+      <c r="F172" s="13">
         <f t="shared" si="18"/>
-        <v>171</v>
-      </c>
-      <c r="B172" s="10">
-        <v>100</v>
-      </c>
-      <c r="C172" s="10">
-        <v>0</v>
-      </c>
-      <c r="E172" s="12">
-        <f t="shared" si="19"/>
-        <v>9475</v>
-      </c>
-      <c r="F172" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
+        <f t="shared" si="16"/>
+        <v>172</v>
+      </c>
+      <c r="B173" s="10">
+        <f t="shared" si="15"/>
+        <v>73</v>
+      </c>
+      <c r="C173" s="10">
+        <v>0</v>
+      </c>
+      <c r="E173" s="12">
+        <f t="shared" si="17"/>
+        <v>5587</v>
+      </c>
+      <c r="F173" s="13">
         <f t="shared" si="18"/>
-        <v>172</v>
-      </c>
-      <c r="B173" s="10">
-        <v>100</v>
-      </c>
-      <c r="C173" s="10">
-        <v>0</v>
-      </c>
-      <c r="E173" s="12">
-        <f t="shared" si="19"/>
-        <v>9575</v>
-      </c>
-      <c r="F173" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
+        <f t="shared" si="16"/>
+        <v>173</v>
+      </c>
+      <c r="B174" s="10">
+        <f t="shared" si="15"/>
+        <v>74</v>
+      </c>
+      <c r="C174" s="10">
+        <v>0</v>
+      </c>
+      <c r="E174" s="12">
+        <f t="shared" si="17"/>
+        <v>5661</v>
+      </c>
+      <c r="F174" s="13">
         <f t="shared" si="18"/>
-        <v>173</v>
-      </c>
-      <c r="B174" s="10">
-        <v>100</v>
-      </c>
-      <c r="C174" s="10">
-        <v>0</v>
-      </c>
-      <c r="E174" s="12">
-        <f t="shared" si="19"/>
-        <v>9675</v>
-      </c>
-      <c r="F174" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
+        <f t="shared" si="16"/>
+        <v>174</v>
+      </c>
+      <c r="B175" s="10">
+        <f t="shared" si="15"/>
+        <v>74</v>
+      </c>
+      <c r="C175" s="10">
+        <v>0</v>
+      </c>
+      <c r="E175" s="12">
+        <f t="shared" si="17"/>
+        <v>5735</v>
+      </c>
+      <c r="F175" s="13">
         <f t="shared" si="18"/>
-        <v>174</v>
-      </c>
-      <c r="B175" s="10">
-        <v>100</v>
-      </c>
-      <c r="C175" s="10">
-        <v>0</v>
-      </c>
-      <c r="E175" s="12">
-        <f t="shared" si="19"/>
-        <v>9775</v>
-      </c>
-      <c r="F175" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
+        <f t="shared" si="16"/>
+        <v>175</v>
+      </c>
+      <c r="B176" s="10">
+        <f t="shared" si="15"/>
+        <v>75</v>
+      </c>
+      <c r="C176" s="10">
+        <v>0</v>
+      </c>
+      <c r="E176" s="12">
+        <f t="shared" si="17"/>
+        <v>5810</v>
+      </c>
+      <c r="F176" s="13">
         <f t="shared" si="18"/>
-        <v>175</v>
-      </c>
-      <c r="B176" s="10">
-        <v>100</v>
-      </c>
-      <c r="C176" s="10">
-        <v>0</v>
-      </c>
-      <c r="E176" s="12">
-        <f t="shared" si="19"/>
-        <v>9875</v>
-      </c>
-      <c r="F176" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
+        <f t="shared" si="16"/>
+        <v>176</v>
+      </c>
+      <c r="B177" s="10">
+        <f t="shared" si="15"/>
+        <v>75</v>
+      </c>
+      <c r="C177" s="10">
+        <v>0</v>
+      </c>
+      <c r="E177" s="12">
+        <f t="shared" si="17"/>
+        <v>5885</v>
+      </c>
+      <c r="F177" s="13">
         <f t="shared" si="18"/>
-        <v>176</v>
-      </c>
-      <c r="B177" s="10">
-        <v>100</v>
-      </c>
-      <c r="C177" s="10">
-        <v>0</v>
-      </c>
-      <c r="E177" s="12">
-        <f t="shared" si="19"/>
-        <v>9975</v>
-      </c>
-      <c r="F177" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
+        <f t="shared" si="16"/>
+        <v>177</v>
+      </c>
+      <c r="B178" s="10">
+        <f t="shared" si="15"/>
+        <v>76</v>
+      </c>
+      <c r="C178" s="10">
+        <v>0</v>
+      </c>
+      <c r="E178" s="12">
+        <f t="shared" si="17"/>
+        <v>5961</v>
+      </c>
+      <c r="F178" s="13">
         <f t="shared" si="18"/>
-        <v>177</v>
-      </c>
-      <c r="B178" s="10">
-        <v>100</v>
-      </c>
-      <c r="C178" s="10">
-        <v>0</v>
-      </c>
-      <c r="E178" s="12">
-        <f t="shared" si="19"/>
-        <v>10075</v>
-      </c>
-      <c r="F178" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
+        <f t="shared" si="16"/>
+        <v>178</v>
+      </c>
+      <c r="B179" s="10">
+        <f t="shared" si="15"/>
+        <v>76</v>
+      </c>
+      <c r="C179" s="10">
+        <v>0</v>
+      </c>
+      <c r="E179" s="12">
+        <f t="shared" si="17"/>
+        <v>6037</v>
+      </c>
+      <c r="F179" s="13">
         <f t="shared" si="18"/>
-        <v>178</v>
-      </c>
-      <c r="B179" s="10">
-        <v>100</v>
-      </c>
-      <c r="C179" s="10">
-        <v>0</v>
-      </c>
-      <c r="E179" s="12">
-        <f t="shared" si="19"/>
-        <v>10175</v>
-      </c>
-      <c r="F179" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
+        <f t="shared" si="16"/>
+        <v>179</v>
+      </c>
+      <c r="B180" s="10">
+        <f t="shared" si="15"/>
+        <v>77</v>
+      </c>
+      <c r="C180" s="10">
+        <v>0</v>
+      </c>
+      <c r="E180" s="12">
+        <f t="shared" si="17"/>
+        <v>6114</v>
+      </c>
+      <c r="F180" s="13">
         <f t="shared" si="18"/>
-        <v>179</v>
-      </c>
-      <c r="B180" s="10">
-        <v>100</v>
-      </c>
-      <c r="C180" s="10">
-        <v>0</v>
-      </c>
-      <c r="E180" s="12">
-        <f t="shared" si="19"/>
-        <v>10275</v>
-      </c>
-      <c r="F180" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
+        <f t="shared" si="16"/>
+        <v>180</v>
+      </c>
+      <c r="B181" s="10">
+        <f t="shared" si="15"/>
+        <v>77</v>
+      </c>
+      <c r="C181" s="10">
+        <v>0</v>
+      </c>
+      <c r="E181" s="12">
+        <f t="shared" si="17"/>
+        <v>6191</v>
+      </c>
+      <c r="F181" s="13">
         <f t="shared" si="18"/>
-        <v>180</v>
-      </c>
-      <c r="B181" s="10">
-        <v>100</v>
-      </c>
-      <c r="C181" s="10">
-        <v>0</v>
-      </c>
-      <c r="E181" s="12">
-        <f t="shared" si="19"/>
-        <v>10375</v>
-      </c>
-      <c r="F181" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
+        <f t="shared" si="16"/>
+        <v>181</v>
+      </c>
+      <c r="B182" s="10">
+        <f t="shared" si="15"/>
+        <v>78</v>
+      </c>
+      <c r="C182" s="10">
+        <v>0</v>
+      </c>
+      <c r="E182" s="12">
+        <f t="shared" si="17"/>
+        <v>6269</v>
+      </c>
+      <c r="F182" s="13">
         <f t="shared" si="18"/>
-        <v>181</v>
-      </c>
-      <c r="B182" s="10">
-        <v>100</v>
-      </c>
-      <c r="C182" s="10">
-        <v>0</v>
-      </c>
-      <c r="E182" s="12">
-        <f t="shared" si="19"/>
-        <v>10475</v>
-      </c>
-      <c r="F182" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
+        <f t="shared" si="16"/>
+        <v>182</v>
+      </c>
+      <c r="B183" s="10">
+        <f t="shared" si="15"/>
+        <v>78</v>
+      </c>
+      <c r="C183" s="10">
+        <v>0</v>
+      </c>
+      <c r="E183" s="12">
+        <f t="shared" si="17"/>
+        <v>6347</v>
+      </c>
+      <c r="F183" s="13">
         <f t="shared" si="18"/>
-        <v>182</v>
-      </c>
-      <c r="B183" s="10">
-        <v>100</v>
-      </c>
-      <c r="C183" s="10">
-        <v>0</v>
-      </c>
-      <c r="E183" s="12">
-        <f t="shared" si="19"/>
-        <v>10575</v>
-      </c>
-      <c r="F183" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
+        <f t="shared" si="16"/>
+        <v>183</v>
+      </c>
+      <c r="B184" s="10">
+        <f t="shared" si="15"/>
+        <v>79</v>
+      </c>
+      <c r="C184" s="10">
+        <v>0</v>
+      </c>
+      <c r="E184" s="12">
+        <f t="shared" si="17"/>
+        <v>6426</v>
+      </c>
+      <c r="F184" s="13">
         <f t="shared" si="18"/>
-        <v>183</v>
-      </c>
-      <c r="B184" s="10">
-        <v>100</v>
-      </c>
-      <c r="C184" s="10">
-        <v>0</v>
-      </c>
-      <c r="E184" s="12">
-        <f t="shared" si="19"/>
-        <v>10675</v>
-      </c>
-      <c r="F184" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
+        <f t="shared" si="16"/>
+        <v>184</v>
+      </c>
+      <c r="B185" s="10">
+        <f t="shared" si="15"/>
+        <v>79</v>
+      </c>
+      <c r="C185" s="10">
+        <v>0</v>
+      </c>
+      <c r="E185" s="12">
+        <f t="shared" si="17"/>
+        <v>6505</v>
+      </c>
+      <c r="F185" s="13">
         <f t="shared" si="18"/>
-        <v>184</v>
-      </c>
-      <c r="B185" s="10">
-        <v>100</v>
-      </c>
-      <c r="C185" s="10">
-        <v>0</v>
-      </c>
-      <c r="E185" s="12">
-        <f t="shared" si="19"/>
-        <v>10775</v>
-      </c>
-      <c r="F185" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
+        <f t="shared" si="16"/>
+        <v>185</v>
+      </c>
+      <c r="B186" s="10">
+        <f t="shared" si="15"/>
+        <v>80</v>
+      </c>
+      <c r="C186" s="10">
+        <v>0</v>
+      </c>
+      <c r="E186" s="12">
+        <f t="shared" si="17"/>
+        <v>6585</v>
+      </c>
+      <c r="F186" s="13">
         <f t="shared" si="18"/>
-        <v>185</v>
-      </c>
-      <c r="B186" s="10">
-        <v>100</v>
-      </c>
-      <c r="C186" s="10">
-        <v>0</v>
-      </c>
-      <c r="E186" s="12">
-        <f t="shared" si="19"/>
-        <v>10875</v>
-      </c>
-      <c r="F186" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
+        <f t="shared" si="16"/>
+        <v>186</v>
+      </c>
+      <c r="B187" s="10">
+        <f t="shared" si="15"/>
+        <v>80</v>
+      </c>
+      <c r="C187" s="10">
+        <v>0</v>
+      </c>
+      <c r="E187" s="12">
+        <f t="shared" si="17"/>
+        <v>6665</v>
+      </c>
+      <c r="F187" s="13">
         <f t="shared" si="18"/>
-        <v>186</v>
-      </c>
-      <c r="B187" s="10">
-        <v>100</v>
-      </c>
-      <c r="C187" s="10">
-        <v>0</v>
-      </c>
-      <c r="E187" s="12">
-        <f t="shared" si="19"/>
-        <v>10975</v>
-      </c>
-      <c r="F187" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
+        <f t="shared" si="16"/>
+        <v>187</v>
+      </c>
+      <c r="B188" s="10">
+        <f t="shared" si="15"/>
+        <v>81</v>
+      </c>
+      <c r="C188" s="10">
+        <v>0</v>
+      </c>
+      <c r="E188" s="12">
+        <f t="shared" si="17"/>
+        <v>6746</v>
+      </c>
+      <c r="F188" s="13">
         <f t="shared" si="18"/>
-        <v>187</v>
-      </c>
-      <c r="B188" s="10">
-        <v>100</v>
-      </c>
-      <c r="C188" s="10">
-        <v>0</v>
-      </c>
-      <c r="E188" s="12">
-        <f t="shared" si="19"/>
-        <v>11075</v>
-      </c>
-      <c r="F188" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
+        <f t="shared" si="16"/>
+        <v>188</v>
+      </c>
+      <c r="B189" s="10">
+        <f t="shared" ref="B189:B227" si="19">B187+1</f>
+        <v>81</v>
+      </c>
+      <c r="C189" s="10">
+        <v>0</v>
+      </c>
+      <c r="E189" s="12">
+        <f t="shared" si="17"/>
+        <v>6827</v>
+      </c>
+      <c r="F189" s="13">
         <f t="shared" si="18"/>
-        <v>188</v>
-      </c>
-      <c r="B189" s="10">
-        <v>100</v>
-      </c>
-      <c r="C189" s="10">
-        <v>0</v>
-      </c>
-      <c r="E189" s="12">
-        <f t="shared" si="19"/>
-        <v>11175</v>
-      </c>
-      <c r="F189" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
+        <f t="shared" si="16"/>
+        <v>189</v>
+      </c>
+      <c r="B190" s="10">
+        <f t="shared" si="19"/>
+        <v>82</v>
+      </c>
+      <c r="C190" s="10">
+        <v>0</v>
+      </c>
+      <c r="E190" s="12">
+        <f t="shared" si="17"/>
+        <v>6909</v>
+      </c>
+      <c r="F190" s="13">
         <f t="shared" si="18"/>
-        <v>189</v>
-      </c>
-      <c r="B190" s="10">
-        <v>100</v>
-      </c>
-      <c r="C190" s="10">
-        <v>0</v>
-      </c>
-      <c r="E190" s="12">
-        <f t="shared" si="19"/>
-        <v>11275</v>
-      </c>
-      <c r="F190" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
+        <f t="shared" si="16"/>
+        <v>190</v>
+      </c>
+      <c r="B191" s="10">
+        <f t="shared" si="19"/>
+        <v>82</v>
+      </c>
+      <c r="C191" s="10">
+        <v>0</v>
+      </c>
+      <c r="E191" s="12">
+        <f t="shared" si="17"/>
+        <v>6991</v>
+      </c>
+      <c r="F191" s="13">
         <f t="shared" si="18"/>
-        <v>190</v>
-      </c>
-      <c r="B191" s="10">
-        <v>100</v>
-      </c>
-      <c r="C191" s="10">
-        <v>0</v>
-      </c>
-      <c r="E191" s="12">
-        <f t="shared" si="19"/>
-        <v>11375</v>
-      </c>
-      <c r="F191" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
+        <f t="shared" si="16"/>
+        <v>191</v>
+      </c>
+      <c r="B192" s="10">
+        <f t="shared" si="19"/>
+        <v>83</v>
+      </c>
+      <c r="C192" s="10">
+        <v>0</v>
+      </c>
+      <c r="E192" s="12">
+        <f t="shared" si="17"/>
+        <v>7074</v>
+      </c>
+      <c r="F192" s="13">
         <f t="shared" si="18"/>
-        <v>191</v>
-      </c>
-      <c r="B192" s="10">
-        <v>100</v>
-      </c>
-      <c r="C192" s="10">
-        <v>0</v>
-      </c>
-      <c r="E192" s="12">
-        <f t="shared" si="19"/>
-        <v>11475</v>
-      </c>
-      <c r="F192" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
+        <f t="shared" si="16"/>
+        <v>192</v>
+      </c>
+      <c r="B193" s="10">
+        <f t="shared" si="19"/>
+        <v>83</v>
+      </c>
+      <c r="C193" s="10">
+        <v>0</v>
+      </c>
+      <c r="E193" s="12">
+        <f t="shared" si="17"/>
+        <v>7157</v>
+      </c>
+      <c r="F193" s="13">
         <f t="shared" si="18"/>
-        <v>192</v>
-      </c>
-      <c r="B193" s="10">
-        <v>100</v>
-      </c>
-      <c r="C193" s="10">
-        <v>0</v>
-      </c>
-      <c r="E193" s="12">
-        <f t="shared" si="19"/>
-        <v>11575</v>
-      </c>
-      <c r="F193" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
+        <f t="shared" si="16"/>
+        <v>193</v>
+      </c>
+      <c r="B194" s="10">
+        <f t="shared" si="19"/>
+        <v>84</v>
+      </c>
+      <c r="C194" s="10">
+        <v>0</v>
+      </c>
+      <c r="E194" s="12">
+        <f t="shared" si="17"/>
+        <v>7241</v>
+      </c>
+      <c r="F194" s="13">
         <f t="shared" si="18"/>
-        <v>193</v>
-      </c>
-      <c r="B194" s="10">
-        <v>100</v>
-      </c>
-      <c r="C194" s="10">
-        <v>0</v>
-      </c>
-      <c r="E194" s="12">
-        <f t="shared" si="19"/>
-        <v>11675</v>
-      </c>
-      <c r="F194" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
+        <f t="shared" si="16"/>
+        <v>194</v>
+      </c>
+      <c r="B195" s="10">
+        <f t="shared" si="19"/>
+        <v>84</v>
+      </c>
+      <c r="C195" s="10">
+        <v>0</v>
+      </c>
+      <c r="E195" s="12">
+        <f t="shared" si="17"/>
+        <v>7325</v>
+      </c>
+      <c r="F195" s="13">
         <f t="shared" si="18"/>
-        <v>194</v>
-      </c>
-      <c r="B195" s="10">
-        <v>100</v>
-      </c>
-      <c r="C195" s="10">
-        <v>0</v>
-      </c>
-      <c r="E195" s="12">
-        <f t="shared" si="19"/>
-        <v>11775</v>
-      </c>
-      <c r="F195" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
+        <f t="shared" si="16"/>
+        <v>195</v>
+      </c>
+      <c r="B196" s="10">
+        <f t="shared" si="19"/>
+        <v>85</v>
+      </c>
+      <c r="C196" s="10">
+        <v>0</v>
+      </c>
+      <c r="E196" s="12">
+        <f t="shared" si="17"/>
+        <v>7410</v>
+      </c>
+      <c r="F196" s="13">
         <f t="shared" si="18"/>
-        <v>195</v>
-      </c>
-      <c r="B196" s="10">
-        <v>100</v>
-      </c>
-      <c r="C196" s="10">
-        <v>0</v>
-      </c>
-      <c r="E196" s="12">
-        <f t="shared" si="19"/>
-        <v>11875</v>
-      </c>
-      <c r="F196" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
+        <f t="shared" si="16"/>
+        <v>196</v>
+      </c>
+      <c r="B197" s="10">
+        <f t="shared" si="19"/>
+        <v>85</v>
+      </c>
+      <c r="C197" s="10">
+        <v>0</v>
+      </c>
+      <c r="E197" s="12">
+        <f t="shared" si="17"/>
+        <v>7495</v>
+      </c>
+      <c r="F197" s="13">
         <f t="shared" si="18"/>
-        <v>196</v>
-      </c>
-      <c r="B197" s="10">
-        <v>100</v>
-      </c>
-      <c r="C197" s="10">
-        <v>0</v>
-      </c>
-      <c r="E197" s="12">
-        <f t="shared" si="19"/>
-        <v>11975</v>
-      </c>
-      <c r="F197" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
+        <f t="shared" si="16"/>
+        <v>197</v>
+      </c>
+      <c r="B198" s="10">
+        <f t="shared" si="19"/>
+        <v>86</v>
+      </c>
+      <c r="C198" s="10">
+        <v>0</v>
+      </c>
+      <c r="E198" s="12">
+        <f t="shared" si="17"/>
+        <v>7581</v>
+      </c>
+      <c r="F198" s="13">
         <f t="shared" si="18"/>
-        <v>197</v>
-      </c>
-      <c r="B198" s="10">
-        <v>100</v>
-      </c>
-      <c r="C198" s="10">
-        <v>0</v>
-      </c>
-      <c r="E198" s="12">
-        <f t="shared" si="19"/>
-        <v>12075</v>
-      </c>
-      <c r="F198" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
+        <f t="shared" si="16"/>
+        <v>198</v>
+      </c>
+      <c r="B199" s="10">
+        <f t="shared" si="19"/>
+        <v>86</v>
+      </c>
+      <c r="C199" s="10">
+        <v>0</v>
+      </c>
+      <c r="E199" s="12">
+        <f t="shared" si="17"/>
+        <v>7667</v>
+      </c>
+      <c r="F199" s="13">
         <f t="shared" si="18"/>
-        <v>198</v>
-      </c>
-      <c r="B199" s="10">
-        <v>100</v>
-      </c>
-      <c r="C199" s="10">
-        <v>0</v>
-      </c>
-      <c r="E199" s="12">
-        <f t="shared" si="19"/>
-        <v>12175</v>
-      </c>
-      <c r="F199" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
+        <f t="shared" si="16"/>
+        <v>199</v>
+      </c>
+      <c r="B200" s="10">
+        <f t="shared" si="19"/>
+        <v>87</v>
+      </c>
+      <c r="C200" s="10">
+        <v>0</v>
+      </c>
+      <c r="E200" s="12">
+        <f t="shared" si="17"/>
+        <v>7754</v>
+      </c>
+      <c r="F200" s="13">
         <f t="shared" si="18"/>
-        <v>199</v>
-      </c>
-      <c r="B200" s="10">
-        <v>100</v>
-      </c>
-      <c r="C200" s="10">
-        <v>0</v>
-      </c>
-      <c r="E200" s="12">
-        <f t="shared" si="19"/>
-        <v>12275</v>
-      </c>
-      <c r="F200" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
+        <f t="shared" si="16"/>
+        <v>200</v>
+      </c>
+      <c r="B201" s="10">
+        <f t="shared" si="19"/>
+        <v>87</v>
+      </c>
+      <c r="C201" s="10">
+        <v>0</v>
+      </c>
+      <c r="E201" s="12">
+        <f t="shared" si="17"/>
+        <v>7841</v>
+      </c>
+      <c r="F201" s="13">
         <f t="shared" si="18"/>
-        <v>200</v>
-      </c>
-      <c r="B201" s="10">
-        <v>100</v>
-      </c>
-      <c r="C201" s="10">
-        <v>0</v>
-      </c>
-      <c r="E201" s="12">
-        <f t="shared" si="19"/>
-        <v>12375</v>
-      </c>
-      <c r="F201" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
+        <f t="shared" si="16"/>
+        <v>201</v>
+      </c>
+      <c r="B202" s="10">
+        <f t="shared" si="19"/>
+        <v>88</v>
+      </c>
+      <c r="C202" s="10">
+        <v>0</v>
+      </c>
+      <c r="E202" s="12">
+        <f t="shared" si="17"/>
+        <v>7929</v>
+      </c>
+      <c r="F202" s="13">
         <f t="shared" si="18"/>
-        <v>201</v>
-      </c>
-      <c r="B202" s="10">
-        <v>100</v>
-      </c>
-      <c r="C202" s="10">
-        <v>0</v>
-      </c>
-      <c r="E202" s="12">
-        <f t="shared" si="19"/>
-        <v>12475</v>
-      </c>
-      <c r="F202" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
+        <f t="shared" si="16"/>
+        <v>202</v>
+      </c>
+      <c r="B203" s="10">
+        <f t="shared" si="19"/>
+        <v>88</v>
+      </c>
+      <c r="C203" s="10">
+        <v>0</v>
+      </c>
+      <c r="E203" s="12">
+        <f t="shared" si="17"/>
+        <v>8017</v>
+      </c>
+      <c r="F203" s="13">
         <f t="shared" si="18"/>
-        <v>202</v>
-      </c>
-      <c r="B203" s="10">
-        <v>100</v>
-      </c>
-      <c r="C203" s="10">
-        <v>0</v>
-      </c>
-      <c r="E203" s="12">
-        <f t="shared" si="19"/>
-        <v>12575</v>
-      </c>
-      <c r="F203" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
+        <f t="shared" si="16"/>
+        <v>203</v>
+      </c>
+      <c r="B204" s="10">
+        <f t="shared" si="19"/>
+        <v>89</v>
+      </c>
+      <c r="C204" s="10">
+        <v>0</v>
+      </c>
+      <c r="E204" s="12">
+        <f t="shared" si="17"/>
+        <v>8106</v>
+      </c>
+      <c r="F204" s="13">
         <f t="shared" si="18"/>
-        <v>203</v>
-      </c>
-      <c r="B204" s="10">
-        <v>100</v>
-      </c>
-      <c r="C204" s="10">
-        <v>0</v>
-      </c>
-      <c r="E204" s="12">
-        <f t="shared" si="19"/>
-        <v>12675</v>
-      </c>
-      <c r="F204" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
+        <f t="shared" si="16"/>
+        <v>204</v>
+      </c>
+      <c r="B205" s="10">
+        <f t="shared" si="19"/>
+        <v>89</v>
+      </c>
+      <c r="C205" s="10">
+        <v>0</v>
+      </c>
+      <c r="E205" s="12">
+        <f t="shared" si="17"/>
+        <v>8195</v>
+      </c>
+      <c r="F205" s="13">
         <f t="shared" si="18"/>
-        <v>204</v>
-      </c>
-      <c r="B205" s="10">
-        <v>100</v>
-      </c>
-      <c r="C205" s="10">
-        <v>0</v>
-      </c>
-      <c r="E205" s="12">
-        <f t="shared" si="19"/>
-        <v>12775</v>
-      </c>
-      <c r="F205" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
+        <f t="shared" si="16"/>
+        <v>205</v>
+      </c>
+      <c r="B206" s="10">
+        <f t="shared" si="19"/>
+        <v>90</v>
+      </c>
+      <c r="C206" s="10">
+        <v>0</v>
+      </c>
+      <c r="E206" s="12">
+        <f t="shared" si="17"/>
+        <v>8285</v>
+      </c>
+      <c r="F206" s="13">
         <f t="shared" si="18"/>
-        <v>205</v>
-      </c>
-      <c r="B206" s="10">
-        <v>100</v>
-      </c>
-      <c r="C206" s="10">
-        <v>0</v>
-      </c>
-      <c r="E206" s="12">
-        <f t="shared" si="19"/>
-        <v>12875</v>
-      </c>
-      <c r="F206" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
+        <f t="shared" si="16"/>
+        <v>206</v>
+      </c>
+      <c r="B207" s="10">
+        <f t="shared" si="19"/>
+        <v>90</v>
+      </c>
+      <c r="C207" s="10">
+        <v>0</v>
+      </c>
+      <c r="E207" s="12">
+        <f t="shared" si="17"/>
+        <v>8375</v>
+      </c>
+      <c r="F207" s="13">
         <f t="shared" si="18"/>
-        <v>206</v>
-      </c>
-      <c r="B207" s="10">
-        <v>100</v>
-      </c>
-      <c r="C207" s="10">
-        <v>0</v>
-      </c>
-      <c r="E207" s="12">
-        <f t="shared" si="19"/>
-        <v>12975</v>
-      </c>
-      <c r="F207" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
+        <f t="shared" si="16"/>
+        <v>207</v>
+      </c>
+      <c r="B208" s="10">
+        <f t="shared" si="19"/>
+        <v>91</v>
+      </c>
+      <c r="C208" s="10">
+        <v>0</v>
+      </c>
+      <c r="E208" s="12">
+        <f t="shared" si="17"/>
+        <v>8466</v>
+      </c>
+      <c r="F208" s="13">
         <f t="shared" si="18"/>
-        <v>207</v>
-      </c>
-      <c r="B208" s="10">
-        <v>100</v>
-      </c>
-      <c r="C208" s="10">
-        <v>0</v>
-      </c>
-      <c r="E208" s="12">
-        <f t="shared" si="19"/>
-        <v>13075</v>
-      </c>
-      <c r="F208" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
+        <f t="shared" si="16"/>
+        <v>208</v>
+      </c>
+      <c r="B209" s="10">
+        <f t="shared" si="19"/>
+        <v>91</v>
+      </c>
+      <c r="C209" s="10">
+        <v>0</v>
+      </c>
+      <c r="E209" s="12">
+        <f t="shared" si="17"/>
+        <v>8557</v>
+      </c>
+      <c r="F209" s="13">
         <f t="shared" si="18"/>
-        <v>208</v>
-      </c>
-      <c r="B209" s="10">
-        <v>100</v>
-      </c>
-      <c r="C209" s="10">
-        <v>0</v>
-      </c>
-      <c r="E209" s="12">
-        <f t="shared" si="19"/>
-        <v>13175</v>
-      </c>
-      <c r="F209" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
+        <f t="shared" si="16"/>
+        <v>209</v>
+      </c>
+      <c r="B210" s="10">
+        <f t="shared" si="19"/>
+        <v>92</v>
+      </c>
+      <c r="C210" s="10">
+        <v>0</v>
+      </c>
+      <c r="E210" s="12">
+        <f t="shared" si="17"/>
+        <v>8649</v>
+      </c>
+      <c r="F210" s="13">
         <f t="shared" si="18"/>
-        <v>209</v>
-      </c>
-      <c r="B210" s="10">
-        <v>100</v>
-      </c>
-      <c r="C210" s="10">
-        <v>0</v>
-      </c>
-      <c r="E210" s="12">
-        <f t="shared" si="19"/>
-        <v>13275</v>
-      </c>
-      <c r="F210" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
+        <f t="shared" si="16"/>
+        <v>210</v>
+      </c>
+      <c r="B211" s="10">
+        <f t="shared" si="19"/>
+        <v>92</v>
+      </c>
+      <c r="C211" s="10">
+        <v>0</v>
+      </c>
+      <c r="E211" s="12">
+        <f t="shared" si="17"/>
+        <v>8741</v>
+      </c>
+      <c r="F211" s="13">
         <f t="shared" si="18"/>
-        <v>210</v>
-      </c>
-      <c r="B211" s="10">
-        <v>100</v>
-      </c>
-      <c r="C211" s="10">
-        <v>0</v>
-      </c>
-      <c r="E211" s="12">
-        <f t="shared" si="19"/>
-        <v>13375</v>
-      </c>
-      <c r="F211" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
+        <f t="shared" si="16"/>
+        <v>211</v>
+      </c>
+      <c r="B212" s="10">
+        <f t="shared" si="19"/>
+        <v>93</v>
+      </c>
+      <c r="C212" s="10">
+        <v>0</v>
+      </c>
+      <c r="E212" s="12">
+        <f t="shared" si="17"/>
+        <v>8834</v>
+      </c>
+      <c r="F212" s="13">
         <f t="shared" si="18"/>
-        <v>211</v>
-      </c>
-      <c r="B212" s="10">
-        <v>100</v>
-      </c>
-      <c r="C212" s="10">
-        <v>0</v>
-      </c>
-      <c r="E212" s="12">
-        <f t="shared" si="19"/>
-        <v>13475</v>
-      </c>
-      <c r="F212" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
+        <f t="shared" si="16"/>
+        <v>212</v>
+      </c>
+      <c r="B213" s="10">
+        <f t="shared" si="19"/>
+        <v>93</v>
+      </c>
+      <c r="C213" s="10">
+        <v>0</v>
+      </c>
+      <c r="E213" s="12">
+        <f t="shared" si="17"/>
+        <v>8927</v>
+      </c>
+      <c r="F213" s="13">
         <f t="shared" si="18"/>
-        <v>212</v>
-      </c>
-      <c r="B213" s="10">
-        <v>100</v>
-      </c>
-      <c r="C213" s="10">
-        <v>0</v>
-      </c>
-      <c r="E213" s="12">
-        <f t="shared" si="19"/>
-        <v>13575</v>
-      </c>
-      <c r="F213" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
+        <f t="shared" si="16"/>
+        <v>213</v>
+      </c>
+      <c r="B214" s="10">
+        <f t="shared" si="19"/>
+        <v>94</v>
+      </c>
+      <c r="C214" s="10">
+        <v>0</v>
+      </c>
+      <c r="E214" s="12">
+        <f t="shared" si="17"/>
+        <v>9021</v>
+      </c>
+      <c r="F214" s="13">
         <f t="shared" si="18"/>
-        <v>213</v>
-      </c>
-      <c r="B214" s="10">
-        <v>100</v>
-      </c>
-      <c r="C214" s="10">
-        <v>0</v>
-      </c>
-      <c r="E214" s="12">
-        <f t="shared" si="19"/>
-        <v>13675</v>
-      </c>
-      <c r="F214" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
+        <f t="shared" si="16"/>
+        <v>214</v>
+      </c>
+      <c r="B215" s="10">
+        <f t="shared" si="19"/>
+        <v>94</v>
+      </c>
+      <c r="C215" s="10">
+        <v>0</v>
+      </c>
+      <c r="E215" s="12">
+        <f t="shared" si="17"/>
+        <v>9115</v>
+      </c>
+      <c r="F215" s="13">
         <f t="shared" si="18"/>
-        <v>214</v>
-      </c>
-      <c r="B215" s="10">
-        <v>100</v>
-      </c>
-      <c r="C215" s="10">
-        <v>0</v>
-      </c>
-      <c r="E215" s="12">
-        <f t="shared" si="19"/>
-        <v>13775</v>
-      </c>
-      <c r="F215" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
+        <f t="shared" si="16"/>
+        <v>215</v>
+      </c>
+      <c r="B216" s="10">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="C216" s="10">
+        <v>0</v>
+      </c>
+      <c r="E216" s="12">
+        <f t="shared" si="17"/>
+        <v>9210</v>
+      </c>
+      <c r="F216" s="13">
         <f t="shared" si="18"/>
-        <v>215</v>
-      </c>
-      <c r="B216" s="10">
-        <v>100</v>
-      </c>
-      <c r="C216" s="10">
-        <v>0</v>
-      </c>
-      <c r="E216" s="12">
-        <f t="shared" si="19"/>
-        <v>13875</v>
-      </c>
-      <c r="F216" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
+        <f t="shared" si="16"/>
+        <v>216</v>
+      </c>
+      <c r="B217" s="10">
+        <f t="shared" si="19"/>
+        <v>95</v>
+      </c>
+      <c r="C217" s="10">
+        <v>0</v>
+      </c>
+      <c r="E217" s="12">
+        <f t="shared" si="17"/>
+        <v>9305</v>
+      </c>
+      <c r="F217" s="13">
         <f t="shared" si="18"/>
-        <v>216</v>
-      </c>
-      <c r="B217" s="10">
-        <v>100</v>
-      </c>
-      <c r="C217" s="10">
-        <v>0</v>
-      </c>
-      <c r="E217" s="12">
-        <f t="shared" si="19"/>
-        <v>13975</v>
-      </c>
-      <c r="F217" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
+        <f t="shared" si="16"/>
+        <v>217</v>
+      </c>
+      <c r="B218" s="10">
+        <f t="shared" si="19"/>
+        <v>96</v>
+      </c>
+      <c r="C218" s="10">
+        <v>0</v>
+      </c>
+      <c r="E218" s="12">
+        <f t="shared" si="17"/>
+        <v>9401</v>
+      </c>
+      <c r="F218" s="13">
         <f t="shared" si="18"/>
-        <v>217</v>
-      </c>
-      <c r="B218" s="10">
-        <v>100</v>
-      </c>
-      <c r="C218" s="10">
-        <v>0</v>
-      </c>
-      <c r="E218" s="12">
-        <f t="shared" si="19"/>
-        <v>14075</v>
-      </c>
-      <c r="F218" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
+        <f t="shared" si="16"/>
+        <v>218</v>
+      </c>
+      <c r="B219" s="10">
+        <f t="shared" si="19"/>
+        <v>96</v>
+      </c>
+      <c r="C219" s="10">
+        <v>0</v>
+      </c>
+      <c r="E219" s="12">
+        <f t="shared" si="17"/>
+        <v>9497</v>
+      </c>
+      <c r="F219" s="13">
         <f t="shared" si="18"/>
-        <v>218</v>
-      </c>
-      <c r="B219" s="10">
-        <v>100</v>
-      </c>
-      <c r="C219" s="10">
-        <v>0</v>
-      </c>
-      <c r="E219" s="12">
-        <f t="shared" si="19"/>
-        <v>14175</v>
-      </c>
-      <c r="F219" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
+        <f t="shared" si="16"/>
+        <v>219</v>
+      </c>
+      <c r="B220" s="10">
+        <f t="shared" si="19"/>
+        <v>97</v>
+      </c>
+      <c r="C220" s="10">
+        <v>0</v>
+      </c>
+      <c r="E220" s="12">
+        <f t="shared" si="17"/>
+        <v>9594</v>
+      </c>
+      <c r="F220" s="13">
         <f t="shared" si="18"/>
-        <v>219</v>
-      </c>
-      <c r="B220" s="10">
-        <v>100</v>
-      </c>
-      <c r="C220" s="10">
-        <v>0</v>
-      </c>
-      <c r="E220" s="12">
-        <f t="shared" si="19"/>
-        <v>14275</v>
-      </c>
-      <c r="F220" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
+        <f t="shared" si="16"/>
+        <v>220</v>
+      </c>
+      <c r="B221" s="10">
+        <f t="shared" si="19"/>
+        <v>97</v>
+      </c>
+      <c r="C221" s="10">
+        <v>0</v>
+      </c>
+      <c r="E221" s="12">
+        <f t="shared" si="17"/>
+        <v>9691</v>
+      </c>
+      <c r="F221" s="13">
         <f t="shared" si="18"/>
-        <v>220</v>
-      </c>
-      <c r="B221" s="10">
-        <v>100</v>
-      </c>
-      <c r="C221" s="10">
-        <v>0</v>
-      </c>
-      <c r="E221" s="12">
-        <f t="shared" si="19"/>
-        <v>14375</v>
-      </c>
-      <c r="F221" s="13">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
-        <f t="shared" ref="A222:A285" si="21">A221+1</f>
+        <f t="shared" ref="A222:B285" si="20">A221+1</f>
         <v>221</v>
       </c>
       <c r="B222" s="10">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>98</v>
       </c>
       <c r="C222" s="10">
         <v>0</v>
       </c>
       <c r="E222" s="12">
-        <f t="shared" si="19"/>
-        <v>14475</v>
+        <f t="shared" si="17"/>
+        <v>9789</v>
       </c>
       <c r="F222" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>222</v>
       </c>
       <c r="B223" s="10">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>98</v>
       </c>
       <c r="C223" s="10">
         <v>0</v>
       </c>
       <c r="E223" s="12">
-        <f t="shared" si="19"/>
-        <v>14575</v>
+        <f t="shared" si="17"/>
+        <v>9887</v>
       </c>
       <c r="F223" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>223</v>
       </c>
       <c r="B224" s="10">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>99</v>
       </c>
       <c r="C224" s="10">
         <v>0</v>
       </c>
       <c r="E224" s="12">
-        <f t="shared" si="19"/>
-        <v>14675</v>
+        <f t="shared" si="17"/>
+        <v>9986</v>
       </c>
       <c r="F224" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>224</v>
       </c>
       <c r="B225" s="10">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>99</v>
       </c>
       <c r="C225" s="10">
         <v>0</v>
       </c>
       <c r="E225" s="12">
-        <f t="shared" si="19"/>
-        <v>14775</v>
+        <f t="shared" si="17"/>
+        <v>10085</v>
       </c>
       <c r="F225" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>225</v>
       </c>
       <c r="B226" s="10">
+        <f t="shared" si="19"/>
         <v>100</v>
       </c>
       <c r="C226" s="10">
         <v>0</v>
       </c>
       <c r="E226" s="12">
-        <f t="shared" si="19"/>
-        <v>14875</v>
+        <f t="shared" si="17"/>
+        <v>10185</v>
       </c>
       <c r="F226" s="13">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>226</v>
       </c>
       <c r="B227" s="10">
+        <f t="shared" si="19"/>
         <v>100</v>
       </c>
       <c r="C227" s="10">
         <v>0</v>
       </c>
       <c r="E227" s="12">
-        <f t="shared" si="19"/>
-        <v>14975</v>
+        <f t="shared" si="17"/>
+        <v>10285</v>
       </c>
       <c r="F227" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>227</v>
       </c>
       <c r="B228" s="10">
@@ -5219,17 +5340,17 @@
         <v>0</v>
       </c>
       <c r="E228" s="12">
-        <f t="shared" si="19"/>
-        <v>15075</v>
+        <f t="shared" si="17"/>
+        <v>10385</v>
       </c>
       <c r="F228" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>228</v>
       </c>
       <c r="B229" s="10">
@@ -5239,1137 +5360,1137 @@
         <v>0</v>
       </c>
       <c r="E229" s="12">
-        <f t="shared" ref="E229:E292" si="22">E228+B229</f>
-        <v>15175</v>
+        <f t="shared" ref="E229:E292" si="21">E228+B229</f>
+        <v>10485</v>
       </c>
       <c r="F229" s="13">
-        <f t="shared" ref="F229:F292" si="23">B229-B228</f>
+        <f t="shared" ref="F229:F292" si="22">B229-B228</f>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
+        <f t="shared" si="20"/>
+        <v>229</v>
+      </c>
+      <c r="B230" s="10">
+        <v>100</v>
+      </c>
+      <c r="C230" s="10">
+        <v>0</v>
+      </c>
+      <c r="E230" s="12">
         <f t="shared" si="21"/>
-        <v>229</v>
-      </c>
-      <c r="B230" s="10">
-        <v>100</v>
-      </c>
-      <c r="C230" s="10">
-        <v>0</v>
-      </c>
-      <c r="E230" s="12">
+        <v>10585</v>
+      </c>
+      <c r="F230" s="13">
         <f t="shared" si="22"/>
-        <v>15275</v>
-      </c>
-      <c r="F230" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
+        <f t="shared" si="20"/>
+        <v>230</v>
+      </c>
+      <c r="B231" s="10">
+        <v>100</v>
+      </c>
+      <c r="C231" s="10">
+        <v>0</v>
+      </c>
+      <c r="E231" s="12">
         <f t="shared" si="21"/>
-        <v>230</v>
-      </c>
-      <c r="B231" s="10">
-        <v>100</v>
-      </c>
-      <c r="C231" s="10">
-        <v>0</v>
-      </c>
-      <c r="E231" s="12">
+        <v>10685</v>
+      </c>
+      <c r="F231" s="13">
         <f t="shared" si="22"/>
-        <v>15375</v>
-      </c>
-      <c r="F231" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
+        <f t="shared" si="20"/>
+        <v>231</v>
+      </c>
+      <c r="B232" s="10">
+        <v>100</v>
+      </c>
+      <c r="C232" s="10">
+        <v>0</v>
+      </c>
+      <c r="E232" s="12">
         <f t="shared" si="21"/>
-        <v>231</v>
-      </c>
-      <c r="B232" s="10">
-        <v>100</v>
-      </c>
-      <c r="C232" s="10">
-        <v>0</v>
-      </c>
-      <c r="E232" s="12">
+        <v>10785</v>
+      </c>
+      <c r="F232" s="13">
         <f t="shared" si="22"/>
-        <v>15475</v>
-      </c>
-      <c r="F232" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
+        <f t="shared" si="20"/>
+        <v>232</v>
+      </c>
+      <c r="B233" s="10">
+        <v>100</v>
+      </c>
+      <c r="C233" s="10">
+        <v>0</v>
+      </c>
+      <c r="E233" s="12">
         <f t="shared" si="21"/>
-        <v>232</v>
-      </c>
-      <c r="B233" s="10">
-        <v>100</v>
-      </c>
-      <c r="C233" s="10">
-        <v>0</v>
-      </c>
-      <c r="E233" s="12">
+        <v>10885</v>
+      </c>
+      <c r="F233" s="13">
         <f t="shared" si="22"/>
-        <v>15575</v>
-      </c>
-      <c r="F233" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
+        <f t="shared" si="20"/>
+        <v>233</v>
+      </c>
+      <c r="B234" s="10">
+        <v>100</v>
+      </c>
+      <c r="C234" s="10">
+        <v>0</v>
+      </c>
+      <c r="E234" s="12">
         <f t="shared" si="21"/>
-        <v>233</v>
-      </c>
-      <c r="B234" s="10">
-        <v>100</v>
-      </c>
-      <c r="C234" s="10">
-        <v>0</v>
-      </c>
-      <c r="E234" s="12">
+        <v>10985</v>
+      </c>
+      <c r="F234" s="13">
         <f t="shared" si="22"/>
-        <v>15675</v>
-      </c>
-      <c r="F234" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
+        <f t="shared" si="20"/>
+        <v>234</v>
+      </c>
+      <c r="B235" s="10">
+        <v>100</v>
+      </c>
+      <c r="C235" s="10">
+        <v>0</v>
+      </c>
+      <c r="E235" s="12">
         <f t="shared" si="21"/>
-        <v>234</v>
-      </c>
-      <c r="B235" s="10">
-        <v>100</v>
-      </c>
-      <c r="C235" s="10">
-        <v>0</v>
-      </c>
-      <c r="E235" s="12">
+        <v>11085</v>
+      </c>
+      <c r="F235" s="13">
         <f t="shared" si="22"/>
-        <v>15775</v>
-      </c>
-      <c r="F235" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
+        <f t="shared" si="20"/>
+        <v>235</v>
+      </c>
+      <c r="B236" s="10">
+        <v>100</v>
+      </c>
+      <c r="C236" s="10">
+        <v>0</v>
+      </c>
+      <c r="E236" s="12">
         <f t="shared" si="21"/>
-        <v>235</v>
-      </c>
-      <c r="B236" s="10">
-        <v>100</v>
-      </c>
-      <c r="C236" s="10">
-        <v>0</v>
-      </c>
-      <c r="E236" s="12">
+        <v>11185</v>
+      </c>
+      <c r="F236" s="13">
         <f t="shared" si="22"/>
-        <v>15875</v>
-      </c>
-      <c r="F236" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
+        <f t="shared" si="20"/>
+        <v>236</v>
+      </c>
+      <c r="B237" s="10">
+        <v>100</v>
+      </c>
+      <c r="C237" s="10">
+        <v>0</v>
+      </c>
+      <c r="E237" s="12">
         <f t="shared" si="21"/>
-        <v>236</v>
-      </c>
-      <c r="B237" s="10">
-        <v>100</v>
-      </c>
-      <c r="C237" s="10">
-        <v>0</v>
-      </c>
-      <c r="E237" s="12">
+        <v>11285</v>
+      </c>
+      <c r="F237" s="13">
         <f t="shared" si="22"/>
-        <v>15975</v>
-      </c>
-      <c r="F237" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
+        <f t="shared" si="20"/>
+        <v>237</v>
+      </c>
+      <c r="B238" s="10">
+        <v>100</v>
+      </c>
+      <c r="C238" s="10">
+        <v>0</v>
+      </c>
+      <c r="E238" s="12">
         <f t="shared" si="21"/>
-        <v>237</v>
-      </c>
-      <c r="B238" s="10">
-        <v>100</v>
-      </c>
-      <c r="C238" s="10">
-        <v>0</v>
-      </c>
-      <c r="E238" s="12">
+        <v>11385</v>
+      </c>
+      <c r="F238" s="13">
         <f t="shared" si="22"/>
-        <v>16075</v>
-      </c>
-      <c r="F238" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
+        <f t="shared" si="20"/>
+        <v>238</v>
+      </c>
+      <c r="B239" s="10">
+        <v>100</v>
+      </c>
+      <c r="C239" s="10">
+        <v>0</v>
+      </c>
+      <c r="E239" s="12">
         <f t="shared" si="21"/>
-        <v>238</v>
-      </c>
-      <c r="B239" s="10">
-        <v>100</v>
-      </c>
-      <c r="C239" s="10">
-        <v>0</v>
-      </c>
-      <c r="E239" s="12">
+        <v>11485</v>
+      </c>
+      <c r="F239" s="13">
         <f t="shared" si="22"/>
-        <v>16175</v>
-      </c>
-      <c r="F239" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
+        <f t="shared" si="20"/>
+        <v>239</v>
+      </c>
+      <c r="B240" s="10">
+        <v>100</v>
+      </c>
+      <c r="C240" s="10">
+        <v>0</v>
+      </c>
+      <c r="E240" s="12">
         <f t="shared" si="21"/>
-        <v>239</v>
-      </c>
-      <c r="B240" s="10">
-        <v>100</v>
-      </c>
-      <c r="C240" s="10">
-        <v>0</v>
-      </c>
-      <c r="E240" s="12">
+        <v>11585</v>
+      </c>
+      <c r="F240" s="13">
         <f t="shared" si="22"/>
-        <v>16275</v>
-      </c>
-      <c r="F240" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
+        <f t="shared" si="20"/>
+        <v>240</v>
+      </c>
+      <c r="B241" s="10">
+        <v>100</v>
+      </c>
+      <c r="C241" s="10">
+        <v>0</v>
+      </c>
+      <c r="E241" s="12">
         <f t="shared" si="21"/>
-        <v>240</v>
-      </c>
-      <c r="B241" s="10">
-        <v>100</v>
-      </c>
-      <c r="C241" s="10">
-        <v>0</v>
-      </c>
-      <c r="E241" s="12">
+        <v>11685</v>
+      </c>
+      <c r="F241" s="13">
         <f t="shared" si="22"/>
-        <v>16375</v>
-      </c>
-      <c r="F241" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
+        <f t="shared" si="20"/>
+        <v>241</v>
+      </c>
+      <c r="B242" s="10">
+        <v>100</v>
+      </c>
+      <c r="C242" s="10">
+        <v>0</v>
+      </c>
+      <c r="E242" s="12">
         <f t="shared" si="21"/>
-        <v>241</v>
-      </c>
-      <c r="B242" s="10">
-        <v>100</v>
-      </c>
-      <c r="C242" s="10">
-        <v>0</v>
-      </c>
-      <c r="E242" s="12">
+        <v>11785</v>
+      </c>
+      <c r="F242" s="13">
         <f t="shared" si="22"/>
-        <v>16475</v>
-      </c>
-      <c r="F242" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
+        <f t="shared" si="20"/>
+        <v>242</v>
+      </c>
+      <c r="B243" s="10">
+        <v>100</v>
+      </c>
+      <c r="C243" s="10">
+        <v>0</v>
+      </c>
+      <c r="E243" s="12">
         <f t="shared" si="21"/>
-        <v>242</v>
-      </c>
-      <c r="B243" s="10">
-        <v>100</v>
-      </c>
-      <c r="C243" s="10">
-        <v>0</v>
-      </c>
-      <c r="E243" s="12">
+        <v>11885</v>
+      </c>
+      <c r="F243" s="13">
         <f t="shared" si="22"/>
-        <v>16575</v>
-      </c>
-      <c r="F243" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
+        <f t="shared" si="20"/>
+        <v>243</v>
+      </c>
+      <c r="B244" s="10">
+        <v>100</v>
+      </c>
+      <c r="C244" s="10">
+        <v>0</v>
+      </c>
+      <c r="E244" s="12">
         <f t="shared" si="21"/>
-        <v>243</v>
-      </c>
-      <c r="B244" s="10">
-        <v>100</v>
-      </c>
-      <c r="C244" s="10">
-        <v>0</v>
-      </c>
-      <c r="E244" s="12">
+        <v>11985</v>
+      </c>
+      <c r="F244" s="13">
         <f t="shared" si="22"/>
-        <v>16675</v>
-      </c>
-      <c r="F244" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
+        <f t="shared" si="20"/>
+        <v>244</v>
+      </c>
+      <c r="B245" s="10">
+        <v>100</v>
+      </c>
+      <c r="C245" s="10">
+        <v>0</v>
+      </c>
+      <c r="E245" s="12">
         <f t="shared" si="21"/>
-        <v>244</v>
-      </c>
-      <c r="B245" s="10">
-        <v>100</v>
-      </c>
-      <c r="C245" s="10">
-        <v>0</v>
-      </c>
-      <c r="E245" s="12">
+        <v>12085</v>
+      </c>
+      <c r="F245" s="13">
         <f t="shared" si="22"/>
-        <v>16775</v>
-      </c>
-      <c r="F245" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
+        <f t="shared" si="20"/>
+        <v>245</v>
+      </c>
+      <c r="B246" s="10">
+        <v>100</v>
+      </c>
+      <c r="C246" s="10">
+        <v>0</v>
+      </c>
+      <c r="E246" s="12">
         <f t="shared" si="21"/>
-        <v>245</v>
-      </c>
-      <c r="B246" s="10">
-        <v>100</v>
-      </c>
-      <c r="C246" s="10">
-        <v>0</v>
-      </c>
-      <c r="E246" s="12">
+        <v>12185</v>
+      </c>
+      <c r="F246" s="13">
         <f t="shared" si="22"/>
-        <v>16875</v>
-      </c>
-      <c r="F246" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
+        <f t="shared" si="20"/>
+        <v>246</v>
+      </c>
+      <c r="B247" s="10">
+        <v>100</v>
+      </c>
+      <c r="C247" s="10">
+        <v>0</v>
+      </c>
+      <c r="E247" s="12">
         <f t="shared" si="21"/>
-        <v>246</v>
-      </c>
-      <c r="B247" s="10">
-        <v>100</v>
-      </c>
-      <c r="C247" s="10">
-        <v>0</v>
-      </c>
-      <c r="E247" s="12">
+        <v>12285</v>
+      </c>
+      <c r="F247" s="13">
         <f t="shared" si="22"/>
-        <v>16975</v>
-      </c>
-      <c r="F247" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
+        <f t="shared" si="20"/>
+        <v>247</v>
+      </c>
+      <c r="B248" s="10">
+        <v>100</v>
+      </c>
+      <c r="C248" s="10">
+        <v>0</v>
+      </c>
+      <c r="E248" s="12">
         <f t="shared" si="21"/>
-        <v>247</v>
-      </c>
-      <c r="B248" s="10">
-        <v>100</v>
-      </c>
-      <c r="C248" s="10">
-        <v>0</v>
-      </c>
-      <c r="E248" s="12">
+        <v>12385</v>
+      </c>
+      <c r="F248" s="13">
         <f t="shared" si="22"/>
-        <v>17075</v>
-      </c>
-      <c r="F248" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
+        <f t="shared" si="20"/>
+        <v>248</v>
+      </c>
+      <c r="B249" s="10">
+        <v>100</v>
+      </c>
+      <c r="C249" s="10">
+        <v>0</v>
+      </c>
+      <c r="E249" s="12">
         <f t="shared" si="21"/>
-        <v>248</v>
-      </c>
-      <c r="B249" s="10">
-        <v>100</v>
-      </c>
-      <c r="C249" s="10">
-        <v>0</v>
-      </c>
-      <c r="E249" s="12">
+        <v>12485</v>
+      </c>
+      <c r="F249" s="13">
         <f t="shared" si="22"/>
-        <v>17175</v>
-      </c>
-      <c r="F249" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
+        <f t="shared" si="20"/>
+        <v>249</v>
+      </c>
+      <c r="B250" s="10">
+        <v>100</v>
+      </c>
+      <c r="C250" s="10">
+        <v>0</v>
+      </c>
+      <c r="E250" s="12">
         <f t="shared" si="21"/>
-        <v>249</v>
-      </c>
-      <c r="B250" s="10">
-        <v>100</v>
-      </c>
-      <c r="C250" s="10">
-        <v>0</v>
-      </c>
-      <c r="E250" s="12">
+        <v>12585</v>
+      </c>
+      <c r="F250" s="13">
         <f t="shared" si="22"/>
-        <v>17275</v>
-      </c>
-      <c r="F250" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
+        <f t="shared" si="20"/>
+        <v>250</v>
+      </c>
+      <c r="B251" s="10">
+        <v>100</v>
+      </c>
+      <c r="C251" s="10">
+        <v>0</v>
+      </c>
+      <c r="E251" s="12">
         <f t="shared" si="21"/>
-        <v>250</v>
-      </c>
-      <c r="B251" s="10">
-        <v>100</v>
-      </c>
-      <c r="C251" s="10">
-        <v>0</v>
-      </c>
-      <c r="E251" s="12">
+        <v>12685</v>
+      </c>
+      <c r="F251" s="13">
         <f t="shared" si="22"/>
-        <v>17375</v>
-      </c>
-      <c r="F251" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
+        <f t="shared" si="20"/>
+        <v>251</v>
+      </c>
+      <c r="B252" s="10">
+        <v>100</v>
+      </c>
+      <c r="C252" s="10">
+        <v>0</v>
+      </c>
+      <c r="E252" s="12">
         <f t="shared" si="21"/>
-        <v>251</v>
-      </c>
-      <c r="B252" s="10">
-        <v>100</v>
-      </c>
-      <c r="C252" s="10">
-        <v>0</v>
-      </c>
-      <c r="E252" s="12">
+        <v>12785</v>
+      </c>
+      <c r="F252" s="13">
         <f t="shared" si="22"/>
-        <v>17475</v>
-      </c>
-      <c r="F252" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
+        <f t="shared" si="20"/>
+        <v>252</v>
+      </c>
+      <c r="B253" s="10">
+        <v>100</v>
+      </c>
+      <c r="C253" s="10">
+        <v>0</v>
+      </c>
+      <c r="E253" s="12">
         <f t="shared" si="21"/>
-        <v>252</v>
-      </c>
-      <c r="B253" s="10">
-        <v>100</v>
-      </c>
-      <c r="C253" s="10">
-        <v>0</v>
-      </c>
-      <c r="E253" s="12">
+        <v>12885</v>
+      </c>
+      <c r="F253" s="13">
         <f t="shared" si="22"/>
-        <v>17575</v>
-      </c>
-      <c r="F253" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
+        <f t="shared" si="20"/>
+        <v>253</v>
+      </c>
+      <c r="B254" s="10">
+        <v>100</v>
+      </c>
+      <c r="C254" s="10">
+        <v>0</v>
+      </c>
+      <c r="E254" s="12">
         <f t="shared" si="21"/>
-        <v>253</v>
-      </c>
-      <c r="B254" s="10">
-        <v>100</v>
-      </c>
-      <c r="C254" s="10">
-        <v>0</v>
-      </c>
-      <c r="E254" s="12">
+        <v>12985</v>
+      </c>
+      <c r="F254" s="13">
         <f t="shared" si="22"/>
-        <v>17675</v>
-      </c>
-      <c r="F254" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
+        <f t="shared" si="20"/>
+        <v>254</v>
+      </c>
+      <c r="B255" s="10">
+        <v>100</v>
+      </c>
+      <c r="C255" s="10">
+        <v>0</v>
+      </c>
+      <c r="E255" s="12">
         <f t="shared" si="21"/>
-        <v>254</v>
-      </c>
-      <c r="B255" s="10">
-        <v>100</v>
-      </c>
-      <c r="C255" s="10">
-        <v>0</v>
-      </c>
-      <c r="E255" s="12">
+        <v>13085</v>
+      </c>
+      <c r="F255" s="13">
         <f t="shared" si="22"/>
-        <v>17775</v>
-      </c>
-      <c r="F255" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
+        <f t="shared" si="20"/>
+        <v>255</v>
+      </c>
+      <c r="B256" s="10">
+        <v>100</v>
+      </c>
+      <c r="C256" s="10">
+        <v>0</v>
+      </c>
+      <c r="E256" s="12">
         <f t="shared" si="21"/>
-        <v>255</v>
-      </c>
-      <c r="B256" s="10">
-        <v>100</v>
-      </c>
-      <c r="C256" s="10">
-        <v>0</v>
-      </c>
-      <c r="E256" s="12">
+        <v>13185</v>
+      </c>
+      <c r="F256" s="13">
         <f t="shared" si="22"/>
-        <v>17875</v>
-      </c>
-      <c r="F256" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
+        <f t="shared" si="20"/>
+        <v>256</v>
+      </c>
+      <c r="B257" s="10">
+        <v>100</v>
+      </c>
+      <c r="C257" s="10">
+        <v>0</v>
+      </c>
+      <c r="E257" s="12">
         <f t="shared" si="21"/>
-        <v>256</v>
-      </c>
-      <c r="B257" s="10">
-        <v>100</v>
-      </c>
-      <c r="C257" s="10">
-        <v>0</v>
-      </c>
-      <c r="E257" s="12">
+        <v>13285</v>
+      </c>
+      <c r="F257" s="13">
         <f t="shared" si="22"/>
-        <v>17975</v>
-      </c>
-      <c r="F257" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
+        <f t="shared" si="20"/>
+        <v>257</v>
+      </c>
+      <c r="B258" s="10">
+        <v>100</v>
+      </c>
+      <c r="C258" s="10">
+        <v>0</v>
+      </c>
+      <c r="E258" s="12">
         <f t="shared" si="21"/>
-        <v>257</v>
-      </c>
-      <c r="B258" s="10">
-        <v>100</v>
-      </c>
-      <c r="C258" s="10">
-        <v>0</v>
-      </c>
-      <c r="E258" s="12">
+        <v>13385</v>
+      </c>
+      <c r="F258" s="13">
         <f t="shared" si="22"/>
-        <v>18075</v>
-      </c>
-      <c r="F258" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
+        <f t="shared" si="20"/>
+        <v>258</v>
+      </c>
+      <c r="B259" s="10">
+        <v>100</v>
+      </c>
+      <c r="C259" s="10">
+        <v>0</v>
+      </c>
+      <c r="E259" s="12">
         <f t="shared" si="21"/>
-        <v>258</v>
-      </c>
-      <c r="B259" s="10">
-        <v>100</v>
-      </c>
-      <c r="C259" s="10">
-        <v>0</v>
-      </c>
-      <c r="E259" s="12">
+        <v>13485</v>
+      </c>
+      <c r="F259" s="13">
         <f t="shared" si="22"/>
-        <v>18175</v>
-      </c>
-      <c r="F259" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
+        <f t="shared" si="20"/>
+        <v>259</v>
+      </c>
+      <c r="B260" s="10">
+        <v>100</v>
+      </c>
+      <c r="C260" s="10">
+        <v>0</v>
+      </c>
+      <c r="E260" s="12">
         <f t="shared" si="21"/>
-        <v>259</v>
-      </c>
-      <c r="B260" s="10">
-        <v>100</v>
-      </c>
-      <c r="C260" s="10">
-        <v>0</v>
-      </c>
-      <c r="E260" s="12">
+        <v>13585</v>
+      </c>
+      <c r="F260" s="13">
         <f t="shared" si="22"/>
-        <v>18275</v>
-      </c>
-      <c r="F260" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
+        <f t="shared" si="20"/>
+        <v>260</v>
+      </c>
+      <c r="B261" s="10">
+        <v>100</v>
+      </c>
+      <c r="C261" s="10">
+        <v>0</v>
+      </c>
+      <c r="E261" s="12">
         <f t="shared" si="21"/>
-        <v>260</v>
-      </c>
-      <c r="B261" s="10">
-        <v>100</v>
-      </c>
-      <c r="C261" s="10">
-        <v>0</v>
-      </c>
-      <c r="E261" s="12">
+        <v>13685</v>
+      </c>
+      <c r="F261" s="13">
         <f t="shared" si="22"/>
-        <v>18375</v>
-      </c>
-      <c r="F261" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
+        <f t="shared" si="20"/>
+        <v>261</v>
+      </c>
+      <c r="B262" s="10">
+        <v>100</v>
+      </c>
+      <c r="C262" s="10">
+        <v>0</v>
+      </c>
+      <c r="E262" s="12">
         <f t="shared" si="21"/>
-        <v>261</v>
-      </c>
-      <c r="B262" s="10">
-        <v>100</v>
-      </c>
-      <c r="C262" s="10">
-        <v>0</v>
-      </c>
-      <c r="E262" s="12">
+        <v>13785</v>
+      </c>
+      <c r="F262" s="13">
         <f t="shared" si="22"/>
-        <v>18475</v>
-      </c>
-      <c r="F262" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
+        <f t="shared" si="20"/>
+        <v>262</v>
+      </c>
+      <c r="B263" s="10">
+        <v>100</v>
+      </c>
+      <c r="C263" s="10">
+        <v>0</v>
+      </c>
+      <c r="E263" s="12">
         <f t="shared" si="21"/>
-        <v>262</v>
-      </c>
-      <c r="B263" s="10">
-        <v>100</v>
-      </c>
-      <c r="C263" s="10">
-        <v>0</v>
-      </c>
-      <c r="E263" s="12">
+        <v>13885</v>
+      </c>
+      <c r="F263" s="13">
         <f t="shared" si="22"/>
-        <v>18575</v>
-      </c>
-      <c r="F263" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
+        <f t="shared" si="20"/>
+        <v>263</v>
+      </c>
+      <c r="B264" s="10">
+        <v>100</v>
+      </c>
+      <c r="C264" s="10">
+        <v>0</v>
+      </c>
+      <c r="E264" s="12">
         <f t="shared" si="21"/>
-        <v>263</v>
-      </c>
-      <c r="B264" s="10">
-        <v>100</v>
-      </c>
-      <c r="C264" s="10">
-        <v>0</v>
-      </c>
-      <c r="E264" s="12">
+        <v>13985</v>
+      </c>
+      <c r="F264" s="13">
         <f t="shared" si="22"/>
-        <v>18675</v>
-      </c>
-      <c r="F264" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
+        <f t="shared" si="20"/>
+        <v>264</v>
+      </c>
+      <c r="B265" s="10">
+        <v>100</v>
+      </c>
+      <c r="C265" s="10">
+        <v>0</v>
+      </c>
+      <c r="E265" s="12">
         <f t="shared" si="21"/>
-        <v>264</v>
-      </c>
-      <c r="B265" s="10">
-        <v>100</v>
-      </c>
-      <c r="C265" s="10">
-        <v>0</v>
-      </c>
-      <c r="E265" s="12">
+        <v>14085</v>
+      </c>
+      <c r="F265" s="13">
         <f t="shared" si="22"/>
-        <v>18775</v>
-      </c>
-      <c r="F265" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
+        <f t="shared" si="20"/>
+        <v>265</v>
+      </c>
+      <c r="B266" s="10">
+        <v>100</v>
+      </c>
+      <c r="C266" s="10">
+        <v>0</v>
+      </c>
+      <c r="E266" s="12">
         <f t="shared" si="21"/>
-        <v>265</v>
-      </c>
-      <c r="B266" s="10">
-        <v>100</v>
-      </c>
-      <c r="C266" s="10">
-        <v>0</v>
-      </c>
-      <c r="E266" s="12">
+        <v>14185</v>
+      </c>
+      <c r="F266" s="13">
         <f t="shared" si="22"/>
-        <v>18875</v>
-      </c>
-      <c r="F266" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
+        <f t="shared" si="20"/>
+        <v>266</v>
+      </c>
+      <c r="B267" s="10">
+        <v>100</v>
+      </c>
+      <c r="C267" s="10">
+        <v>0</v>
+      </c>
+      <c r="E267" s="12">
         <f t="shared" si="21"/>
-        <v>266</v>
-      </c>
-      <c r="B267" s="10">
-        <v>100</v>
-      </c>
-      <c r="C267" s="10">
-        <v>0</v>
-      </c>
-      <c r="E267" s="12">
+        <v>14285</v>
+      </c>
+      <c r="F267" s="13">
         <f t="shared" si="22"/>
-        <v>18975</v>
-      </c>
-      <c r="F267" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
+        <f t="shared" si="20"/>
+        <v>267</v>
+      </c>
+      <c r="B268" s="10">
+        <v>100</v>
+      </c>
+      <c r="C268" s="10">
+        <v>0</v>
+      </c>
+      <c r="E268" s="12">
         <f t="shared" si="21"/>
-        <v>267</v>
-      </c>
-      <c r="B268" s="10">
-        <v>100</v>
-      </c>
-      <c r="C268" s="10">
-        <v>0</v>
-      </c>
-      <c r="E268" s="12">
+        <v>14385</v>
+      </c>
+      <c r="F268" s="13">
         <f t="shared" si="22"/>
-        <v>19075</v>
-      </c>
-      <c r="F268" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
+        <f t="shared" si="20"/>
+        <v>268</v>
+      </c>
+      <c r="B269" s="10">
+        <v>100</v>
+      </c>
+      <c r="C269" s="10">
+        <v>0</v>
+      </c>
+      <c r="E269" s="12">
         <f t="shared" si="21"/>
-        <v>268</v>
-      </c>
-      <c r="B269" s="10">
-        <v>100</v>
-      </c>
-      <c r="C269" s="10">
-        <v>0</v>
-      </c>
-      <c r="E269" s="12">
+        <v>14485</v>
+      </c>
+      <c r="F269" s="13">
         <f t="shared" si="22"/>
-        <v>19175</v>
-      </c>
-      <c r="F269" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
+        <f t="shared" si="20"/>
+        <v>269</v>
+      </c>
+      <c r="B270" s="10">
+        <v>100</v>
+      </c>
+      <c r="C270" s="10">
+        <v>0</v>
+      </c>
+      <c r="E270" s="12">
         <f t="shared" si="21"/>
-        <v>269</v>
-      </c>
-      <c r="B270" s="10">
-        <v>100</v>
-      </c>
-      <c r="C270" s="10">
-        <v>0</v>
-      </c>
-      <c r="E270" s="12">
+        <v>14585</v>
+      </c>
+      <c r="F270" s="13">
         <f t="shared" si="22"/>
-        <v>19275</v>
-      </c>
-      <c r="F270" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
+        <f t="shared" si="20"/>
+        <v>270</v>
+      </c>
+      <c r="B271" s="10">
+        <v>100</v>
+      </c>
+      <c r="C271" s="10">
+        <v>0</v>
+      </c>
+      <c r="E271" s="12">
         <f t="shared" si="21"/>
-        <v>270</v>
-      </c>
-      <c r="B271" s="10">
-        <v>100</v>
-      </c>
-      <c r="C271" s="10">
-        <v>0</v>
-      </c>
-      <c r="E271" s="12">
+        <v>14685</v>
+      </c>
+      <c r="F271" s="13">
         <f t="shared" si="22"/>
-        <v>19375</v>
-      </c>
-      <c r="F271" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
+        <f t="shared" si="20"/>
+        <v>271</v>
+      </c>
+      <c r="B272" s="10">
+        <v>100</v>
+      </c>
+      <c r="C272" s="10">
+        <v>0</v>
+      </c>
+      <c r="E272" s="12">
         <f t="shared" si="21"/>
-        <v>271</v>
-      </c>
-      <c r="B272" s="10">
-        <v>100</v>
-      </c>
-      <c r="C272" s="10">
-        <v>0</v>
-      </c>
-      <c r="E272" s="12">
+        <v>14785</v>
+      </c>
+      <c r="F272" s="13">
         <f t="shared" si="22"/>
-        <v>19475</v>
-      </c>
-      <c r="F272" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
+        <f t="shared" si="20"/>
+        <v>272</v>
+      </c>
+      <c r="B273" s="10">
+        <v>100</v>
+      </c>
+      <c r="C273" s="10">
+        <v>0</v>
+      </c>
+      <c r="E273" s="12">
         <f t="shared" si="21"/>
-        <v>272</v>
-      </c>
-      <c r="B273" s="10">
-        <v>100</v>
-      </c>
-      <c r="C273" s="10">
-        <v>0</v>
-      </c>
-      <c r="E273" s="12">
+        <v>14885</v>
+      </c>
+      <c r="F273" s="13">
         <f t="shared" si="22"/>
-        <v>19575</v>
-      </c>
-      <c r="F273" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
+        <f t="shared" si="20"/>
+        <v>273</v>
+      </c>
+      <c r="B274" s="10">
+        <v>100</v>
+      </c>
+      <c r="C274" s="10">
+        <v>0</v>
+      </c>
+      <c r="E274" s="12">
         <f t="shared" si="21"/>
-        <v>273</v>
-      </c>
-      <c r="B274" s="10">
-        <v>100</v>
-      </c>
-      <c r="C274" s="10">
-        <v>0</v>
-      </c>
-      <c r="E274" s="12">
+        <v>14985</v>
+      </c>
+      <c r="F274" s="13">
         <f t="shared" si="22"/>
-        <v>19675</v>
-      </c>
-      <c r="F274" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
+        <f t="shared" si="20"/>
+        <v>274</v>
+      </c>
+      <c r="B275" s="10">
+        <v>100</v>
+      </c>
+      <c r="C275" s="10">
+        <v>0</v>
+      </c>
+      <c r="E275" s="12">
         <f t="shared" si="21"/>
-        <v>274</v>
-      </c>
-      <c r="B275" s="10">
-        <v>100</v>
-      </c>
-      <c r="C275" s="10">
-        <v>0</v>
-      </c>
-      <c r="E275" s="12">
+        <v>15085</v>
+      </c>
+      <c r="F275" s="13">
         <f t="shared" si="22"/>
-        <v>19775</v>
-      </c>
-      <c r="F275" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5">
+        <f t="shared" si="20"/>
+        <v>275</v>
+      </c>
+      <c r="B276" s="10">
+        <v>100</v>
+      </c>
+      <c r="C276" s="10">
+        <v>0</v>
+      </c>
+      <c r="E276" s="12">
         <f t="shared" si="21"/>
-        <v>275</v>
-      </c>
-      <c r="B276" s="10">
-        <v>100</v>
-      </c>
-      <c r="C276" s="10">
-        <v>0</v>
-      </c>
-      <c r="E276" s="12">
+        <v>15185</v>
+      </c>
+      <c r="F276" s="13">
         <f t="shared" si="22"/>
-        <v>19875</v>
-      </c>
-      <c r="F276" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
+        <f t="shared" si="20"/>
+        <v>276</v>
+      </c>
+      <c r="B277" s="10">
+        <v>100</v>
+      </c>
+      <c r="C277" s="10">
+        <v>0</v>
+      </c>
+      <c r="E277" s="12">
         <f t="shared" si="21"/>
-        <v>276</v>
-      </c>
-      <c r="B277" s="10">
-        <v>100</v>
-      </c>
-      <c r="C277" s="10">
-        <v>0</v>
-      </c>
-      <c r="E277" s="12">
+        <v>15285</v>
+      </c>
+      <c r="F277" s="13">
         <f t="shared" si="22"/>
-        <v>19975</v>
-      </c>
-      <c r="F277" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5">
+        <f t="shared" si="20"/>
+        <v>277</v>
+      </c>
+      <c r="B278" s="10">
+        <v>100</v>
+      </c>
+      <c r="C278" s="10">
+        <v>0</v>
+      </c>
+      <c r="E278" s="12">
         <f t="shared" si="21"/>
-        <v>277</v>
-      </c>
-      <c r="B278" s="10">
-        <v>100</v>
-      </c>
-      <c r="C278" s="10">
-        <v>0</v>
-      </c>
-      <c r="E278" s="12">
+        <v>15385</v>
+      </c>
+      <c r="F278" s="13">
         <f t="shared" si="22"/>
-        <v>20075</v>
-      </c>
-      <c r="F278" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
+        <f t="shared" si="20"/>
+        <v>278</v>
+      </c>
+      <c r="B279" s="10">
+        <v>100</v>
+      </c>
+      <c r="C279" s="10">
+        <v>0</v>
+      </c>
+      <c r="E279" s="12">
         <f t="shared" si="21"/>
-        <v>278</v>
-      </c>
-      <c r="B279" s="10">
-        <v>100</v>
-      </c>
-      <c r="C279" s="10">
-        <v>0</v>
-      </c>
-      <c r="E279" s="12">
+        <v>15485</v>
+      </c>
+      <c r="F279" s="13">
         <f t="shared" si="22"/>
-        <v>20175</v>
-      </c>
-      <c r="F279" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
+        <f t="shared" si="20"/>
+        <v>279</v>
+      </c>
+      <c r="B280" s="10">
+        <v>100</v>
+      </c>
+      <c r="C280" s="10">
+        <v>0</v>
+      </c>
+      <c r="E280" s="12">
         <f t="shared" si="21"/>
-        <v>279</v>
-      </c>
-      <c r="B280" s="10">
-        <v>100</v>
-      </c>
-      <c r="C280" s="10">
-        <v>0</v>
-      </c>
-      <c r="E280" s="12">
+        <v>15585</v>
+      </c>
+      <c r="F280" s="13">
         <f t="shared" si="22"/>
-        <v>20275</v>
-      </c>
-      <c r="F280" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
+        <f t="shared" si="20"/>
+        <v>280</v>
+      </c>
+      <c r="B281" s="10">
+        <v>100</v>
+      </c>
+      <c r="C281" s="10">
+        <v>0</v>
+      </c>
+      <c r="E281" s="12">
         <f t="shared" si="21"/>
-        <v>280</v>
-      </c>
-      <c r="B281" s="10">
-        <v>100</v>
-      </c>
-      <c r="C281" s="10">
-        <v>0</v>
-      </c>
-      <c r="E281" s="12">
+        <v>15685</v>
+      </c>
+      <c r="F281" s="13">
         <f t="shared" si="22"/>
-        <v>20375</v>
-      </c>
-      <c r="F281" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
+        <f t="shared" si="20"/>
+        <v>281</v>
+      </c>
+      <c r="B282" s="10">
+        <v>100</v>
+      </c>
+      <c r="C282" s="10">
+        <v>0</v>
+      </c>
+      <c r="E282" s="12">
         <f t="shared" si="21"/>
-        <v>281</v>
-      </c>
-      <c r="B282" s="10">
-        <v>100</v>
-      </c>
-      <c r="C282" s="10">
-        <v>0</v>
-      </c>
-      <c r="E282" s="12">
+        <v>15785</v>
+      </c>
+      <c r="F282" s="13">
         <f t="shared" si="22"/>
-        <v>20475</v>
-      </c>
-      <c r="F282" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
+        <f t="shared" si="20"/>
+        <v>282</v>
+      </c>
+      <c r="B283" s="10">
+        <v>100</v>
+      </c>
+      <c r="C283" s="10">
+        <v>0</v>
+      </c>
+      <c r="E283" s="12">
         <f t="shared" si="21"/>
-        <v>282</v>
-      </c>
-      <c r="B283" s="10">
-        <v>100</v>
-      </c>
-      <c r="C283" s="10">
-        <v>0</v>
-      </c>
-      <c r="E283" s="12">
+        <v>15885</v>
+      </c>
+      <c r="F283" s="13">
         <f t="shared" si="22"/>
-        <v>20575</v>
-      </c>
-      <c r="F283" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
+        <f t="shared" si="20"/>
+        <v>283</v>
+      </c>
+      <c r="B284" s="10">
+        <v>100</v>
+      </c>
+      <c r="C284" s="10">
+        <v>0</v>
+      </c>
+      <c r="E284" s="12">
         <f t="shared" si="21"/>
-        <v>283</v>
-      </c>
-      <c r="B284" s="10">
-        <v>100</v>
-      </c>
-      <c r="C284" s="10">
-        <v>0</v>
-      </c>
-      <c r="E284" s="12">
+        <v>15985</v>
+      </c>
+      <c r="F284" s="13">
         <f t="shared" si="22"/>
-        <v>20675</v>
-      </c>
-      <c r="F284" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
+        <f t="shared" si="20"/>
+        <v>284</v>
+      </c>
+      <c r="B285" s="10">
+        <v>100</v>
+      </c>
+      <c r="C285" s="10">
+        <v>0</v>
+      </c>
+      <c r="E285" s="12">
         <f t="shared" si="21"/>
-        <v>284</v>
-      </c>
-      <c r="B285" s="10">
-        <v>100</v>
-      </c>
-      <c r="C285" s="10">
-        <v>0</v>
-      </c>
-      <c r="E285" s="12">
+        <v>16085</v>
+      </c>
+      <c r="F285" s="13">
         <f t="shared" si="22"/>
-        <v>20775</v>
-      </c>
-      <c r="F285" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
-        <f t="shared" ref="A286:A305" si="24">A285+1</f>
+        <f t="shared" ref="A286:B301" si="23">A285+1</f>
         <v>285</v>
       </c>
       <c r="B286" s="10">
@@ -6379,17 +6500,17 @@
         <v>0</v>
       </c>
       <c r="E286" s="12">
+        <f t="shared" si="21"/>
+        <v>16185</v>
+      </c>
+      <c r="F286" s="13">
         <f t="shared" si="22"/>
-        <v>20875</v>
-      </c>
-      <c r="F286" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>286</v>
       </c>
       <c r="B287" s="10">
@@ -6399,17 +6520,17 @@
         <v>0</v>
       </c>
       <c r="E287" s="12">
+        <f t="shared" si="21"/>
+        <v>16285</v>
+      </c>
+      <c r="F287" s="13">
         <f t="shared" si="22"/>
-        <v>20975</v>
-      </c>
-      <c r="F287" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>287</v>
       </c>
       <c r="B288" s="10">
@@ -6419,17 +6540,17 @@
         <v>0</v>
       </c>
       <c r="E288" s="12">
+        <f t="shared" si="21"/>
+        <v>16385</v>
+      </c>
+      <c r="F288" s="13">
         <f t="shared" si="22"/>
-        <v>21075</v>
-      </c>
-      <c r="F288" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>288</v>
       </c>
       <c r="B289" s="10">
@@ -6439,17 +6560,17 @@
         <v>0</v>
       </c>
       <c r="E289" s="12">
+        <f t="shared" si="21"/>
+        <v>16485</v>
+      </c>
+      <c r="F289" s="13">
         <f t="shared" si="22"/>
-        <v>21175</v>
-      </c>
-      <c r="F289" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>289</v>
       </c>
       <c r="B290" s="10">
@@ -6459,17 +6580,17 @@
         <v>0</v>
       </c>
       <c r="E290" s="12">
+        <f t="shared" si="21"/>
+        <v>16585</v>
+      </c>
+      <c r="F290" s="13">
         <f t="shared" si="22"/>
-        <v>21275</v>
-      </c>
-      <c r="F290" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>290</v>
       </c>
       <c r="B291" s="10">
@@ -6479,17 +6600,17 @@
         <v>0</v>
       </c>
       <c r="E291" s="12">
+        <f t="shared" si="21"/>
+        <v>16685</v>
+      </c>
+      <c r="F291" s="13">
         <f t="shared" si="22"/>
-        <v>21375</v>
-      </c>
-      <c r="F291" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>291</v>
       </c>
       <c r="B292" s="10">
@@ -6499,17 +6620,17 @@
         <v>0</v>
       </c>
       <c r="E292" s="12">
+        <f t="shared" si="21"/>
+        <v>16785</v>
+      </c>
+      <c r="F292" s="13">
         <f t="shared" si="22"/>
-        <v>21475</v>
-      </c>
-      <c r="F292" s="13">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>292</v>
       </c>
       <c r="B293" s="10">
@@ -6519,171 +6640,171 @@
         <v>0</v>
       </c>
       <c r="E293" s="12">
-        <f t="shared" ref="E293:E305" si="25">E292+B293</f>
-        <v>21575</v>
+        <f t="shared" ref="E293:E301" si="24">E292+B293</f>
+        <v>16885</v>
       </c>
       <c r="F293" s="13">
-        <f t="shared" ref="F293:F305" si="26">B293-B292</f>
+        <f t="shared" ref="F293:F301" si="25">B293-B292</f>
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
+        <f t="shared" si="23"/>
+        <v>293</v>
+      </c>
+      <c r="B294" s="10">
+        <v>100</v>
+      </c>
+      <c r="C294" s="10">
+        <v>0</v>
+      </c>
+      <c r="E294" s="12">
         <f t="shared" si="24"/>
-        <v>293</v>
-      </c>
-      <c r="B294" s="10">
-        <v>100</v>
-      </c>
-      <c r="C294" s="10">
-        <v>0</v>
-      </c>
-      <c r="E294" s="12">
+        <v>16985</v>
+      </c>
+      <c r="F294" s="13">
         <f t="shared" si="25"/>
-        <v>21675</v>
-      </c>
-      <c r="F294" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="5">
+        <f t="shared" si="23"/>
+        <v>294</v>
+      </c>
+      <c r="B295" s="10">
+        <v>100</v>
+      </c>
+      <c r="C295" s="10">
+        <v>0</v>
+      </c>
+      <c r="E295" s="12">
         <f t="shared" si="24"/>
-        <v>294</v>
-      </c>
-      <c r="B295" s="10">
-        <v>100</v>
-      </c>
-      <c r="C295" s="10">
-        <v>0</v>
-      </c>
-      <c r="E295" s="12">
+        <v>17085</v>
+      </c>
+      <c r="F295" s="13">
         <f t="shared" si="25"/>
-        <v>21775</v>
-      </c>
-      <c r="F295" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
+        <f t="shared" si="23"/>
+        <v>295</v>
+      </c>
+      <c r="B296" s="10">
+        <v>100</v>
+      </c>
+      <c r="C296" s="10">
+        <v>0</v>
+      </c>
+      <c r="E296" s="12">
         <f t="shared" si="24"/>
-        <v>295</v>
-      </c>
-      <c r="B296" s="10">
-        <v>100</v>
-      </c>
-      <c r="C296" s="10">
-        <v>0</v>
-      </c>
-      <c r="E296" s="12">
+        <v>17185</v>
+      </c>
+      <c r="F296" s="13">
         <f t="shared" si="25"/>
-        <v>21875</v>
-      </c>
-      <c r="F296" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="5">
+        <f t="shared" si="23"/>
+        <v>296</v>
+      </c>
+      <c r="B297" s="10">
+        <v>100</v>
+      </c>
+      <c r="C297" s="10">
+        <v>0</v>
+      </c>
+      <c r="E297" s="12">
         <f t="shared" si="24"/>
-        <v>296</v>
-      </c>
-      <c r="B297" s="10">
-        <v>100</v>
-      </c>
-      <c r="C297" s="10">
-        <v>0</v>
-      </c>
-      <c r="E297" s="12">
+        <v>17285</v>
+      </c>
+      <c r="F297" s="13">
         <f t="shared" si="25"/>
-        <v>21975</v>
-      </c>
-      <c r="F297" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
+        <f t="shared" si="23"/>
+        <v>297</v>
+      </c>
+      <c r="B298" s="10">
+        <v>100</v>
+      </c>
+      <c r="C298" s="10">
+        <v>0</v>
+      </c>
+      <c r="E298" s="12">
         <f t="shared" si="24"/>
-        <v>297</v>
-      </c>
-      <c r="B298" s="10">
-        <v>100</v>
-      </c>
-      <c r="C298" s="10">
-        <v>0</v>
-      </c>
-      <c r="E298" s="12">
+        <v>17385</v>
+      </c>
+      <c r="F298" s="13">
         <f t="shared" si="25"/>
-        <v>22075</v>
-      </c>
-      <c r="F298" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="5">
+        <f t="shared" si="23"/>
+        <v>298</v>
+      </c>
+      <c r="B299" s="10">
+        <v>100</v>
+      </c>
+      <c r="C299" s="10">
+        <v>0</v>
+      </c>
+      <c r="E299" s="12">
         <f t="shared" si="24"/>
-        <v>298</v>
-      </c>
-      <c r="B299" s="10">
-        <v>100</v>
-      </c>
-      <c r="C299" s="10">
-        <v>0</v>
-      </c>
-      <c r="E299" s="12">
+        <v>17485</v>
+      </c>
+      <c r="F299" s="13">
         <f t="shared" si="25"/>
-        <v>22175</v>
-      </c>
-      <c r="F299" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
+        <f t="shared" si="23"/>
+        <v>299</v>
+      </c>
+      <c r="B300" s="10">
+        <v>100</v>
+      </c>
+      <c r="C300" s="10">
+        <v>0</v>
+      </c>
+      <c r="E300" s="12">
         <f t="shared" si="24"/>
-        <v>299</v>
-      </c>
-      <c r="B300" s="10">
-        <v>100</v>
-      </c>
-      <c r="C300" s="10">
-        <v>0</v>
-      </c>
-      <c r="E300" s="12">
+        <v>17585</v>
+      </c>
+      <c r="F300" s="13">
         <f t="shared" si="25"/>
-        <v>22275</v>
-      </c>
-      <c r="F300" s="13">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="5">
+        <f t="shared" si="23"/>
+        <v>300</v>
+      </c>
+      <c r="B301" s="4">
+        <v>-1</v>
+      </c>
+      <c r="C301" s="10">
+        <v>0</v>
+      </c>
+      <c r="E301" s="12">
         <f t="shared" si="24"/>
-        <v>300</v>
-      </c>
-      <c r="B301" s="15">
-        <v>-1</v>
-      </c>
-      <c r="C301" s="10">
-        <v>0</v>
-      </c>
-      <c r="E301" s="12">
+        <v>17584</v>
+      </c>
+      <c r="F301" s="7">
         <f t="shared" si="25"/>
-        <v>22274</v>
-      </c>
-      <c r="F301" s="16">
-        <f t="shared" si="26"/>
         <v>-101</v>
       </c>
     </row>
@@ -6709,7 +6830,40 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E301">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{85758CF9-4AF1-483A-978B-C6FE5D6837D7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{85758CF9-4AF1-483A-978B-C6FE5D6837D7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E2:E301</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Assets/AddressableResource/Data/Excels/LevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/LevelData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF238E6-922D-4C43-90FE-F9648A52A5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E04EA6D-B855-4EF1-937D-E76E9650A927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,11 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>level</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,14 +115,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.249977111117893"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -179,15 +167,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -201,9 +186,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -528,6305 +510,6297 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:XFA305"/>
+  <dimension ref="A1:K305"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.875" style="6" customWidth="1"/>
-    <col min="2" max="3" width="18.875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="19" style="10" customWidth="1"/>
-    <col min="5" max="5" width="19" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="4" customWidth="1"/>
-    <col min="7" max="10" width="17.625" style="4"/>
-    <col min="11" max="11" width="11.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.625" style="4"/>
-    <col min="17" max="16380" width="17.625" style="4"/>
-    <col min="16381" max="16381" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16382" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="18.875" style="5" customWidth="1"/>
+    <col min="2" max="3" width="18.875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="19" style="8" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.375" style="3" customWidth="1"/>
+    <col min="7" max="10" width="17.625" style="3"/>
+    <col min="11" max="11" width="11.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="17.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
         <v>2</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="XFA1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10">
-        <v>2</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="C2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9">
         <f>B2</f>
         <v>2</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="F2" s="6"/>
+      <c r="G2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="12">
+      <c r="C3" s="8">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
         <f>E2+B3</f>
         <v>4</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="11">
         <f>B3-B2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <f t="shared" ref="A4:B67" si="0">A3+1</f>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="12">
+      <c r="C4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
         <f t="shared" ref="E4:E67" si="1">E3+B4</f>
         <v>6</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <f t="shared" ref="F4:F67" si="2">B4-B3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>2</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="C5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>2</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>4</v>
+      <c r="G6" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="8">
         <f>B2+1</f>
         <v>3</v>
       </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12">
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="8">
         <f t="shared" ref="B8:B35" si="3">B3+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12">
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="C10" s="10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="C10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <v>3</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="10">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="G11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
+      <c r="C12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C14" s="10">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="8">
         <v>4</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="10">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11 16381:16381" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="C16" s="10">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C17" s="10">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12">
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C18" s="10">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="C18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10">
         <f>E17+B18</f>
         <v>55</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C19" s="10">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12">
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
         <f t="shared" ref="E19:E34" si="4">E18+B18</f>
         <v>60</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C20" s="10">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="C20" s="8">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="8">
         <v>5</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="10">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>7</v>
+      <c r="G21" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C22" s="10">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12">
+      <c r="C22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="8">
         <v>6</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="10">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>8</v>
+      <c r="G23" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C24" s="10">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12">
+      <c r="C24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10">
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="8">
         <v>7</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="10">
         <f t="shared" si="4"/>
         <v>93</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>9</v>
+      <c r="G25" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="8">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="C26" s="10">
-        <v>0</v>
-      </c>
-      <c r="E26" s="12">
+      <c r="C26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
         <f t="shared" si="4"/>
         <v>99</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="8">
         <v>8</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="10">
         <f t="shared" si="4"/>
         <v>105</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>10</v>
+      <c r="G27" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C28" s="10">
-        <v>0</v>
-      </c>
-      <c r="E28" s="12">
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10">
         <f t="shared" si="4"/>
         <v>112</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C29" s="10">
-        <v>0</v>
-      </c>
-      <c r="E29" s="12">
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C30" s="10">
-        <v>0</v>
-      </c>
-      <c r="E30" s="12">
+      <c r="C30" s="8">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
         <f t="shared" si="4"/>
         <v>126</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="C31" s="10">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12">
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10">
         <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="C32" s="10">
-        <v>0</v>
-      </c>
-      <c r="E32" s="12">
+      <c r="C32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10">
         <f t="shared" si="4"/>
         <v>140</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="C33" s="10">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12">
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10">
         <f t="shared" si="4"/>
         <v>148</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="C34" s="10">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12">
+      <c r="C34" s="8">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10">
         <f t="shared" si="4"/>
         <v>156</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="C35" s="10">
-        <v>0</v>
-      </c>
-      <c r="E35" s="12">
+      <c r="C35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10">
         <f t="shared" si="1"/>
         <v>164</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="8">
         <f>B32+1</f>
         <v>9</v>
       </c>
-      <c r="C36" s="10">
-        <v>0</v>
-      </c>
-      <c r="E36" s="12">
+      <c r="C36" s="8">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="8">
         <f t="shared" ref="B37:B42" si="5">B33+1</f>
         <v>9</v>
       </c>
-      <c r="C37" s="10">
-        <v>0</v>
-      </c>
-      <c r="E37" s="12">
+      <c r="C37" s="8">
+        <v>0</v>
+      </c>
+      <c r="E37" s="10">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="8">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="C38" s="10">
-        <v>0</v>
-      </c>
-      <c r="E38" s="12">
+      <c r="C38" s="8">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="8">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="C39" s="10">
-        <v>0</v>
-      </c>
-      <c r="E39" s="12">
+      <c r="C39" s="8">
+        <v>0</v>
+      </c>
+      <c r="E39" s="10">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="8">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="C40" s="10">
-        <v>0</v>
-      </c>
-      <c r="E40" s="12">
+      <c r="C40" s="8">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="8">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="C41" s="10">
-        <v>0</v>
-      </c>
-      <c r="E41" s="12">
+      <c r="C41" s="8">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10">
         <f t="shared" si="1"/>
         <v>220</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="8">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="C42" s="10">
-        <v>0</v>
-      </c>
-      <c r="E42" s="12">
+      <c r="C42" s="8">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="8">
         <f>B40+1</f>
         <v>11</v>
       </c>
-      <c r="C43" s="10">
-        <v>0</v>
-      </c>
-      <c r="E43" s="12">
+      <c r="C43" s="8">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10">
         <f t="shared" si="1"/>
         <v>241</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="10">
-        <f t="shared" ref="B44:B107" si="6">B41+1</f>
+      <c r="B44" s="8">
+        <f t="shared" ref="B44:B59" si="6">B41+1</f>
         <v>11</v>
       </c>
-      <c r="C44" s="10">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12">
+      <c r="C44" s="8">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10">
         <f t="shared" si="1"/>
         <v>252</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="8">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C45" s="10">
-        <v>0</v>
-      </c>
-      <c r="E45" s="12">
+      <c r="C45" s="8">
+        <v>0</v>
+      </c>
+      <c r="E45" s="10">
         <f t="shared" si="1"/>
         <v>263</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="8">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C46" s="10">
-        <v>0</v>
-      </c>
-      <c r="E46" s="12">
+      <c r="C46" s="8">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10">
         <f t="shared" si="1"/>
         <v>275</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="8">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C47" s="10">
-        <v>0</v>
-      </c>
-      <c r="E47" s="12">
+      <c r="C47" s="8">
+        <v>0</v>
+      </c>
+      <c r="E47" s="10">
         <f t="shared" si="1"/>
         <v>287</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="8">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C48" s="10">
-        <v>0</v>
-      </c>
-      <c r="E48" s="12">
+      <c r="C48" s="8">
+        <v>0</v>
+      </c>
+      <c r="E48" s="10">
         <f t="shared" si="1"/>
         <v>299</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="8">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C49" s="10">
-        <v>0</v>
-      </c>
-      <c r="E49" s="12">
+      <c r="C49" s="8">
+        <v>0</v>
+      </c>
+      <c r="E49" s="10">
         <f t="shared" si="1"/>
         <v>312</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="8">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C50" s="10">
-        <v>0</v>
-      </c>
-      <c r="E50" s="12">
+      <c r="C50" s="8">
+        <v>0</v>
+      </c>
+      <c r="E50" s="10">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="8">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C51" s="10">
-        <v>0</v>
-      </c>
-      <c r="E51" s="12">
+      <c r="C51" s="8">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10">
         <f t="shared" si="1"/>
         <v>338</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="8">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C52" s="10">
-        <v>0</v>
-      </c>
-      <c r="E52" s="12">
+      <c r="C52" s="8">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10">
         <f t="shared" si="1"/>
         <v>352</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="8">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C53" s="10">
-        <v>0</v>
-      </c>
-      <c r="E53" s="12">
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10">
         <f t="shared" si="1"/>
         <v>366</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="8">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C54" s="10">
-        <v>0</v>
-      </c>
-      <c r="E54" s="12">
+      <c r="C54" s="8">
+        <v>0</v>
+      </c>
+      <c r="E54" s="10">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C55" s="10">
-        <v>0</v>
-      </c>
-      <c r="E55" s="12">
+      <c r="C55" s="8">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10">
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C56" s="10">
-        <v>0</v>
-      </c>
-      <c r="E56" s="12">
+      <c r="C56" s="8">
+        <v>0</v>
+      </c>
+      <c r="E56" s="10">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="8">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C57" s="10">
-        <v>0</v>
-      </c>
-      <c r="E57" s="12">
+      <c r="C57" s="8">
+        <v>0</v>
+      </c>
+      <c r="E57" s="10">
         <f t="shared" si="1"/>
         <v>425</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="8">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C58" s="10">
-        <v>0</v>
-      </c>
-      <c r="E58" s="12">
+      <c r="C58" s="8">
+        <v>0</v>
+      </c>
+      <c r="E58" s="10">
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="8">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C59" s="10">
-        <v>0</v>
-      </c>
-      <c r="E59" s="12">
+      <c r="C59" s="8">
+        <v>0</v>
+      </c>
+      <c r="E59" s="10">
         <f t="shared" si="1"/>
         <v>457</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="8">
         <f>B58+1</f>
         <v>17</v>
       </c>
-      <c r="C60" s="10">
-        <v>0</v>
-      </c>
-      <c r="E60" s="12">
+      <c r="C60" s="8">
+        <v>0</v>
+      </c>
+      <c r="E60" s="10">
         <f t="shared" si="1"/>
         <v>474</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="8">
         <f t="shared" ref="B61:B124" si="7">B59+1</f>
         <v>17</v>
       </c>
-      <c r="C61" s="10">
-        <v>0</v>
-      </c>
-      <c r="E61" s="12">
+      <c r="C61" s="8">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10">
         <f t="shared" si="1"/>
         <v>491</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="8">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="C62" s="10">
-        <v>0</v>
-      </c>
-      <c r="E62" s="12">
+      <c r="C62" s="8">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10">
         <f t="shared" si="1"/>
         <v>509</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="8">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="C63" s="10">
-        <v>0</v>
-      </c>
-      <c r="E63" s="12">
+      <c r="C63" s="8">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10">
         <f t="shared" si="1"/>
         <v>527</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="8">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="C64" s="10">
-        <v>0</v>
-      </c>
-      <c r="E64" s="12">
+      <c r="C64" s="8">
+        <v>0</v>
+      </c>
+      <c r="E64" s="10">
         <f t="shared" si="1"/>
         <v>546</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="8">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="C65" s="10">
-        <v>0</v>
-      </c>
-      <c r="E65" s="12">
+      <c r="C65" s="8">
+        <v>0</v>
+      </c>
+      <c r="E65" s="10">
         <f t="shared" si="1"/>
         <v>565</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="8">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="C66" s="10">
-        <v>0</v>
-      </c>
-      <c r="E66" s="12">
+      <c r="C66" s="8">
+        <v>0</v>
+      </c>
+      <c r="E66" s="10">
         <f t="shared" si="1"/>
         <v>585</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="8">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="C67" s="10">
-        <v>0</v>
-      </c>
-      <c r="E67" s="12">
+      <c r="C67" s="8">
+        <v>0</v>
+      </c>
+      <c r="E67" s="10">
         <f t="shared" si="1"/>
         <v>605</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="5">
-        <f t="shared" ref="A68:B73" si="8">A67+1</f>
+      <c r="A68" s="4">
+        <f t="shared" ref="A68:A73" si="8">A67+1</f>
         <v>67</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="8">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="C68" s="10">
-        <v>0</v>
-      </c>
-      <c r="E68" s="12">
+      <c r="C68" s="8">
+        <v>0</v>
+      </c>
+      <c r="E68" s="10">
         <f t="shared" ref="E68:E100" si="9">E67+B68</f>
         <v>626</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="11">
         <f t="shared" ref="F68:F100" si="10">B68-B67</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <f t="shared" si="8"/>
         <v>68</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="8">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="C69" s="10">
-        <v>0</v>
-      </c>
-      <c r="E69" s="12">
+      <c r="C69" s="8">
+        <v>0</v>
+      </c>
+      <c r="E69" s="10">
         <f t="shared" si="9"/>
         <v>647</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <f t="shared" si="8"/>
         <v>69</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="8">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="C70" s="10">
-        <v>0</v>
-      </c>
-      <c r="E70" s="12">
+      <c r="C70" s="8">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10">
         <f t="shared" si="9"/>
         <v>669</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <f t="shared" si="8"/>
         <v>70</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="8">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-      <c r="C71" s="10">
-        <v>0</v>
-      </c>
-      <c r="E71" s="12">
+      <c r="C71" s="8">
+        <v>0</v>
+      </c>
+      <c r="E71" s="10">
         <f t="shared" si="9"/>
         <v>691</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <f t="shared" si="8"/>
         <v>71</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="8">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="C72" s="10">
-        <v>0</v>
-      </c>
-      <c r="E72" s="12">
+      <c r="C72" s="8">
+        <v>0</v>
+      </c>
+      <c r="E72" s="10">
         <f t="shared" si="9"/>
         <v>714</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <f t="shared" si="8"/>
         <v>72</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="8">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
-      <c r="C73" s="10">
-        <v>0</v>
-      </c>
-      <c r="E73" s="12">
+      <c r="C73" s="8">
+        <v>0</v>
+      </c>
+      <c r="E73" s="10">
         <f t="shared" si="9"/>
         <v>737</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="5">
-        <f t="shared" ref="A74:B93" si="11">A73+1</f>
+      <c r="A74" s="4">
+        <f t="shared" ref="A74:A93" si="11">A73+1</f>
         <v>73</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="8">
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="C74" s="10">
-        <v>0</v>
-      </c>
-      <c r="E74" s="12">
+      <c r="C74" s="8">
+        <v>0</v>
+      </c>
+      <c r="E74" s="10">
         <f t="shared" si="9"/>
         <v>761</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="5">
+      <c r="A75" s="4">
         <f t="shared" si="11"/>
         <v>74</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="8">
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="C75" s="10">
-        <v>0</v>
-      </c>
-      <c r="E75" s="12">
+      <c r="C75" s="8">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10">
         <f t="shared" si="9"/>
         <v>785</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <f t="shared" si="11"/>
         <v>75</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="8">
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="C76" s="10">
-        <v>0</v>
-      </c>
-      <c r="E76" s="12">
+      <c r="C76" s="8">
+        <v>0</v>
+      </c>
+      <c r="E76" s="10">
         <f t="shared" si="9"/>
         <v>810</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <f t="shared" si="11"/>
         <v>76</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="8">
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="C77" s="10">
-        <v>0</v>
-      </c>
-      <c r="E77" s="12">
+      <c r="C77" s="8">
+        <v>0</v>
+      </c>
+      <c r="E77" s="10">
         <f t="shared" si="9"/>
         <v>835</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <f t="shared" si="11"/>
         <v>77</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="8">
         <f t="shared" si="7"/>
         <v>26</v>
       </c>
-      <c r="C78" s="10">
-        <v>0</v>
-      </c>
-      <c r="E78" s="12">
+      <c r="C78" s="8">
+        <v>0</v>
+      </c>
+      <c r="E78" s="10">
         <f t="shared" si="9"/>
         <v>861</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="5">
+      <c r="A79" s="4">
         <f t="shared" si="11"/>
         <v>78</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="8">
         <f t="shared" si="7"/>
         <v>26</v>
       </c>
-      <c r="C79" s="10">
-        <v>0</v>
-      </c>
-      <c r="E79" s="12">
+      <c r="C79" s="8">
+        <v>0</v>
+      </c>
+      <c r="E79" s="10">
         <f t="shared" si="9"/>
         <v>887</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="5">
+      <c r="A80" s="4">
         <f t="shared" si="11"/>
         <v>79</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="8">
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="C80" s="10">
-        <v>0</v>
-      </c>
-      <c r="E80" s="12">
+      <c r="C80" s="8">
+        <v>0</v>
+      </c>
+      <c r="E80" s="10">
         <f t="shared" si="9"/>
         <v>914</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="5">
+      <c r="A81" s="4">
         <f t="shared" si="11"/>
         <v>80</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="8">
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="C81" s="10">
-        <v>0</v>
-      </c>
-      <c r="E81" s="12">
+      <c r="C81" s="8">
+        <v>0</v>
+      </c>
+      <c r="E81" s="10">
         <f t="shared" si="9"/>
         <v>941</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="5">
+      <c r="A82" s="4">
         <f t="shared" si="11"/>
         <v>81</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="8">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="C82" s="10">
-        <v>0</v>
-      </c>
-      <c r="E82" s="12">
+      <c r="C82" s="8">
+        <v>0</v>
+      </c>
+      <c r="E82" s="10">
         <f t="shared" si="9"/>
         <v>969</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="5">
+      <c r="A83" s="4">
         <f t="shared" si="11"/>
         <v>82</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="8">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="C83" s="10">
-        <v>0</v>
-      </c>
-      <c r="E83" s="12">
+      <c r="C83" s="8">
+        <v>0</v>
+      </c>
+      <c r="E83" s="10">
         <f t="shared" si="9"/>
         <v>997</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <f t="shared" si="11"/>
         <v>83</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="8">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="C84" s="10">
-        <v>0</v>
-      </c>
-      <c r="E84" s="12">
+      <c r="C84" s="8">
+        <v>0</v>
+      </c>
+      <c r="E84" s="10">
         <f t="shared" si="9"/>
         <v>1026</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <f t="shared" si="11"/>
         <v>84</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="8">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="C85" s="10">
-        <v>0</v>
-      </c>
-      <c r="E85" s="12">
+      <c r="C85" s="8">
+        <v>0</v>
+      </c>
+      <c r="E85" s="10">
         <f t="shared" si="9"/>
         <v>1055</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <f t="shared" si="11"/>
         <v>85</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="C86" s="10">
-        <v>0</v>
-      </c>
-      <c r="E86" s="12">
+      <c r="C86" s="8">
+        <v>0</v>
+      </c>
+      <c r="E86" s="10">
         <f t="shared" si="9"/>
         <v>1085</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <f t="shared" si="11"/>
         <v>86</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="C87" s="10">
-        <v>0</v>
-      </c>
-      <c r="E87" s="12">
+      <c r="C87" s="8">
+        <v>0</v>
+      </c>
+      <c r="E87" s="10">
         <f t="shared" si="9"/>
         <v>1115</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <f t="shared" si="11"/>
         <v>87</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
-      <c r="C88" s="10">
-        <v>0</v>
-      </c>
-      <c r="E88" s="12">
+      <c r="C88" s="8">
+        <v>0</v>
+      </c>
+      <c r="E88" s="10">
         <f t="shared" si="9"/>
         <v>1146</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <f t="shared" si="11"/>
         <v>88</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
-      <c r="C89" s="10">
-        <v>0</v>
-      </c>
-      <c r="E89" s="12">
+      <c r="C89" s="8">
+        <v>0</v>
+      </c>
+      <c r="E89" s="10">
         <f t="shared" si="9"/>
         <v>1177</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="5">
+      <c r="A90" s="4">
         <f t="shared" si="11"/>
         <v>89</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="8">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="C90" s="10">
-        <v>0</v>
-      </c>
-      <c r="E90" s="12">
+      <c r="C90" s="8">
+        <v>0</v>
+      </c>
+      <c r="E90" s="10">
         <f t="shared" si="9"/>
         <v>1209</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="5">
+      <c r="A91" s="4">
         <f t="shared" si="11"/>
         <v>90</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="8">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="C91" s="10">
-        <v>0</v>
-      </c>
-      <c r="E91" s="12">
+      <c r="C91" s="8">
+        <v>0</v>
+      </c>
+      <c r="E91" s="10">
         <f t="shared" si="9"/>
         <v>1241</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="5">
+      <c r="A92" s="4">
         <f t="shared" si="11"/>
         <v>91</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="8">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="C92" s="10">
-        <v>0</v>
-      </c>
-      <c r="E92" s="12">
+      <c r="C92" s="8">
+        <v>0</v>
+      </c>
+      <c r="E92" s="10">
         <f t="shared" si="9"/>
         <v>1274</v>
       </c>
-      <c r="F92" s="13">
+      <c r="F92" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="5">
+      <c r="A93" s="4">
         <f t="shared" si="11"/>
         <v>92</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="8">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="C93" s="10">
-        <v>0</v>
-      </c>
-      <c r="E93" s="12">
+      <c r="C93" s="8">
+        <v>0</v>
+      </c>
+      <c r="E93" s="10">
         <f t="shared" si="9"/>
         <v>1307</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="5">
-        <f t="shared" ref="A94:B157" si="12">A93+1</f>
+      <c r="A94" s="4">
+        <f t="shared" ref="A94:A157" si="12">A93+1</f>
         <v>93</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="8">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="C94" s="10">
-        <v>0</v>
-      </c>
-      <c r="E94" s="12">
+      <c r="C94" s="8">
+        <v>0</v>
+      </c>
+      <c r="E94" s="10">
         <f t="shared" si="9"/>
         <v>1341</v>
       </c>
-      <c r="F94" s="13">
+      <c r="F94" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="5">
+      <c r="A95" s="4">
         <f t="shared" si="12"/>
         <v>94</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="8">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="C95" s="10">
-        <v>0</v>
-      </c>
-      <c r="E95" s="12">
+      <c r="C95" s="8">
+        <v>0</v>
+      </c>
+      <c r="E95" s="10">
         <f t="shared" si="9"/>
         <v>1375</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="5">
+      <c r="A96" s="4">
         <f t="shared" si="12"/>
         <v>95</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="8">
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="C96" s="10">
-        <v>0</v>
-      </c>
-      <c r="E96" s="12">
+      <c r="C96" s="8">
+        <v>0</v>
+      </c>
+      <c r="E96" s="10">
         <f t="shared" si="9"/>
         <v>1410</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <f t="shared" si="12"/>
         <v>96</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="8">
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="C97" s="10">
-        <v>0</v>
-      </c>
-      <c r="E97" s="12">
+      <c r="C97" s="8">
+        <v>0</v>
+      </c>
+      <c r="E97" s="10">
         <f t="shared" si="9"/>
         <v>1445</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <f t="shared" si="12"/>
         <v>97</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="8">
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="C98" s="10">
-        <v>0</v>
-      </c>
-      <c r="E98" s="12">
+      <c r="C98" s="8">
+        <v>0</v>
+      </c>
+      <c r="E98" s="10">
         <f t="shared" si="9"/>
         <v>1481</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <f t="shared" si="12"/>
         <v>98</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="8">
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="C99" s="10">
-        <v>0</v>
-      </c>
-      <c r="E99" s="12">
+      <c r="C99" s="8">
+        <v>0</v>
+      </c>
+      <c r="E99" s="10">
         <f t="shared" si="9"/>
         <v>1517</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="11">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <f t="shared" si="12"/>
         <v>99</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="8">
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
-      <c r="C100" s="10">
-        <v>0</v>
-      </c>
-      <c r="E100" s="12">
+      <c r="C100" s="8">
+        <v>0</v>
+      </c>
+      <c r="E100" s="10">
         <f t="shared" si="9"/>
         <v>1554</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="8">
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
-      <c r="C101" s="10">
-        <v>0</v>
-      </c>
-      <c r="E101" s="12">
+      <c r="C101" s="8">
+        <v>0</v>
+      </c>
+      <c r="E101" s="10">
         <f t="shared" ref="E101:E164" si="13">E100+B101</f>
         <v>1591</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="11">
         <f t="shared" ref="F101:F164" si="14">B101-B100</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="5">
+      <c r="A102" s="4">
         <f t="shared" si="12"/>
         <v>101</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="8">
         <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="C102" s="10">
-        <v>0</v>
-      </c>
-      <c r="E102" s="12">
+      <c r="C102" s="8">
+        <v>0</v>
+      </c>
+      <c r="E102" s="10">
         <f t="shared" si="13"/>
         <v>1629</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <f t="shared" si="12"/>
         <v>102</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="8">
         <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="C103" s="10">
-        <v>0</v>
-      </c>
-      <c r="E103" s="12">
+      <c r="C103" s="8">
+        <v>0</v>
+      </c>
+      <c r="E103" s="10">
         <f t="shared" si="13"/>
         <v>1667</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="5">
+      <c r="A104" s="4">
         <f t="shared" si="12"/>
         <v>103</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="8">
         <f t="shared" si="7"/>
         <v>39</v>
       </c>
-      <c r="C104" s="10">
-        <v>0</v>
-      </c>
-      <c r="E104" s="12">
+      <c r="C104" s="8">
+        <v>0</v>
+      </c>
+      <c r="E104" s="10">
         <f t="shared" si="13"/>
         <v>1706</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <f t="shared" si="12"/>
         <v>104</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="8">
         <f t="shared" si="7"/>
         <v>39</v>
       </c>
-      <c r="C105" s="10">
-        <v>0</v>
-      </c>
-      <c r="E105" s="12">
+      <c r="C105" s="8">
+        <v>0</v>
+      </c>
+      <c r="E105" s="10">
         <f t="shared" si="13"/>
         <v>1745</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="5">
+      <c r="A106" s="4">
         <f t="shared" si="12"/>
         <v>105</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="8">
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="C106" s="10">
-        <v>0</v>
-      </c>
-      <c r="E106" s="12">
+      <c r="C106" s="8">
+        <v>0</v>
+      </c>
+      <c r="E106" s="10">
         <f t="shared" si="13"/>
         <v>1785</v>
       </c>
-      <c r="F106" s="13">
+      <c r="F106" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <f t="shared" si="12"/>
         <v>106</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="8">
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="C107" s="10">
-        <v>0</v>
-      </c>
-      <c r="E107" s="12">
+      <c r="C107" s="8">
+        <v>0</v>
+      </c>
+      <c r="E107" s="10">
         <f t="shared" si="13"/>
         <v>1825</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="5">
+      <c r="A108" s="4">
         <f t="shared" si="12"/>
         <v>107</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="8">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="C108" s="10">
-        <v>0</v>
-      </c>
-      <c r="E108" s="12">
+      <c r="C108" s="8">
+        <v>0</v>
+      </c>
+      <c r="E108" s="10">
         <f t="shared" si="13"/>
         <v>1866</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <f t="shared" si="12"/>
         <v>108</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="8">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
-      <c r="C109" s="10">
-        <v>0</v>
-      </c>
-      <c r="E109" s="12">
+      <c r="C109" s="8">
+        <v>0</v>
+      </c>
+      <c r="E109" s="10">
         <f t="shared" si="13"/>
         <v>1907</v>
       </c>
-      <c r="F109" s="13">
+      <c r="F109" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="5">
+      <c r="A110" s="4">
         <f t="shared" si="12"/>
         <v>109</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="8">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="C110" s="10">
-        <v>0</v>
-      </c>
-      <c r="E110" s="12">
+      <c r="C110" s="8">
+        <v>0</v>
+      </c>
+      <c r="E110" s="10">
         <f t="shared" si="13"/>
         <v>1949</v>
       </c>
-      <c r="F110" s="13">
+      <c r="F110" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <f t="shared" si="12"/>
         <v>110</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="8">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="C111" s="10">
-        <v>0</v>
-      </c>
-      <c r="E111" s="12">
+      <c r="C111" s="8">
+        <v>0</v>
+      </c>
+      <c r="E111" s="10">
         <f t="shared" si="13"/>
         <v>1991</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="5">
+      <c r="A112" s="4">
         <f t="shared" si="12"/>
         <v>111</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="8">
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="C112" s="10">
-        <v>0</v>
-      </c>
-      <c r="E112" s="12">
+      <c r="C112" s="8">
+        <v>0</v>
+      </c>
+      <c r="E112" s="10">
         <f t="shared" si="13"/>
         <v>2034</v>
       </c>
-      <c r="F112" s="13">
+      <c r="F112" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="5">
+      <c r="A113" s="4">
         <f t="shared" si="12"/>
         <v>112</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="8">
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="C113" s="10">
-        <v>0</v>
-      </c>
-      <c r="E113" s="12">
+      <c r="C113" s="8">
+        <v>0</v>
+      </c>
+      <c r="E113" s="10">
         <f t="shared" si="13"/>
         <v>2077</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <f t="shared" si="12"/>
         <v>113</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="8">
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="C114" s="10">
-        <v>0</v>
-      </c>
-      <c r="E114" s="12">
+      <c r="C114" s="8">
+        <v>0</v>
+      </c>
+      <c r="E114" s="10">
         <f t="shared" si="13"/>
         <v>2121</v>
       </c>
-      <c r="F114" s="13">
+      <c r="F114" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <f t="shared" si="12"/>
         <v>114</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="8">
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="C115" s="10">
-        <v>0</v>
-      </c>
-      <c r="E115" s="12">
+      <c r="C115" s="8">
+        <v>0</v>
+      </c>
+      <c r="E115" s="10">
         <f t="shared" si="13"/>
         <v>2165</v>
       </c>
-      <c r="F115" s="13">
+      <c r="F115" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <f t="shared" si="12"/>
         <v>115</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="8">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="C116" s="10">
-        <v>0</v>
-      </c>
-      <c r="E116" s="12">
+      <c r="C116" s="8">
+        <v>0</v>
+      </c>
+      <c r="E116" s="10">
         <f t="shared" si="13"/>
         <v>2210</v>
       </c>
-      <c r="F116" s="13">
+      <c r="F116" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="5">
+      <c r="A117" s="4">
         <f t="shared" si="12"/>
         <v>116</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="8">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="C117" s="10">
-        <v>0</v>
-      </c>
-      <c r="E117" s="12">
+      <c r="C117" s="8">
+        <v>0</v>
+      </c>
+      <c r="E117" s="10">
         <f t="shared" si="13"/>
         <v>2255</v>
       </c>
-      <c r="F117" s="13">
+      <c r="F117" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="5">
+      <c r="A118" s="4">
         <f t="shared" si="12"/>
         <v>117</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="8">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
-      <c r="C118" s="10">
-        <v>0</v>
-      </c>
-      <c r="E118" s="12">
+      <c r="C118" s="8">
+        <v>0</v>
+      </c>
+      <c r="E118" s="10">
         <f t="shared" si="13"/>
         <v>2301</v>
       </c>
-      <c r="F118" s="13">
+      <c r="F118" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="5">
+      <c r="A119" s="4">
         <f t="shared" si="12"/>
         <v>118</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="8">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
-      <c r="C119" s="10">
-        <v>0</v>
-      </c>
-      <c r="E119" s="12">
+      <c r="C119" s="8">
+        <v>0</v>
+      </c>
+      <c r="E119" s="10">
         <f t="shared" si="13"/>
         <v>2347</v>
       </c>
-      <c r="F119" s="13">
+      <c r="F119" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="5">
+      <c r="A120" s="4">
         <f t="shared" si="12"/>
         <v>119</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="8">
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="C120" s="10">
-        <v>0</v>
-      </c>
-      <c r="E120" s="12">
+      <c r="C120" s="8">
+        <v>0</v>
+      </c>
+      <c r="E120" s="10">
         <f t="shared" si="13"/>
         <v>2394</v>
       </c>
-      <c r="F120" s="13">
+      <c r="F120" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="5">
+      <c r="A121" s="4">
         <f t="shared" si="12"/>
         <v>120</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="8">
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="C121" s="10">
-        <v>0</v>
-      </c>
-      <c r="E121" s="12">
+      <c r="C121" s="8">
+        <v>0</v>
+      </c>
+      <c r="E121" s="10">
         <f t="shared" si="13"/>
         <v>2441</v>
       </c>
-      <c r="F121" s="13">
+      <c r="F121" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="5">
+      <c r="A122" s="4">
         <f t="shared" si="12"/>
         <v>121</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="8">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
-      <c r="C122" s="10">
-        <v>0</v>
-      </c>
-      <c r="E122" s="12">
+      <c r="C122" s="8">
+        <v>0</v>
+      </c>
+      <c r="E122" s="10">
         <f t="shared" si="13"/>
         <v>2489</v>
       </c>
-      <c r="F122" s="13">
+      <c r="F122" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="5">
+      <c r="A123" s="4">
         <f t="shared" si="12"/>
         <v>122</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="8">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
-      <c r="C123" s="10">
-        <v>0</v>
-      </c>
-      <c r="E123" s="12">
+      <c r="C123" s="8">
+        <v>0</v>
+      </c>
+      <c r="E123" s="10">
         <f t="shared" si="13"/>
         <v>2537</v>
       </c>
-      <c r="F123" s="13">
+      <c r="F123" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="5">
+      <c r="A124" s="4">
         <f t="shared" si="12"/>
         <v>123</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="8">
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
-      <c r="C124" s="10">
-        <v>0</v>
-      </c>
-      <c r="E124" s="12">
+      <c r="C124" s="8">
+        <v>0</v>
+      </c>
+      <c r="E124" s="10">
         <f t="shared" si="13"/>
         <v>2586</v>
       </c>
-      <c r="F124" s="13">
+      <c r="F124" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="5">
+      <c r="A125" s="4">
         <f t="shared" si="12"/>
         <v>124</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="8">
         <f t="shared" ref="B125:B188" si="15">B123+1</f>
         <v>49</v>
       </c>
-      <c r="C125" s="10">
-        <v>0</v>
-      </c>
-      <c r="E125" s="12">
+      <c r="C125" s="8">
+        <v>0</v>
+      </c>
+      <c r="E125" s="10">
         <f t="shared" si="13"/>
         <v>2635</v>
       </c>
-      <c r="F125" s="13">
+      <c r="F125" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="5">
+      <c r="A126" s="4">
         <f t="shared" si="12"/>
         <v>125</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="8">
         <f t="shared" si="15"/>
         <v>50</v>
       </c>
-      <c r="C126" s="10">
-        <v>0</v>
-      </c>
-      <c r="E126" s="12">
+      <c r="C126" s="8">
+        <v>0</v>
+      </c>
+      <c r="E126" s="10">
         <f t="shared" si="13"/>
         <v>2685</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="5">
+      <c r="A127" s="4">
         <f t="shared" si="12"/>
         <v>126</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="8">
         <f t="shared" si="15"/>
         <v>50</v>
       </c>
-      <c r="C127" s="10">
-        <v>0</v>
-      </c>
-      <c r="E127" s="12">
+      <c r="C127" s="8">
+        <v>0</v>
+      </c>
+      <c r="E127" s="10">
         <f t="shared" si="13"/>
         <v>2735</v>
       </c>
-      <c r="F127" s="13">
+      <c r="F127" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="5">
+      <c r="A128" s="4">
         <f t="shared" si="12"/>
         <v>127</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="8">
         <f t="shared" si="15"/>
         <v>51</v>
       </c>
-      <c r="C128" s="10">
-        <v>0</v>
-      </c>
-      <c r="E128" s="12">
+      <c r="C128" s="8">
+        <v>0</v>
+      </c>
+      <c r="E128" s="10">
         <f t="shared" si="13"/>
         <v>2786</v>
       </c>
-      <c r="F128" s="13">
+      <c r="F128" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="5">
+      <c r="A129" s="4">
         <f t="shared" si="12"/>
         <v>128</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="8">
         <f t="shared" si="15"/>
         <v>51</v>
       </c>
-      <c r="C129" s="10">
-        <v>0</v>
-      </c>
-      <c r="E129" s="12">
+      <c r="C129" s="8">
+        <v>0</v>
+      </c>
+      <c r="E129" s="10">
         <f t="shared" si="13"/>
         <v>2837</v>
       </c>
-      <c r="F129" s="13">
+      <c r="F129" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="5">
+      <c r="A130" s="4">
         <f t="shared" si="12"/>
         <v>129</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="8">
         <f t="shared" si="15"/>
         <v>52</v>
       </c>
-      <c r="C130" s="10">
-        <v>0</v>
-      </c>
-      <c r="E130" s="12">
+      <c r="C130" s="8">
+        <v>0</v>
+      </c>
+      <c r="E130" s="10">
         <f t="shared" si="13"/>
         <v>2889</v>
       </c>
-      <c r="F130" s="13">
+      <c r="F130" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="5">
+      <c r="A131" s="4">
         <f t="shared" si="12"/>
         <v>130</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="8">
         <f t="shared" si="15"/>
         <v>52</v>
       </c>
-      <c r="C131" s="10">
-        <v>0</v>
-      </c>
-      <c r="E131" s="12">
+      <c r="C131" s="8">
+        <v>0</v>
+      </c>
+      <c r="E131" s="10">
         <f t="shared" si="13"/>
         <v>2941</v>
       </c>
-      <c r="F131" s="13">
+      <c r="F131" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="5">
+      <c r="A132" s="4">
         <f t="shared" si="12"/>
         <v>131</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="8">
         <f t="shared" si="15"/>
         <v>53</v>
       </c>
-      <c r="C132" s="10">
-        <v>0</v>
-      </c>
-      <c r="E132" s="12">
+      <c r="C132" s="8">
+        <v>0</v>
+      </c>
+      <c r="E132" s="10">
         <f t="shared" si="13"/>
         <v>2994</v>
       </c>
-      <c r="F132" s="13">
+      <c r="F132" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="5">
+      <c r="A133" s="4">
         <f t="shared" si="12"/>
         <v>132</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="8">
         <f t="shared" si="15"/>
         <v>53</v>
       </c>
-      <c r="C133" s="10">
-        <v>0</v>
-      </c>
-      <c r="E133" s="12">
+      <c r="C133" s="8">
+        <v>0</v>
+      </c>
+      <c r="E133" s="10">
         <f t="shared" si="13"/>
         <v>3047</v>
       </c>
-      <c r="F133" s="13">
+      <c r="F133" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="5">
+      <c r="A134" s="4">
         <f t="shared" si="12"/>
         <v>133</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="8">
         <f t="shared" si="15"/>
         <v>54</v>
       </c>
-      <c r="C134" s="10">
-        <v>0</v>
-      </c>
-      <c r="E134" s="12">
+      <c r="C134" s="8">
+        <v>0</v>
+      </c>
+      <c r="E134" s="10">
         <f t="shared" si="13"/>
         <v>3101</v>
       </c>
-      <c r="F134" s="13">
+      <c r="F134" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="5">
+      <c r="A135" s="4">
         <f t="shared" si="12"/>
         <v>134</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="8">
         <f t="shared" si="15"/>
         <v>54</v>
       </c>
-      <c r="C135" s="10">
-        <v>0</v>
-      </c>
-      <c r="E135" s="12">
+      <c r="C135" s="8">
+        <v>0</v>
+      </c>
+      <c r="E135" s="10">
         <f t="shared" si="13"/>
         <v>3155</v>
       </c>
-      <c r="F135" s="13">
+      <c r="F135" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5">
+      <c r="A136" s="4">
         <f t="shared" si="12"/>
         <v>135</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="8">
         <f t="shared" si="15"/>
         <v>55</v>
       </c>
-      <c r="C136" s="10">
-        <v>0</v>
-      </c>
-      <c r="E136" s="12">
+      <c r="C136" s="8">
+        <v>0</v>
+      </c>
+      <c r="E136" s="10">
         <f t="shared" si="13"/>
         <v>3210</v>
       </c>
-      <c r="F136" s="13">
+      <c r="F136" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="5">
+      <c r="A137" s="4">
         <f t="shared" si="12"/>
         <v>136</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="8">
         <f t="shared" si="15"/>
         <v>55</v>
       </c>
-      <c r="C137" s="10">
-        <v>0</v>
-      </c>
-      <c r="E137" s="12">
+      <c r="C137" s="8">
+        <v>0</v>
+      </c>
+      <c r="E137" s="10">
         <f t="shared" si="13"/>
         <v>3265</v>
       </c>
-      <c r="F137" s="13">
+      <c r="F137" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="5">
+      <c r="A138" s="4">
         <f t="shared" si="12"/>
         <v>137</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="8">
         <f t="shared" si="15"/>
         <v>56</v>
       </c>
-      <c r="C138" s="10">
-        <v>0</v>
-      </c>
-      <c r="E138" s="12">
+      <c r="C138" s="8">
+        <v>0</v>
+      </c>
+      <c r="E138" s="10">
         <f t="shared" si="13"/>
         <v>3321</v>
       </c>
-      <c r="F138" s="13">
+      <c r="F138" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="5">
+      <c r="A139" s="4">
         <f t="shared" si="12"/>
         <v>138</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="8">
         <f t="shared" si="15"/>
         <v>56</v>
       </c>
-      <c r="C139" s="10">
-        <v>0</v>
-      </c>
-      <c r="E139" s="12">
+      <c r="C139" s="8">
+        <v>0</v>
+      </c>
+      <c r="E139" s="10">
         <f t="shared" si="13"/>
         <v>3377</v>
       </c>
-      <c r="F139" s="13">
+      <c r="F139" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="5">
+      <c r="A140" s="4">
         <f t="shared" si="12"/>
         <v>139</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="8">
         <f t="shared" si="15"/>
         <v>57</v>
       </c>
-      <c r="C140" s="10">
-        <v>0</v>
-      </c>
-      <c r="E140" s="12">
+      <c r="C140" s="8">
+        <v>0</v>
+      </c>
+      <c r="E140" s="10">
         <f t="shared" si="13"/>
         <v>3434</v>
       </c>
-      <c r="F140" s="13">
+      <c r="F140" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="5">
+      <c r="A141" s="4">
         <f t="shared" si="12"/>
         <v>140</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="8">
         <f t="shared" si="15"/>
         <v>57</v>
       </c>
-      <c r="C141" s="10">
-        <v>0</v>
-      </c>
-      <c r="E141" s="12">
+      <c r="C141" s="8">
+        <v>0</v>
+      </c>
+      <c r="E141" s="10">
         <f t="shared" si="13"/>
         <v>3491</v>
       </c>
-      <c r="F141" s="13">
+      <c r="F141" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="5">
+      <c r="A142" s="4">
         <f t="shared" si="12"/>
         <v>141</v>
       </c>
-      <c r="B142" s="10">
+      <c r="B142" s="8">
         <f t="shared" si="15"/>
         <v>58</v>
       </c>
-      <c r="C142" s="10">
-        <v>0</v>
-      </c>
-      <c r="E142" s="12">
+      <c r="C142" s="8">
+        <v>0</v>
+      </c>
+      <c r="E142" s="10">
         <f t="shared" si="13"/>
         <v>3549</v>
       </c>
-      <c r="F142" s="13">
+      <c r="F142" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="5">
+      <c r="A143" s="4">
         <f t="shared" si="12"/>
         <v>142</v>
       </c>
-      <c r="B143" s="10">
+      <c r="B143" s="8">
         <f t="shared" si="15"/>
         <v>58</v>
       </c>
-      <c r="C143" s="10">
-        <v>0</v>
-      </c>
-      <c r="E143" s="12">
+      <c r="C143" s="8">
+        <v>0</v>
+      </c>
+      <c r="E143" s="10">
         <f t="shared" si="13"/>
         <v>3607</v>
       </c>
-      <c r="F143" s="13">
+      <c r="F143" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5">
+      <c r="A144" s="4">
         <f t="shared" si="12"/>
         <v>143</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="8">
         <f t="shared" si="15"/>
         <v>59</v>
       </c>
-      <c r="C144" s="10">
-        <v>0</v>
-      </c>
-      <c r="E144" s="12">
+      <c r="C144" s="8">
+        <v>0</v>
+      </c>
+      <c r="E144" s="10">
         <f t="shared" si="13"/>
         <v>3666</v>
       </c>
-      <c r="F144" s="13">
+      <c r="F144" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="5">
+      <c r="A145" s="4">
         <f t="shared" si="12"/>
         <v>144</v>
       </c>
-      <c r="B145" s="10">
+      <c r="B145" s="8">
         <f t="shared" si="15"/>
         <v>59</v>
       </c>
-      <c r="C145" s="10">
-        <v>0</v>
-      </c>
-      <c r="E145" s="12">
+      <c r="C145" s="8">
+        <v>0</v>
+      </c>
+      <c r="E145" s="10">
         <f t="shared" si="13"/>
         <v>3725</v>
       </c>
-      <c r="F145" s="13">
+      <c r="F145" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="5">
+      <c r="A146" s="4">
         <f t="shared" si="12"/>
         <v>145</v>
       </c>
-      <c r="B146" s="10">
+      <c r="B146" s="8">
         <f t="shared" si="15"/>
         <v>60</v>
       </c>
-      <c r="C146" s="10">
-        <v>0</v>
-      </c>
-      <c r="E146" s="12">
+      <c r="C146" s="8">
+        <v>0</v>
+      </c>
+      <c r="E146" s="10">
         <f t="shared" si="13"/>
         <v>3785</v>
       </c>
-      <c r="F146" s="13">
+      <c r="F146" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="5">
+      <c r="A147" s="4">
         <f t="shared" si="12"/>
         <v>146</v>
       </c>
-      <c r="B147" s="10">
+      <c r="B147" s="8">
         <f t="shared" si="15"/>
         <v>60</v>
       </c>
-      <c r="C147" s="10">
-        <v>0</v>
-      </c>
-      <c r="E147" s="12">
+      <c r="C147" s="8">
+        <v>0</v>
+      </c>
+      <c r="E147" s="10">
         <f t="shared" si="13"/>
         <v>3845</v>
       </c>
-      <c r="F147" s="13">
+      <c r="F147" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="5">
+      <c r="A148" s="4">
         <f t="shared" si="12"/>
         <v>147</v>
       </c>
-      <c r="B148" s="10">
+      <c r="B148" s="8">
         <f t="shared" si="15"/>
         <v>61</v>
       </c>
-      <c r="C148" s="10">
-        <v>0</v>
-      </c>
-      <c r="E148" s="12">
+      <c r="C148" s="8">
+        <v>0</v>
+      </c>
+      <c r="E148" s="10">
         <f t="shared" si="13"/>
         <v>3906</v>
       </c>
-      <c r="F148" s="13">
+      <c r="F148" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="5">
+      <c r="A149" s="4">
         <f t="shared" si="12"/>
         <v>148</v>
       </c>
-      <c r="B149" s="10">
+      <c r="B149" s="8">
         <f t="shared" si="15"/>
         <v>61</v>
       </c>
-      <c r="C149" s="10">
-        <v>0</v>
-      </c>
-      <c r="E149" s="12">
+      <c r="C149" s="8">
+        <v>0</v>
+      </c>
+      <c r="E149" s="10">
         <f t="shared" si="13"/>
         <v>3967</v>
       </c>
-      <c r="F149" s="13">
+      <c r="F149" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="5">
+      <c r="A150" s="4">
         <f t="shared" si="12"/>
         <v>149</v>
       </c>
-      <c r="B150" s="10">
+      <c r="B150" s="8">
         <f t="shared" si="15"/>
         <v>62</v>
       </c>
-      <c r="C150" s="10">
-        <v>0</v>
-      </c>
-      <c r="E150" s="12">
+      <c r="C150" s="8">
+        <v>0</v>
+      </c>
+      <c r="E150" s="10">
         <f t="shared" si="13"/>
         <v>4029</v>
       </c>
-      <c r="F150" s="13">
+      <c r="F150" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="5">
+      <c r="A151" s="4">
         <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="B151" s="10">
+      <c r="B151" s="8">
         <f t="shared" si="15"/>
         <v>62</v>
       </c>
-      <c r="C151" s="10">
-        <v>0</v>
-      </c>
-      <c r="E151" s="12">
+      <c r="C151" s="8">
+        <v>0</v>
+      </c>
+      <c r="E151" s="10">
         <f t="shared" si="13"/>
         <v>4091</v>
       </c>
-      <c r="F151" s="13">
+      <c r="F151" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="5">
+      <c r="A152" s="4">
         <f t="shared" si="12"/>
         <v>151</v>
       </c>
-      <c r="B152" s="10">
+      <c r="B152" s="8">
         <f t="shared" si="15"/>
         <v>63</v>
       </c>
-      <c r="C152" s="10">
-        <v>0</v>
-      </c>
-      <c r="E152" s="12">
+      <c r="C152" s="8">
+        <v>0</v>
+      </c>
+      <c r="E152" s="10">
         <f t="shared" si="13"/>
         <v>4154</v>
       </c>
-      <c r="F152" s="13">
+      <c r="F152" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="5">
+      <c r="A153" s="4">
         <f t="shared" si="12"/>
         <v>152</v>
       </c>
-      <c r="B153" s="10">
+      <c r="B153" s="8">
         <f t="shared" si="15"/>
         <v>63</v>
       </c>
-      <c r="C153" s="10">
-        <v>0</v>
-      </c>
-      <c r="E153" s="12">
+      <c r="C153" s="8">
+        <v>0</v>
+      </c>
+      <c r="E153" s="10">
         <f t="shared" si="13"/>
         <v>4217</v>
       </c>
-      <c r="F153" s="13">
+      <c r="F153" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="5">
+      <c r="A154" s="4">
         <f t="shared" si="12"/>
         <v>153</v>
       </c>
-      <c r="B154" s="10">
+      <c r="B154" s="8">
         <f t="shared" si="15"/>
         <v>64</v>
       </c>
-      <c r="C154" s="10">
-        <v>0</v>
-      </c>
-      <c r="E154" s="12">
+      <c r="C154" s="8">
+        <v>0</v>
+      </c>
+      <c r="E154" s="10">
         <f t="shared" si="13"/>
         <v>4281</v>
       </c>
-      <c r="F154" s="13">
+      <c r="F154" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="5">
+      <c r="A155" s="4">
         <f t="shared" si="12"/>
         <v>154</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="8">
         <f t="shared" si="15"/>
         <v>64</v>
       </c>
-      <c r="C155" s="10">
-        <v>0</v>
-      </c>
-      <c r="E155" s="12">
+      <c r="C155" s="8">
+        <v>0</v>
+      </c>
+      <c r="E155" s="10">
         <f t="shared" si="13"/>
         <v>4345</v>
       </c>
-      <c r="F155" s="13">
+      <c r="F155" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="5">
+      <c r="A156" s="4">
         <f t="shared" si="12"/>
         <v>155</v>
       </c>
-      <c r="B156" s="10">
+      <c r="B156" s="8">
         <f t="shared" si="15"/>
         <v>65</v>
       </c>
-      <c r="C156" s="10">
-        <v>0</v>
-      </c>
-      <c r="E156" s="12">
+      <c r="C156" s="8">
+        <v>0</v>
+      </c>
+      <c r="E156" s="10">
         <f t="shared" si="13"/>
         <v>4410</v>
       </c>
-      <c r="F156" s="13">
+      <c r="F156" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
+      <c r="A157" s="4">
         <f t="shared" si="12"/>
         <v>156</v>
       </c>
-      <c r="B157" s="10">
+      <c r="B157" s="8">
         <f t="shared" si="15"/>
         <v>65</v>
       </c>
-      <c r="C157" s="10">
-        <v>0</v>
-      </c>
-      <c r="E157" s="12">
+      <c r="C157" s="8">
+        <v>0</v>
+      </c>
+      <c r="E157" s="10">
         <f t="shared" si="13"/>
         <v>4475</v>
       </c>
-      <c r="F157" s="13">
+      <c r="F157" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
-        <f t="shared" ref="A158:B221" si="16">A157+1</f>
+      <c r="A158" s="4">
+        <f t="shared" ref="A158:A221" si="16">A157+1</f>
         <v>157</v>
       </c>
-      <c r="B158" s="10">
+      <c r="B158" s="8">
         <f t="shared" si="15"/>
         <v>66</v>
       </c>
-      <c r="C158" s="10">
-        <v>0</v>
-      </c>
-      <c r="E158" s="12">
+      <c r="C158" s="8">
+        <v>0</v>
+      </c>
+      <c r="E158" s="10">
         <f t="shared" si="13"/>
         <v>4541</v>
       </c>
-      <c r="F158" s="13">
+      <c r="F158" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
+      <c r="A159" s="4">
         <f t="shared" si="16"/>
         <v>158</v>
       </c>
-      <c r="B159" s="10">
+      <c r="B159" s="8">
         <f t="shared" si="15"/>
         <v>66</v>
       </c>
-      <c r="C159" s="10">
-        <v>0</v>
-      </c>
-      <c r="E159" s="12">
+      <c r="C159" s="8">
+        <v>0</v>
+      </c>
+      <c r="E159" s="10">
         <f t="shared" si="13"/>
         <v>4607</v>
       </c>
-      <c r="F159" s="13">
+      <c r="F159" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="5">
+      <c r="A160" s="4">
         <f t="shared" si="16"/>
         <v>159</v>
       </c>
-      <c r="B160" s="10">
+      <c r="B160" s="8">
         <f t="shared" si="15"/>
         <v>67</v>
       </c>
-      <c r="C160" s="10">
-        <v>0</v>
-      </c>
-      <c r="E160" s="12">
+      <c r="C160" s="8">
+        <v>0</v>
+      </c>
+      <c r="E160" s="10">
         <f t="shared" si="13"/>
         <v>4674</v>
       </c>
-      <c r="F160" s="13">
+      <c r="F160" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="5">
+      <c r="A161" s="4">
         <f t="shared" si="16"/>
         <v>160</v>
       </c>
-      <c r="B161" s="10">
+      <c r="B161" s="8">
         <f t="shared" si="15"/>
         <v>67</v>
       </c>
-      <c r="C161" s="10">
-        <v>0</v>
-      </c>
-      <c r="E161" s="12">
+      <c r="C161" s="8">
+        <v>0</v>
+      </c>
+      <c r="E161" s="10">
         <f t="shared" si="13"/>
         <v>4741</v>
       </c>
-      <c r="F161" s="13">
+      <c r="F161" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="5">
+      <c r="A162" s="4">
         <f t="shared" si="16"/>
         <v>161</v>
       </c>
-      <c r="B162" s="10">
+      <c r="B162" s="8">
         <f t="shared" si="15"/>
         <v>68</v>
       </c>
-      <c r="C162" s="10">
-        <v>0</v>
-      </c>
-      <c r="E162" s="12">
+      <c r="C162" s="8">
+        <v>0</v>
+      </c>
+      <c r="E162" s="10">
         <f t="shared" si="13"/>
         <v>4809</v>
       </c>
-      <c r="F162" s="13">
+      <c r="F162" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="5">
+      <c r="A163" s="4">
         <f t="shared" si="16"/>
         <v>162</v>
       </c>
-      <c r="B163" s="10">
+      <c r="B163" s="8">
         <f t="shared" si="15"/>
         <v>68</v>
       </c>
-      <c r="C163" s="10">
-        <v>0</v>
-      </c>
-      <c r="E163" s="12">
+      <c r="C163" s="8">
+        <v>0</v>
+      </c>
+      <c r="E163" s="10">
         <f t="shared" si="13"/>
         <v>4877</v>
       </c>
-      <c r="F163" s="13">
+      <c r="F163" s="11">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="5">
+      <c r="A164" s="4">
         <f t="shared" si="16"/>
         <v>163</v>
       </c>
-      <c r="B164" s="10">
+      <c r="B164" s="8">
         <f t="shared" si="15"/>
         <v>69</v>
       </c>
-      <c r="C164" s="10">
-        <v>0</v>
-      </c>
-      <c r="E164" s="12">
+      <c r="C164" s="8">
+        <v>0</v>
+      </c>
+      <c r="E164" s="10">
         <f t="shared" si="13"/>
         <v>4946</v>
       </c>
-      <c r="F164" s="13">
+      <c r="F164" s="11">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="5">
+      <c r="A165" s="4">
         <f t="shared" si="16"/>
         <v>164</v>
       </c>
-      <c r="B165" s="10">
+      <c r="B165" s="8">
         <f t="shared" si="15"/>
         <v>69</v>
       </c>
-      <c r="C165" s="10">
-        <v>0</v>
-      </c>
-      <c r="E165" s="12">
+      <c r="C165" s="8">
+        <v>0</v>
+      </c>
+      <c r="E165" s="10">
         <f t="shared" ref="E165:E228" si="17">E164+B165</f>
         <v>5015</v>
       </c>
-      <c r="F165" s="13">
+      <c r="F165" s="11">
         <f t="shared" ref="F165:F228" si="18">B165-B164</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="5">
+      <c r="A166" s="4">
         <f t="shared" si="16"/>
         <v>165</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B166" s="8">
         <f t="shared" si="15"/>
         <v>70</v>
       </c>
-      <c r="C166" s="10">
-        <v>0</v>
-      </c>
-      <c r="E166" s="12">
+      <c r="C166" s="8">
+        <v>0</v>
+      </c>
+      <c r="E166" s="10">
         <f t="shared" si="17"/>
         <v>5085</v>
       </c>
-      <c r="F166" s="13">
+      <c r="F166" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="5">
+      <c r="A167" s="4">
         <f t="shared" si="16"/>
         <v>166</v>
       </c>
-      <c r="B167" s="10">
+      <c r="B167" s="8">
         <f t="shared" si="15"/>
         <v>70</v>
       </c>
-      <c r="C167" s="10">
-        <v>0</v>
-      </c>
-      <c r="E167" s="12">
+      <c r="C167" s="8">
+        <v>0</v>
+      </c>
+      <c r="E167" s="10">
         <f t="shared" si="17"/>
         <v>5155</v>
       </c>
-      <c r="F167" s="13">
+      <c r="F167" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="5">
+      <c r="A168" s="4">
         <f t="shared" si="16"/>
         <v>167</v>
       </c>
-      <c r="B168" s="10">
+      <c r="B168" s="8">
         <f t="shared" si="15"/>
         <v>71</v>
       </c>
-      <c r="C168" s="10">
-        <v>0</v>
-      </c>
-      <c r="E168" s="12">
+      <c r="C168" s="8">
+        <v>0</v>
+      </c>
+      <c r="E168" s="10">
         <f t="shared" si="17"/>
         <v>5226</v>
       </c>
-      <c r="F168" s="13">
+      <c r="F168" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="5">
+      <c r="A169" s="4">
         <f t="shared" si="16"/>
         <v>168</v>
       </c>
-      <c r="B169" s="10">
+      <c r="B169" s="8">
         <f t="shared" si="15"/>
         <v>71</v>
       </c>
-      <c r="C169" s="10">
-        <v>0</v>
-      </c>
-      <c r="E169" s="12">
+      <c r="C169" s="8">
+        <v>0</v>
+      </c>
+      <c r="E169" s="10">
         <f t="shared" si="17"/>
         <v>5297</v>
       </c>
-      <c r="F169" s="13">
+      <c r="F169" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="5">
+      <c r="A170" s="4">
         <f t="shared" si="16"/>
         <v>169</v>
       </c>
-      <c r="B170" s="10">
+      <c r="B170" s="8">
         <f t="shared" si="15"/>
         <v>72</v>
       </c>
-      <c r="C170" s="10">
-        <v>0</v>
-      </c>
-      <c r="E170" s="12">
+      <c r="C170" s="8">
+        <v>0</v>
+      </c>
+      <c r="E170" s="10">
         <f t="shared" si="17"/>
         <v>5369</v>
       </c>
-      <c r="F170" s="13">
+      <c r="F170" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="5">
+      <c r="A171" s="4">
         <f t="shared" si="16"/>
         <v>170</v>
       </c>
-      <c r="B171" s="10">
+      <c r="B171" s="8">
         <f t="shared" si="15"/>
         <v>72</v>
       </c>
-      <c r="C171" s="10">
-        <v>0</v>
-      </c>
-      <c r="E171" s="12">
+      <c r="C171" s="8">
+        <v>0</v>
+      </c>
+      <c r="E171" s="10">
         <f t="shared" si="17"/>
         <v>5441</v>
       </c>
-      <c r="F171" s="13">
+      <c r="F171" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="5">
+      <c r="A172" s="4">
         <f t="shared" si="16"/>
         <v>171</v>
       </c>
-      <c r="B172" s="10">
+      <c r="B172" s="8">
         <f t="shared" si="15"/>
         <v>73</v>
       </c>
-      <c r="C172" s="10">
-        <v>0</v>
-      </c>
-      <c r="E172" s="12">
+      <c r="C172" s="8">
+        <v>0</v>
+      </c>
+      <c r="E172" s="10">
         <f t="shared" si="17"/>
         <v>5514</v>
       </c>
-      <c r="F172" s="13">
+      <c r="F172" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="5">
+      <c r="A173" s="4">
         <f t="shared" si="16"/>
         <v>172</v>
       </c>
-      <c r="B173" s="10">
+      <c r="B173" s="8">
         <f t="shared" si="15"/>
         <v>73</v>
       </c>
-      <c r="C173" s="10">
-        <v>0</v>
-      </c>
-      <c r="E173" s="12">
+      <c r="C173" s="8">
+        <v>0</v>
+      </c>
+      <c r="E173" s="10">
         <f t="shared" si="17"/>
         <v>5587</v>
       </c>
-      <c r="F173" s="13">
+      <c r="F173" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="5">
+      <c r="A174" s="4">
         <f t="shared" si="16"/>
         <v>173</v>
       </c>
-      <c r="B174" s="10">
+      <c r="B174" s="8">
         <f t="shared" si="15"/>
         <v>74</v>
       </c>
-      <c r="C174" s="10">
-        <v>0</v>
-      </c>
-      <c r="E174" s="12">
+      <c r="C174" s="8">
+        <v>0</v>
+      </c>
+      <c r="E174" s="10">
         <f t="shared" si="17"/>
         <v>5661</v>
       </c>
-      <c r="F174" s="13">
+      <c r="F174" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="5">
+      <c r="A175" s="4">
         <f t="shared" si="16"/>
         <v>174</v>
       </c>
-      <c r="B175" s="10">
+      <c r="B175" s="8">
         <f t="shared" si="15"/>
         <v>74</v>
       </c>
-      <c r="C175" s="10">
-        <v>0</v>
-      </c>
-      <c r="E175" s="12">
+      <c r="C175" s="8">
+        <v>0</v>
+      </c>
+      <c r="E175" s="10">
         <f t="shared" si="17"/>
         <v>5735</v>
       </c>
-      <c r="F175" s="13">
+      <c r="F175" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="5">
+      <c r="A176" s="4">
         <f t="shared" si="16"/>
         <v>175</v>
       </c>
-      <c r="B176" s="10">
+      <c r="B176" s="8">
         <f t="shared" si="15"/>
         <v>75</v>
       </c>
-      <c r="C176" s="10">
-        <v>0</v>
-      </c>
-      <c r="E176" s="12">
+      <c r="C176" s="8">
+        <v>0</v>
+      </c>
+      <c r="E176" s="10">
         <f t="shared" si="17"/>
         <v>5810</v>
       </c>
-      <c r="F176" s="13">
+      <c r="F176" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="5">
+      <c r="A177" s="4">
         <f t="shared" si="16"/>
         <v>176</v>
       </c>
-      <c r="B177" s="10">
+      <c r="B177" s="8">
         <f t="shared" si="15"/>
         <v>75</v>
       </c>
-      <c r="C177" s="10">
-        <v>0</v>
-      </c>
-      <c r="E177" s="12">
+      <c r="C177" s="8">
+        <v>0</v>
+      </c>
+      <c r="E177" s="10">
         <f t="shared" si="17"/>
         <v>5885</v>
       </c>
-      <c r="F177" s="13">
+      <c r="F177" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="5">
+      <c r="A178" s="4">
         <f t="shared" si="16"/>
         <v>177</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B178" s="8">
         <f t="shared" si="15"/>
         <v>76</v>
       </c>
-      <c r="C178" s="10">
-        <v>0</v>
-      </c>
-      <c r="E178" s="12">
+      <c r="C178" s="8">
+        <v>0</v>
+      </c>
+      <c r="E178" s="10">
         <f t="shared" si="17"/>
         <v>5961</v>
       </c>
-      <c r="F178" s="13">
+      <c r="F178" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="5">
+      <c r="A179" s="4">
         <f t="shared" si="16"/>
         <v>178</v>
       </c>
-      <c r="B179" s="10">
+      <c r="B179" s="8">
         <f t="shared" si="15"/>
         <v>76</v>
       </c>
-      <c r="C179" s="10">
-        <v>0</v>
-      </c>
-      <c r="E179" s="12">
+      <c r="C179" s="8">
+        <v>0</v>
+      </c>
+      <c r="E179" s="10">
         <f t="shared" si="17"/>
         <v>6037</v>
       </c>
-      <c r="F179" s="13">
+      <c r="F179" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="5">
+      <c r="A180" s="4">
         <f t="shared" si="16"/>
         <v>179</v>
       </c>
-      <c r="B180" s="10">
+      <c r="B180" s="8">
         <f t="shared" si="15"/>
         <v>77</v>
       </c>
-      <c r="C180" s="10">
-        <v>0</v>
-      </c>
-      <c r="E180" s="12">
+      <c r="C180" s="8">
+        <v>0</v>
+      </c>
+      <c r="E180" s="10">
         <f t="shared" si="17"/>
         <v>6114</v>
       </c>
-      <c r="F180" s="13">
+      <c r="F180" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="5">
+      <c r="A181" s="4">
         <f t="shared" si="16"/>
         <v>180</v>
       </c>
-      <c r="B181" s="10">
+      <c r="B181" s="8">
         <f t="shared" si="15"/>
         <v>77</v>
       </c>
-      <c r="C181" s="10">
-        <v>0</v>
-      </c>
-      <c r="E181" s="12">
+      <c r="C181" s="8">
+        <v>0</v>
+      </c>
+      <c r="E181" s="10">
         <f t="shared" si="17"/>
         <v>6191</v>
       </c>
-      <c r="F181" s="13">
+      <c r="F181" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+      <c r="A182" s="4">
         <f t="shared" si="16"/>
         <v>181</v>
       </c>
-      <c r="B182" s="10">
+      <c r="B182" s="8">
         <f t="shared" si="15"/>
         <v>78</v>
       </c>
-      <c r="C182" s="10">
-        <v>0</v>
-      </c>
-      <c r="E182" s="12">
+      <c r="C182" s="8">
+        <v>0</v>
+      </c>
+      <c r="E182" s="10">
         <f t="shared" si="17"/>
         <v>6269</v>
       </c>
-      <c r="F182" s="13">
+      <c r="F182" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="5">
+      <c r="A183" s="4">
         <f t="shared" si="16"/>
         <v>182</v>
       </c>
-      <c r="B183" s="10">
+      <c r="B183" s="8">
         <f t="shared" si="15"/>
         <v>78</v>
       </c>
-      <c r="C183" s="10">
-        <v>0</v>
-      </c>
-      <c r="E183" s="12">
+      <c r="C183" s="8">
+        <v>0</v>
+      </c>
+      <c r="E183" s="10">
         <f t="shared" si="17"/>
         <v>6347</v>
       </c>
-      <c r="F183" s="13">
+      <c r="F183" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="5">
+      <c r="A184" s="4">
         <f t="shared" si="16"/>
         <v>183</v>
       </c>
-      <c r="B184" s="10">
+      <c r="B184" s="8">
         <f t="shared" si="15"/>
         <v>79</v>
       </c>
-      <c r="C184" s="10">
-        <v>0</v>
-      </c>
-      <c r="E184" s="12">
+      <c r="C184" s="8">
+        <v>0</v>
+      </c>
+      <c r="E184" s="10">
         <f t="shared" si="17"/>
         <v>6426</v>
       </c>
-      <c r="F184" s="13">
+      <c r="F184" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="5">
+      <c r="A185" s="4">
         <f t="shared" si="16"/>
         <v>184</v>
       </c>
-      <c r="B185" s="10">
+      <c r="B185" s="8">
         <f t="shared" si="15"/>
         <v>79</v>
       </c>
-      <c r="C185" s="10">
-        <v>0</v>
-      </c>
-      <c r="E185" s="12">
+      <c r="C185" s="8">
+        <v>0</v>
+      </c>
+      <c r="E185" s="10">
         <f t="shared" si="17"/>
         <v>6505</v>
       </c>
-      <c r="F185" s="13">
+      <c r="F185" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="5">
+      <c r="A186" s="4">
         <f t="shared" si="16"/>
         <v>185</v>
       </c>
-      <c r="B186" s="10">
+      <c r="B186" s="8">
         <f t="shared" si="15"/>
         <v>80</v>
       </c>
-      <c r="C186" s="10">
-        <v>0</v>
-      </c>
-      <c r="E186" s="12">
+      <c r="C186" s="8">
+        <v>0</v>
+      </c>
+      <c r="E186" s="10">
         <f t="shared" si="17"/>
         <v>6585</v>
       </c>
-      <c r="F186" s="13">
+      <c r="F186" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="5">
+      <c r="A187" s="4">
         <f t="shared" si="16"/>
         <v>186</v>
       </c>
-      <c r="B187" s="10">
+      <c r="B187" s="8">
         <f t="shared" si="15"/>
         <v>80</v>
       </c>
-      <c r="C187" s="10">
-        <v>0</v>
-      </c>
-      <c r="E187" s="12">
+      <c r="C187" s="8">
+        <v>0</v>
+      </c>
+      <c r="E187" s="10">
         <f t="shared" si="17"/>
         <v>6665</v>
       </c>
-      <c r="F187" s="13">
+      <c r="F187" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="5">
+      <c r="A188" s="4">
         <f t="shared" si="16"/>
         <v>187</v>
       </c>
-      <c r="B188" s="10">
+      <c r="B188" s="8">
         <f t="shared" si="15"/>
         <v>81</v>
       </c>
-      <c r="C188" s="10">
-        <v>0</v>
-      </c>
-      <c r="E188" s="12">
+      <c r="C188" s="8">
+        <v>0</v>
+      </c>
+      <c r="E188" s="10">
         <f t="shared" si="17"/>
         <v>6746</v>
       </c>
-      <c r="F188" s="13">
+      <c r="F188" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="5">
+      <c r="A189" s="4">
         <f t="shared" si="16"/>
         <v>188</v>
       </c>
-      <c r="B189" s="10">
+      <c r="B189" s="8">
         <f t="shared" ref="B189:B227" si="19">B187+1</f>
         <v>81</v>
       </c>
-      <c r="C189" s="10">
-        <v>0</v>
-      </c>
-      <c r="E189" s="12">
+      <c r="C189" s="8">
+        <v>0</v>
+      </c>
+      <c r="E189" s="10">
         <f t="shared" si="17"/>
         <v>6827</v>
       </c>
-      <c r="F189" s="13">
+      <c r="F189" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="5">
+      <c r="A190" s="4">
         <f t="shared" si="16"/>
         <v>189</v>
       </c>
-      <c r="B190" s="10">
+      <c r="B190" s="8">
         <f t="shared" si="19"/>
         <v>82</v>
       </c>
-      <c r="C190" s="10">
-        <v>0</v>
-      </c>
-      <c r="E190" s="12">
+      <c r="C190" s="8">
+        <v>0</v>
+      </c>
+      <c r="E190" s="10">
         <f t="shared" si="17"/>
         <v>6909</v>
       </c>
-      <c r="F190" s="13">
+      <c r="F190" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="5">
+      <c r="A191" s="4">
         <f t="shared" si="16"/>
         <v>190</v>
       </c>
-      <c r="B191" s="10">
+      <c r="B191" s="8">
         <f t="shared" si="19"/>
         <v>82</v>
       </c>
-      <c r="C191" s="10">
-        <v>0</v>
-      </c>
-      <c r="E191" s="12">
+      <c r="C191" s="8">
+        <v>0</v>
+      </c>
+      <c r="E191" s="10">
         <f t="shared" si="17"/>
         <v>6991</v>
       </c>
-      <c r="F191" s="13">
+      <c r="F191" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="5">
+      <c r="A192" s="4">
         <f t="shared" si="16"/>
         <v>191</v>
       </c>
-      <c r="B192" s="10">
+      <c r="B192" s="8">
         <f t="shared" si="19"/>
         <v>83</v>
       </c>
-      <c r="C192" s="10">
-        <v>0</v>
-      </c>
-      <c r="E192" s="12">
+      <c r="C192" s="8">
+        <v>0</v>
+      </c>
+      <c r="E192" s="10">
         <f t="shared" si="17"/>
         <v>7074</v>
       </c>
-      <c r="F192" s="13">
+      <c r="F192" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="5">
+      <c r="A193" s="4">
         <f t="shared" si="16"/>
         <v>192</v>
       </c>
-      <c r="B193" s="10">
+      <c r="B193" s="8">
         <f t="shared" si="19"/>
         <v>83</v>
       </c>
-      <c r="C193" s="10">
-        <v>0</v>
-      </c>
-      <c r="E193" s="12">
+      <c r="C193" s="8">
+        <v>0</v>
+      </c>
+      <c r="E193" s="10">
         <f t="shared" si="17"/>
         <v>7157</v>
       </c>
-      <c r="F193" s="13">
+      <c r="F193" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="5">
+      <c r="A194" s="4">
         <f t="shared" si="16"/>
         <v>193</v>
       </c>
-      <c r="B194" s="10">
+      <c r="B194" s="8">
         <f t="shared" si="19"/>
         <v>84</v>
       </c>
-      <c r="C194" s="10">
-        <v>0</v>
-      </c>
-      <c r="E194" s="12">
+      <c r="C194" s="8">
+        <v>0</v>
+      </c>
+      <c r="E194" s="10">
         <f t="shared" si="17"/>
         <v>7241</v>
       </c>
-      <c r="F194" s="13">
+      <c r="F194" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="5">
+      <c r="A195" s="4">
         <f t="shared" si="16"/>
         <v>194</v>
       </c>
-      <c r="B195" s="10">
+      <c r="B195" s="8">
         <f t="shared" si="19"/>
         <v>84</v>
       </c>
-      <c r="C195" s="10">
-        <v>0</v>
-      </c>
-      <c r="E195" s="12">
+      <c r="C195" s="8">
+        <v>0</v>
+      </c>
+      <c r="E195" s="10">
         <f t="shared" si="17"/>
         <v>7325</v>
       </c>
-      <c r="F195" s="13">
+      <c r="F195" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="5">
+      <c r="A196" s="4">
         <f t="shared" si="16"/>
         <v>195</v>
       </c>
-      <c r="B196" s="10">
+      <c r="B196" s="8">
         <f t="shared" si="19"/>
         <v>85</v>
       </c>
-      <c r="C196" s="10">
-        <v>0</v>
-      </c>
-      <c r="E196" s="12">
+      <c r="C196" s="8">
+        <v>0</v>
+      </c>
+      <c r="E196" s="10">
         <f t="shared" si="17"/>
         <v>7410</v>
       </c>
-      <c r="F196" s="13">
+      <c r="F196" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="5">
+      <c r="A197" s="4">
         <f t="shared" si="16"/>
         <v>196</v>
       </c>
-      <c r="B197" s="10">
+      <c r="B197" s="8">
         <f t="shared" si="19"/>
         <v>85</v>
       </c>
-      <c r="C197" s="10">
-        <v>0</v>
-      </c>
-      <c r="E197" s="12">
+      <c r="C197" s="8">
+        <v>0</v>
+      </c>
+      <c r="E197" s="10">
         <f t="shared" si="17"/>
         <v>7495</v>
       </c>
-      <c r="F197" s="13">
+      <c r="F197" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="5">
+      <c r="A198" s="4">
         <f t="shared" si="16"/>
         <v>197</v>
       </c>
-      <c r="B198" s="10">
+      <c r="B198" s="8">
         <f t="shared" si="19"/>
         <v>86</v>
       </c>
-      <c r="C198" s="10">
-        <v>0</v>
-      </c>
-      <c r="E198" s="12">
+      <c r="C198" s="8">
+        <v>0</v>
+      </c>
+      <c r="E198" s="10">
         <f t="shared" si="17"/>
         <v>7581</v>
       </c>
-      <c r="F198" s="13">
+      <c r="F198" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="5">
+      <c r="A199" s="4">
         <f t="shared" si="16"/>
         <v>198</v>
       </c>
-      <c r="B199" s="10">
+      <c r="B199" s="8">
         <f t="shared" si="19"/>
         <v>86</v>
       </c>
-      <c r="C199" s="10">
-        <v>0</v>
-      </c>
-      <c r="E199" s="12">
+      <c r="C199" s="8">
+        <v>0</v>
+      </c>
+      <c r="E199" s="10">
         <f t="shared" si="17"/>
         <v>7667</v>
       </c>
-      <c r="F199" s="13">
+      <c r="F199" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="5">
+      <c r="A200" s="4">
         <f t="shared" si="16"/>
         <v>199</v>
       </c>
-      <c r="B200" s="10">
+      <c r="B200" s="8">
         <f t="shared" si="19"/>
         <v>87</v>
       </c>
-      <c r="C200" s="10">
-        <v>0</v>
-      </c>
-      <c r="E200" s="12">
+      <c r="C200" s="8">
+        <v>0</v>
+      </c>
+      <c r="E200" s="10">
         <f t="shared" si="17"/>
         <v>7754</v>
       </c>
-      <c r="F200" s="13">
+      <c r="F200" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" s="5">
+      <c r="A201" s="4">
         <f t="shared" si="16"/>
         <v>200</v>
       </c>
-      <c r="B201" s="10">
+      <c r="B201" s="8">
         <f t="shared" si="19"/>
         <v>87</v>
       </c>
-      <c r="C201" s="10">
-        <v>0</v>
-      </c>
-      <c r="E201" s="12">
+      <c r="C201" s="8">
+        <v>0</v>
+      </c>
+      <c r="E201" s="10">
         <f t="shared" si="17"/>
         <v>7841</v>
       </c>
-      <c r="F201" s="13">
+      <c r="F201" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A202" s="5">
+      <c r="A202" s="4">
         <f t="shared" si="16"/>
         <v>201</v>
       </c>
-      <c r="B202" s="10">
+      <c r="B202" s="8">
         <f t="shared" si="19"/>
         <v>88</v>
       </c>
-      <c r="C202" s="10">
-        <v>0</v>
-      </c>
-      <c r="E202" s="12">
+      <c r="C202" s="8">
+        <v>0</v>
+      </c>
+      <c r="E202" s="10">
         <f t="shared" si="17"/>
         <v>7929</v>
       </c>
-      <c r="F202" s="13">
+      <c r="F202" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A203" s="5">
+      <c r="A203" s="4">
         <f t="shared" si="16"/>
         <v>202</v>
       </c>
-      <c r="B203" s="10">
+      <c r="B203" s="8">
         <f t="shared" si="19"/>
         <v>88</v>
       </c>
-      <c r="C203" s="10">
-        <v>0</v>
-      </c>
-      <c r="E203" s="12">
+      <c r="C203" s="8">
+        <v>0</v>
+      </c>
+      <c r="E203" s="10">
         <f t="shared" si="17"/>
         <v>8017</v>
       </c>
-      <c r="F203" s="13">
+      <c r="F203" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A204" s="5">
+      <c r="A204" s="4">
         <f t="shared" si="16"/>
         <v>203</v>
       </c>
-      <c r="B204" s="10">
+      <c r="B204" s="8">
         <f t="shared" si="19"/>
         <v>89</v>
       </c>
-      <c r="C204" s="10">
-        <v>0</v>
-      </c>
-      <c r="E204" s="12">
+      <c r="C204" s="8">
+        <v>0</v>
+      </c>
+      <c r="E204" s="10">
         <f t="shared" si="17"/>
         <v>8106</v>
       </c>
-      <c r="F204" s="13">
+      <c r="F204" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A205" s="5">
+      <c r="A205" s="4">
         <f t="shared" si="16"/>
         <v>204</v>
       </c>
-      <c r="B205" s="10">
+      <c r="B205" s="8">
         <f t="shared" si="19"/>
         <v>89</v>
       </c>
-      <c r="C205" s="10">
-        <v>0</v>
-      </c>
-      <c r="E205" s="12">
+      <c r="C205" s="8">
+        <v>0</v>
+      </c>
+      <c r="E205" s="10">
         <f t="shared" si="17"/>
         <v>8195</v>
       </c>
-      <c r="F205" s="13">
+      <c r="F205" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="5">
+      <c r="A206" s="4">
         <f t="shared" si="16"/>
         <v>205</v>
       </c>
-      <c r="B206" s="10">
+      <c r="B206" s="8">
         <f t="shared" si="19"/>
         <v>90</v>
       </c>
-      <c r="C206" s="10">
-        <v>0</v>
-      </c>
-      <c r="E206" s="12">
+      <c r="C206" s="8">
+        <v>0</v>
+      </c>
+      <c r="E206" s="10">
         <f t="shared" si="17"/>
         <v>8285</v>
       </c>
-      <c r="F206" s="13">
+      <c r="F206" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="5">
+      <c r="A207" s="4">
         <f t="shared" si="16"/>
         <v>206</v>
       </c>
-      <c r="B207" s="10">
+      <c r="B207" s="8">
         <f t="shared" si="19"/>
         <v>90</v>
       </c>
-      <c r="C207" s="10">
-        <v>0</v>
-      </c>
-      <c r="E207" s="12">
+      <c r="C207" s="8">
+        <v>0</v>
+      </c>
+      <c r="E207" s="10">
         <f t="shared" si="17"/>
         <v>8375</v>
       </c>
-      <c r="F207" s="13">
+      <c r="F207" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="5">
+      <c r="A208" s="4">
         <f t="shared" si="16"/>
         <v>207</v>
       </c>
-      <c r="B208" s="10">
+      <c r="B208" s="8">
         <f t="shared" si="19"/>
         <v>91</v>
       </c>
-      <c r="C208" s="10">
-        <v>0</v>
-      </c>
-      <c r="E208" s="12">
+      <c r="C208" s="8">
+        <v>0</v>
+      </c>
+      <c r="E208" s="10">
         <f t="shared" si="17"/>
         <v>8466</v>
       </c>
-      <c r="F208" s="13">
+      <c r="F208" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209" s="5">
+      <c r="A209" s="4">
         <f t="shared" si="16"/>
         <v>208</v>
       </c>
-      <c r="B209" s="10">
+      <c r="B209" s="8">
         <f t="shared" si="19"/>
         <v>91</v>
       </c>
-      <c r="C209" s="10">
-        <v>0</v>
-      </c>
-      <c r="E209" s="12">
+      <c r="C209" s="8">
+        <v>0</v>
+      </c>
+      <c r="E209" s="10">
         <f t="shared" si="17"/>
         <v>8557</v>
       </c>
-      <c r="F209" s="13">
+      <c r="F209" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210" s="5">
+      <c r="A210" s="4">
         <f t="shared" si="16"/>
         <v>209</v>
       </c>
-      <c r="B210" s="10">
+      <c r="B210" s="8">
         <f t="shared" si="19"/>
         <v>92</v>
       </c>
-      <c r="C210" s="10">
-        <v>0</v>
-      </c>
-      <c r="E210" s="12">
+      <c r="C210" s="8">
+        <v>0</v>
+      </c>
+      <c r="E210" s="10">
         <f t="shared" si="17"/>
         <v>8649</v>
       </c>
-      <c r="F210" s="13">
+      <c r="F210" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A211" s="5">
+      <c r="A211" s="4">
         <f t="shared" si="16"/>
         <v>210</v>
       </c>
-      <c r="B211" s="10">
+      <c r="B211" s="8">
         <f t="shared" si="19"/>
         <v>92</v>
       </c>
-      <c r="C211" s="10">
-        <v>0</v>
-      </c>
-      <c r="E211" s="12">
+      <c r="C211" s="8">
+        <v>0</v>
+      </c>
+      <c r="E211" s="10">
         <f t="shared" si="17"/>
         <v>8741</v>
       </c>
-      <c r="F211" s="13">
+      <c r="F211" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="5">
+      <c r="A212" s="4">
         <f t="shared" si="16"/>
         <v>211</v>
       </c>
-      <c r="B212" s="10">
+      <c r="B212" s="8">
         <f t="shared" si="19"/>
         <v>93</v>
       </c>
-      <c r="C212" s="10">
-        <v>0</v>
-      </c>
-      <c r="E212" s="12">
+      <c r="C212" s="8">
+        <v>0</v>
+      </c>
+      <c r="E212" s="10">
         <f t="shared" si="17"/>
         <v>8834</v>
       </c>
-      <c r="F212" s="13">
+      <c r="F212" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A213" s="5">
+      <c r="A213" s="4">
         <f t="shared" si="16"/>
         <v>212</v>
       </c>
-      <c r="B213" s="10">
+      <c r="B213" s="8">
         <f t="shared" si="19"/>
         <v>93</v>
       </c>
-      <c r="C213" s="10">
-        <v>0</v>
-      </c>
-      <c r="E213" s="12">
+      <c r="C213" s="8">
+        <v>0</v>
+      </c>
+      <c r="E213" s="10">
         <f t="shared" si="17"/>
         <v>8927</v>
       </c>
-      <c r="F213" s="13">
+      <c r="F213" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A214" s="5">
+      <c r="A214" s="4">
         <f t="shared" si="16"/>
         <v>213</v>
       </c>
-      <c r="B214" s="10">
+      <c r="B214" s="8">
         <f t="shared" si="19"/>
         <v>94</v>
       </c>
-      <c r="C214" s="10">
-        <v>0</v>
-      </c>
-      <c r="E214" s="12">
+      <c r="C214" s="8">
+        <v>0</v>
+      </c>
+      <c r="E214" s="10">
         <f t="shared" si="17"/>
         <v>9021</v>
       </c>
-      <c r="F214" s="13">
+      <c r="F214" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A215" s="5">
+      <c r="A215" s="4">
         <f t="shared" si="16"/>
         <v>214</v>
       </c>
-      <c r="B215" s="10">
+      <c r="B215" s="8">
         <f t="shared" si="19"/>
         <v>94</v>
       </c>
-      <c r="C215" s="10">
-        <v>0</v>
-      </c>
-      <c r="E215" s="12">
+      <c r="C215" s="8">
+        <v>0</v>
+      </c>
+      <c r="E215" s="10">
         <f t="shared" si="17"/>
         <v>9115</v>
       </c>
-      <c r="F215" s="13">
+      <c r="F215" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="5">
+      <c r="A216" s="4">
         <f t="shared" si="16"/>
         <v>215</v>
       </c>
-      <c r="B216" s="10">
+      <c r="B216" s="8">
         <f t="shared" si="19"/>
         <v>95</v>
       </c>
-      <c r="C216" s="10">
-        <v>0</v>
-      </c>
-      <c r="E216" s="12">
+      <c r="C216" s="8">
+        <v>0</v>
+      </c>
+      <c r="E216" s="10">
         <f t="shared" si="17"/>
         <v>9210</v>
       </c>
-      <c r="F216" s="13">
+      <c r="F216" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A217" s="5">
+      <c r="A217" s="4">
         <f t="shared" si="16"/>
         <v>216</v>
       </c>
-      <c r="B217" s="10">
+      <c r="B217" s="8">
         <f t="shared" si="19"/>
         <v>95</v>
       </c>
-      <c r="C217" s="10">
-        <v>0</v>
-      </c>
-      <c r="E217" s="12">
+      <c r="C217" s="8">
+        <v>0</v>
+      </c>
+      <c r="E217" s="10">
         <f t="shared" si="17"/>
         <v>9305</v>
       </c>
-      <c r="F217" s="13">
+      <c r="F217" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="5">
+      <c r="A218" s="4">
         <f t="shared" si="16"/>
         <v>217</v>
       </c>
-      <c r="B218" s="10">
+      <c r="B218" s="8">
         <f t="shared" si="19"/>
         <v>96</v>
       </c>
-      <c r="C218" s="10">
-        <v>0</v>
-      </c>
-      <c r="E218" s="12">
+      <c r="C218" s="8">
+        <v>0</v>
+      </c>
+      <c r="E218" s="10">
         <f t="shared" si="17"/>
         <v>9401</v>
       </c>
-      <c r="F218" s="13">
+      <c r="F218" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="5">
+      <c r="A219" s="4">
         <f t="shared" si="16"/>
         <v>218</v>
       </c>
-      <c r="B219" s="10">
+      <c r="B219" s="8">
         <f t="shared" si="19"/>
         <v>96</v>
       </c>
-      <c r="C219" s="10">
-        <v>0</v>
-      </c>
-      <c r="E219" s="12">
+      <c r="C219" s="8">
+        <v>0</v>
+      </c>
+      <c r="E219" s="10">
         <f t="shared" si="17"/>
         <v>9497</v>
       </c>
-      <c r="F219" s="13">
+      <c r="F219" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A220" s="5">
+      <c r="A220" s="4">
         <f t="shared" si="16"/>
         <v>219</v>
       </c>
-      <c r="B220" s="10">
+      <c r="B220" s="8">
         <f t="shared" si="19"/>
         <v>97</v>
       </c>
-      <c r="C220" s="10">
-        <v>0</v>
-      </c>
-      <c r="E220" s="12">
+      <c r="C220" s="8">
+        <v>0</v>
+      </c>
+      <c r="E220" s="10">
         <f t="shared" si="17"/>
         <v>9594</v>
       </c>
-      <c r="F220" s="13">
+      <c r="F220" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A221" s="5">
+      <c r="A221" s="4">
         <f t="shared" si="16"/>
         <v>220</v>
       </c>
-      <c r="B221" s="10">
+      <c r="B221" s="8">
         <f t="shared" si="19"/>
         <v>97</v>
       </c>
-      <c r="C221" s="10">
-        <v>0</v>
-      </c>
-      <c r="E221" s="12">
+      <c r="C221" s="8">
+        <v>0</v>
+      </c>
+      <c r="E221" s="10">
         <f t="shared" si="17"/>
         <v>9691</v>
       </c>
-      <c r="F221" s="13">
+      <c r="F221" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A222" s="5">
-        <f t="shared" ref="A222:B285" si="20">A221+1</f>
+      <c r="A222" s="4">
+        <f t="shared" ref="A222:A285" si="20">A221+1</f>
         <v>221</v>
       </c>
-      <c r="B222" s="10">
+      <c r="B222" s="8">
         <f t="shared" si="19"/>
         <v>98</v>
       </c>
-      <c r="C222" s="10">
-        <v>0</v>
-      </c>
-      <c r="E222" s="12">
+      <c r="C222" s="8">
+        <v>0</v>
+      </c>
+      <c r="E222" s="10">
         <f t="shared" si="17"/>
         <v>9789</v>
       </c>
-      <c r="F222" s="13">
+      <c r="F222" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A223" s="5">
+      <c r="A223" s="4">
         <f t="shared" si="20"/>
         <v>222</v>
       </c>
-      <c r="B223" s="10">
+      <c r="B223" s="8">
         <f t="shared" si="19"/>
         <v>98</v>
       </c>
-      <c r="C223" s="10">
-        <v>0</v>
-      </c>
-      <c r="E223" s="12">
+      <c r="C223" s="8">
+        <v>0</v>
+      </c>
+      <c r="E223" s="10">
         <f t="shared" si="17"/>
         <v>9887</v>
       </c>
-      <c r="F223" s="13">
+      <c r="F223" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A224" s="5">
+      <c r="A224" s="4">
         <f t="shared" si="20"/>
         <v>223</v>
       </c>
-      <c r="B224" s="10">
+      <c r="B224" s="8">
         <f t="shared" si="19"/>
         <v>99</v>
       </c>
-      <c r="C224" s="10">
-        <v>0</v>
-      </c>
-      <c r="E224" s="12">
+      <c r="C224" s="8">
+        <v>0</v>
+      </c>
+      <c r="E224" s="10">
         <f t="shared" si="17"/>
         <v>9986</v>
       </c>
-      <c r="F224" s="13">
+      <c r="F224" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A225" s="5">
+      <c r="A225" s="4">
         <f t="shared" si="20"/>
         <v>224</v>
       </c>
-      <c r="B225" s="10">
+      <c r="B225" s="8">
         <f t="shared" si="19"/>
         <v>99</v>
       </c>
-      <c r="C225" s="10">
-        <v>0</v>
-      </c>
-      <c r="E225" s="12">
+      <c r="C225" s="8">
+        <v>0</v>
+      </c>
+      <c r="E225" s="10">
         <f t="shared" si="17"/>
         <v>10085</v>
       </c>
-      <c r="F225" s="13">
+      <c r="F225" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" s="5">
+      <c r="A226" s="4">
         <f t="shared" si="20"/>
         <v>225</v>
       </c>
-      <c r="B226" s="10">
+      <c r="B226" s="8">
         <f t="shared" si="19"/>
         <v>100</v>
       </c>
-      <c r="C226" s="10">
-        <v>0</v>
-      </c>
-      <c r="E226" s="12">
+      <c r="C226" s="8">
+        <v>0</v>
+      </c>
+      <c r="E226" s="10">
         <f t="shared" si="17"/>
         <v>10185</v>
       </c>
-      <c r="F226" s="13">
+      <c r="F226" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A227" s="5">
+      <c r="A227" s="4">
         <f t="shared" si="20"/>
         <v>226</v>
       </c>
-      <c r="B227" s="10">
+      <c r="B227" s="8">
         <f t="shared" si="19"/>
         <v>100</v>
       </c>
-      <c r="C227" s="10">
-        <v>0</v>
-      </c>
-      <c r="E227" s="12">
+      <c r="C227" s="8">
+        <v>0</v>
+      </c>
+      <c r="E227" s="10">
         <f t="shared" si="17"/>
         <v>10285</v>
       </c>
-      <c r="F227" s="13">
+      <c r="F227" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A228" s="5">
+      <c r="A228" s="4">
         <f t="shared" si="20"/>
         <v>227</v>
       </c>
-      <c r="B228" s="10">
-        <v>100</v>
-      </c>
-      <c r="C228" s="10">
-        <v>0</v>
-      </c>
-      <c r="E228" s="12">
+      <c r="B228" s="8">
+        <v>100</v>
+      </c>
+      <c r="C228" s="8">
+        <v>0</v>
+      </c>
+      <c r="E228" s="10">
         <f t="shared" si="17"/>
         <v>10385</v>
       </c>
-      <c r="F228" s="13">
+      <c r="F228" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A229" s="5">
+      <c r="A229" s="4">
         <f t="shared" si="20"/>
         <v>228</v>
       </c>
-      <c r="B229" s="10">
-        <v>100</v>
-      </c>
-      <c r="C229" s="10">
-        <v>0</v>
-      </c>
-      <c r="E229" s="12">
+      <c r="B229" s="8">
+        <v>100</v>
+      </c>
+      <c r="C229" s="8">
+        <v>0</v>
+      </c>
+      <c r="E229" s="10">
         <f t="shared" ref="E229:E292" si="21">E228+B229</f>
         <v>10485</v>
       </c>
-      <c r="F229" s="13">
+      <c r="F229" s="11">
         <f t="shared" ref="F229:F292" si="22">B229-B228</f>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A230" s="5">
+      <c r="A230" s="4">
         <f t="shared" si="20"/>
         <v>229</v>
       </c>
-      <c r="B230" s="10">
-        <v>100</v>
-      </c>
-      <c r="C230" s="10">
-        <v>0</v>
-      </c>
-      <c r="E230" s="12">
+      <c r="B230" s="8">
+        <v>100</v>
+      </c>
+      <c r="C230" s="8">
+        <v>0</v>
+      </c>
+      <c r="E230" s="10">
         <f t="shared" si="21"/>
         <v>10585</v>
       </c>
-      <c r="F230" s="13">
+      <c r="F230" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A231" s="5">
+      <c r="A231" s="4">
         <f t="shared" si="20"/>
         <v>230</v>
       </c>
-      <c r="B231" s="10">
-        <v>100</v>
-      </c>
-      <c r="C231" s="10">
-        <v>0</v>
-      </c>
-      <c r="E231" s="12">
+      <c r="B231" s="8">
+        <v>100</v>
+      </c>
+      <c r="C231" s="8">
+        <v>0</v>
+      </c>
+      <c r="E231" s="10">
         <f t="shared" si="21"/>
         <v>10685</v>
       </c>
-      <c r="F231" s="13">
+      <c r="F231" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A232" s="5">
+      <c r="A232" s="4">
         <f t="shared" si="20"/>
         <v>231</v>
       </c>
-      <c r="B232" s="10">
-        <v>100</v>
-      </c>
-      <c r="C232" s="10">
-        <v>0</v>
-      </c>
-      <c r="E232" s="12">
+      <c r="B232" s="8">
+        <v>100</v>
+      </c>
+      <c r="C232" s="8">
+        <v>0</v>
+      </c>
+      <c r="E232" s="10">
         <f t="shared" si="21"/>
         <v>10785</v>
       </c>
-      <c r="F232" s="13">
+      <c r="F232" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A233" s="5">
+      <c r="A233" s="4">
         <f t="shared" si="20"/>
         <v>232</v>
       </c>
-      <c r="B233" s="10">
-        <v>100</v>
-      </c>
-      <c r="C233" s="10">
-        <v>0</v>
-      </c>
-      <c r="E233" s="12">
+      <c r="B233" s="8">
+        <v>100</v>
+      </c>
+      <c r="C233" s="8">
+        <v>0</v>
+      </c>
+      <c r="E233" s="10">
         <f t="shared" si="21"/>
         <v>10885</v>
       </c>
-      <c r="F233" s="13">
+      <c r="F233" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A234" s="5">
+      <c r="A234" s="4">
         <f t="shared" si="20"/>
         <v>233</v>
       </c>
-      <c r="B234" s="10">
-        <v>100</v>
-      </c>
-      <c r="C234" s="10">
-        <v>0</v>
-      </c>
-      <c r="E234" s="12">
+      <c r="B234" s="8">
+        <v>100</v>
+      </c>
+      <c r="C234" s="8">
+        <v>0</v>
+      </c>
+      <c r="E234" s="10">
         <f t="shared" si="21"/>
         <v>10985</v>
       </c>
-      <c r="F234" s="13">
+      <c r="F234" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A235" s="5">
+      <c r="A235" s="4">
         <f t="shared" si="20"/>
         <v>234</v>
       </c>
-      <c r="B235" s="10">
-        <v>100</v>
-      </c>
-      <c r="C235" s="10">
-        <v>0</v>
-      </c>
-      <c r="E235" s="12">
+      <c r="B235" s="8">
+        <v>100</v>
+      </c>
+      <c r="C235" s="8">
+        <v>0</v>
+      </c>
+      <c r="E235" s="10">
         <f t="shared" si="21"/>
         <v>11085</v>
       </c>
-      <c r="F235" s="13">
+      <c r="F235" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A236" s="5">
+      <c r="A236" s="4">
         <f t="shared" si="20"/>
         <v>235</v>
       </c>
-      <c r="B236" s="10">
-        <v>100</v>
-      </c>
-      <c r="C236" s="10">
-        <v>0</v>
-      </c>
-      <c r="E236" s="12">
+      <c r="B236" s="8">
+        <v>100</v>
+      </c>
+      <c r="C236" s="8">
+        <v>0</v>
+      </c>
+      <c r="E236" s="10">
         <f t="shared" si="21"/>
         <v>11185</v>
       </c>
-      <c r="F236" s="13">
+      <c r="F236" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A237" s="5">
+      <c r="A237" s="4">
         <f t="shared" si="20"/>
         <v>236</v>
       </c>
-      <c r="B237" s="10">
-        <v>100</v>
-      </c>
-      <c r="C237" s="10">
-        <v>0</v>
-      </c>
-      <c r="E237" s="12">
+      <c r="B237" s="8">
+        <v>100</v>
+      </c>
+      <c r="C237" s="8">
+        <v>0</v>
+      </c>
+      <c r="E237" s="10">
         <f t="shared" si="21"/>
         <v>11285</v>
       </c>
-      <c r="F237" s="13">
+      <c r="F237" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A238" s="5">
+      <c r="A238" s="4">
         <f t="shared" si="20"/>
         <v>237</v>
       </c>
-      <c r="B238" s="10">
-        <v>100</v>
-      </c>
-      <c r="C238" s="10">
-        <v>0</v>
-      </c>
-      <c r="E238" s="12">
+      <c r="B238" s="8">
+        <v>100</v>
+      </c>
+      <c r="C238" s="8">
+        <v>0</v>
+      </c>
+      <c r="E238" s="10">
         <f t="shared" si="21"/>
         <v>11385</v>
       </c>
-      <c r="F238" s="13">
+      <c r="F238" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A239" s="5">
+      <c r="A239" s="4">
         <f t="shared" si="20"/>
         <v>238</v>
       </c>
-      <c r="B239" s="10">
-        <v>100</v>
-      </c>
-      <c r="C239" s="10">
-        <v>0</v>
-      </c>
-      <c r="E239" s="12">
+      <c r="B239" s="8">
+        <v>100</v>
+      </c>
+      <c r="C239" s="8">
+        <v>0</v>
+      </c>
+      <c r="E239" s="10">
         <f t="shared" si="21"/>
         <v>11485</v>
       </c>
-      <c r="F239" s="13">
+      <c r="F239" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A240" s="5">
+      <c r="A240" s="4">
         <f t="shared" si="20"/>
         <v>239</v>
       </c>
-      <c r="B240" s="10">
-        <v>100</v>
-      </c>
-      <c r="C240" s="10">
-        <v>0</v>
-      </c>
-      <c r="E240" s="12">
+      <c r="B240" s="8">
+        <v>100</v>
+      </c>
+      <c r="C240" s="8">
+        <v>0</v>
+      </c>
+      <c r="E240" s="10">
         <f t="shared" si="21"/>
         <v>11585</v>
       </c>
-      <c r="F240" s="13">
+      <c r="F240" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A241" s="5">
+      <c r="A241" s="4">
         <f t="shared" si="20"/>
         <v>240</v>
       </c>
-      <c r="B241" s="10">
-        <v>100</v>
-      </c>
-      <c r="C241" s="10">
-        <v>0</v>
-      </c>
-      <c r="E241" s="12">
+      <c r="B241" s="8">
+        <v>100</v>
+      </c>
+      <c r="C241" s="8">
+        <v>0</v>
+      </c>
+      <c r="E241" s="10">
         <f t="shared" si="21"/>
         <v>11685</v>
       </c>
-      <c r="F241" s="13">
+      <c r="F241" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A242" s="5">
+      <c r="A242" s="4">
         <f t="shared" si="20"/>
         <v>241</v>
       </c>
-      <c r="B242" s="10">
-        <v>100</v>
-      </c>
-      <c r="C242" s="10">
-        <v>0</v>
-      </c>
-      <c r="E242" s="12">
+      <c r="B242" s="8">
+        <v>100</v>
+      </c>
+      <c r="C242" s="8">
+        <v>0</v>
+      </c>
+      <c r="E242" s="10">
         <f t="shared" si="21"/>
         <v>11785</v>
       </c>
-      <c r="F242" s="13">
+      <c r="F242" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A243" s="5">
+      <c r="A243" s="4">
         <f t="shared" si="20"/>
         <v>242</v>
       </c>
-      <c r="B243" s="10">
-        <v>100</v>
-      </c>
-      <c r="C243" s="10">
-        <v>0</v>
-      </c>
-      <c r="E243" s="12">
+      <c r="B243" s="8">
+        <v>100</v>
+      </c>
+      <c r="C243" s="8">
+        <v>0</v>
+      </c>
+      <c r="E243" s="10">
         <f t="shared" si="21"/>
         <v>11885</v>
       </c>
-      <c r="F243" s="13">
+      <c r="F243" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A244" s="5">
+      <c r="A244" s="4">
         <f t="shared" si="20"/>
         <v>243</v>
       </c>
-      <c r="B244" s="10">
-        <v>100</v>
-      </c>
-      <c r="C244" s="10">
-        <v>0</v>
-      </c>
-      <c r="E244" s="12">
+      <c r="B244" s="8">
+        <v>100</v>
+      </c>
+      <c r="C244" s="8">
+        <v>0</v>
+      </c>
+      <c r="E244" s="10">
         <f t="shared" si="21"/>
         <v>11985</v>
       </c>
-      <c r="F244" s="13">
+      <c r="F244" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A245" s="5">
+      <c r="A245" s="4">
         <f t="shared" si="20"/>
         <v>244</v>
       </c>
-      <c r="B245" s="10">
-        <v>100</v>
-      </c>
-      <c r="C245" s="10">
-        <v>0</v>
-      </c>
-      <c r="E245" s="12">
+      <c r="B245" s="8">
+        <v>100</v>
+      </c>
+      <c r="C245" s="8">
+        <v>0</v>
+      </c>
+      <c r="E245" s="10">
         <f t="shared" si="21"/>
         <v>12085</v>
       </c>
-      <c r="F245" s="13">
+      <c r="F245" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A246" s="5">
+      <c r="A246" s="4">
         <f t="shared" si="20"/>
         <v>245</v>
       </c>
-      <c r="B246" s="10">
-        <v>100</v>
-      </c>
-      <c r="C246" s="10">
-        <v>0</v>
-      </c>
-      <c r="E246" s="12">
+      <c r="B246" s="8">
+        <v>100</v>
+      </c>
+      <c r="C246" s="8">
+        <v>0</v>
+      </c>
+      <c r="E246" s="10">
         <f t="shared" si="21"/>
         <v>12185</v>
       </c>
-      <c r="F246" s="13">
+      <c r="F246" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" s="5">
+      <c r="A247" s="4">
         <f t="shared" si="20"/>
         <v>246</v>
       </c>
-      <c r="B247" s="10">
-        <v>100</v>
-      </c>
-      <c r="C247" s="10">
-        <v>0</v>
-      </c>
-      <c r="E247" s="12">
+      <c r="B247" s="8">
+        <v>100</v>
+      </c>
+      <c r="C247" s="8">
+        <v>0</v>
+      </c>
+      <c r="E247" s="10">
         <f t="shared" si="21"/>
         <v>12285</v>
       </c>
-      <c r="F247" s="13">
+      <c r="F247" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A248" s="5">
+      <c r="A248" s="4">
         <f t="shared" si="20"/>
         <v>247</v>
       </c>
-      <c r="B248" s="10">
-        <v>100</v>
-      </c>
-      <c r="C248" s="10">
-        <v>0</v>
-      </c>
-      <c r="E248" s="12">
+      <c r="B248" s="8">
+        <v>100</v>
+      </c>
+      <c r="C248" s="8">
+        <v>0</v>
+      </c>
+      <c r="E248" s="10">
         <f t="shared" si="21"/>
         <v>12385</v>
       </c>
-      <c r="F248" s="13">
+      <c r="F248" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A249" s="5">
+      <c r="A249" s="4">
         <f t="shared" si="20"/>
         <v>248</v>
       </c>
-      <c r="B249" s="10">
-        <v>100</v>
-      </c>
-      <c r="C249" s="10">
-        <v>0</v>
-      </c>
-      <c r="E249" s="12">
+      <c r="B249" s="8">
+        <v>100</v>
+      </c>
+      <c r="C249" s="8">
+        <v>0</v>
+      </c>
+      <c r="E249" s="10">
         <f t="shared" si="21"/>
         <v>12485</v>
       </c>
-      <c r="F249" s="13">
+      <c r="F249" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A250" s="5">
+      <c r="A250" s="4">
         <f t="shared" si="20"/>
         <v>249</v>
       </c>
-      <c r="B250" s="10">
-        <v>100</v>
-      </c>
-      <c r="C250" s="10">
-        <v>0</v>
-      </c>
-      <c r="E250" s="12">
+      <c r="B250" s="8">
+        <v>100</v>
+      </c>
+      <c r="C250" s="8">
+        <v>0</v>
+      </c>
+      <c r="E250" s="10">
         <f t="shared" si="21"/>
         <v>12585</v>
       </c>
-      <c r="F250" s="13">
+      <c r="F250" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A251" s="5">
+      <c r="A251" s="4">
         <f t="shared" si="20"/>
         <v>250</v>
       </c>
-      <c r="B251" s="10">
-        <v>100</v>
-      </c>
-      <c r="C251" s="10">
-        <v>0</v>
-      </c>
-      <c r="E251" s="12">
+      <c r="B251" s="8">
+        <v>100</v>
+      </c>
+      <c r="C251" s="8">
+        <v>0</v>
+      </c>
+      <c r="E251" s="10">
         <f t="shared" si="21"/>
         <v>12685</v>
       </c>
-      <c r="F251" s="13">
+      <c r="F251" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A252" s="5">
+      <c r="A252" s="4">
         <f t="shared" si="20"/>
         <v>251</v>
       </c>
-      <c r="B252" s="10">
-        <v>100</v>
-      </c>
-      <c r="C252" s="10">
-        <v>0</v>
-      </c>
-      <c r="E252" s="12">
+      <c r="B252" s="8">
+        <v>100</v>
+      </c>
+      <c r="C252" s="8">
+        <v>0</v>
+      </c>
+      <c r="E252" s="10">
         <f t="shared" si="21"/>
         <v>12785</v>
       </c>
-      <c r="F252" s="13">
+      <c r="F252" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A253" s="5">
+      <c r="A253" s="4">
         <f t="shared" si="20"/>
         <v>252</v>
       </c>
-      <c r="B253" s="10">
-        <v>100</v>
-      </c>
-      <c r="C253" s="10">
-        <v>0</v>
-      </c>
-      <c r="E253" s="12">
+      <c r="B253" s="8">
+        <v>100</v>
+      </c>
+      <c r="C253" s="8">
+        <v>0</v>
+      </c>
+      <c r="E253" s="10">
         <f t="shared" si="21"/>
         <v>12885</v>
       </c>
-      <c r="F253" s="13">
+      <c r="F253" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A254" s="5">
+      <c r="A254" s="4">
         <f t="shared" si="20"/>
         <v>253</v>
       </c>
-      <c r="B254" s="10">
-        <v>100</v>
-      </c>
-      <c r="C254" s="10">
-        <v>0</v>
-      </c>
-      <c r="E254" s="12">
+      <c r="B254" s="8">
+        <v>100</v>
+      </c>
+      <c r="C254" s="8">
+        <v>0</v>
+      </c>
+      <c r="E254" s="10">
         <f t="shared" si="21"/>
         <v>12985</v>
       </c>
-      <c r="F254" s="13">
+      <c r="F254" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="5">
+      <c r="A255" s="4">
         <f t="shared" si="20"/>
         <v>254</v>
       </c>
-      <c r="B255" s="10">
-        <v>100</v>
-      </c>
-      <c r="C255" s="10">
-        <v>0</v>
-      </c>
-      <c r="E255" s="12">
+      <c r="B255" s="8">
+        <v>100</v>
+      </c>
+      <c r="C255" s="8">
+        <v>0</v>
+      </c>
+      <c r="E255" s="10">
         <f t="shared" si="21"/>
         <v>13085</v>
       </c>
-      <c r="F255" s="13">
+      <c r="F255" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256" s="5">
+      <c r="A256" s="4">
         <f t="shared" si="20"/>
         <v>255</v>
       </c>
-      <c r="B256" s="10">
-        <v>100</v>
-      </c>
-      <c r="C256" s="10">
-        <v>0</v>
-      </c>
-      <c r="E256" s="12">
+      <c r="B256" s="8">
+        <v>100</v>
+      </c>
+      <c r="C256" s="8">
+        <v>0</v>
+      </c>
+      <c r="E256" s="10">
         <f t="shared" si="21"/>
         <v>13185</v>
       </c>
-      <c r="F256" s="13">
+      <c r="F256" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A257" s="5">
+      <c r="A257" s="4">
         <f t="shared" si="20"/>
         <v>256</v>
       </c>
-      <c r="B257" s="10">
-        <v>100</v>
-      </c>
-      <c r="C257" s="10">
-        <v>0</v>
-      </c>
-      <c r="E257" s="12">
+      <c r="B257" s="8">
+        <v>100</v>
+      </c>
+      <c r="C257" s="8">
+        <v>0</v>
+      </c>
+      <c r="E257" s="10">
         <f t="shared" si="21"/>
         <v>13285</v>
       </c>
-      <c r="F257" s="13">
+      <c r="F257" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258" s="5">
+      <c r="A258" s="4">
         <f t="shared" si="20"/>
         <v>257</v>
       </c>
-      <c r="B258" s="10">
-        <v>100</v>
-      </c>
-      <c r="C258" s="10">
-        <v>0</v>
-      </c>
-      <c r="E258" s="12">
+      <c r="B258" s="8">
+        <v>100</v>
+      </c>
+      <c r="C258" s="8">
+        <v>0</v>
+      </c>
+      <c r="E258" s="10">
         <f t="shared" si="21"/>
         <v>13385</v>
       </c>
-      <c r="F258" s="13">
+      <c r="F258" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A259" s="5">
+      <c r="A259" s="4">
         <f t="shared" si="20"/>
         <v>258</v>
       </c>
-      <c r="B259" s="10">
-        <v>100</v>
-      </c>
-      <c r="C259" s="10">
-        <v>0</v>
-      </c>
-      <c r="E259" s="12">
+      <c r="B259" s="8">
+        <v>100</v>
+      </c>
+      <c r="C259" s="8">
+        <v>0</v>
+      </c>
+      <c r="E259" s="10">
         <f t="shared" si="21"/>
         <v>13485</v>
       </c>
-      <c r="F259" s="13">
+      <c r="F259" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="5">
+      <c r="A260" s="4">
         <f t="shared" si="20"/>
         <v>259</v>
       </c>
-      <c r="B260" s="10">
-        <v>100</v>
-      </c>
-      <c r="C260" s="10">
-        <v>0</v>
-      </c>
-      <c r="E260" s="12">
+      <c r="B260" s="8">
+        <v>100</v>
+      </c>
+      <c r="C260" s="8">
+        <v>0</v>
+      </c>
+      <c r="E260" s="10">
         <f t="shared" si="21"/>
         <v>13585</v>
       </c>
-      <c r="F260" s="13">
+      <c r="F260" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="5">
+      <c r="A261" s="4">
         <f t="shared" si="20"/>
         <v>260</v>
       </c>
-      <c r="B261" s="10">
-        <v>100</v>
-      </c>
-      <c r="C261" s="10">
-        <v>0</v>
-      </c>
-      <c r="E261" s="12">
+      <c r="B261" s="8">
+        <v>100</v>
+      </c>
+      <c r="C261" s="8">
+        <v>0</v>
+      </c>
+      <c r="E261" s="10">
         <f t="shared" si="21"/>
         <v>13685</v>
       </c>
-      <c r="F261" s="13">
+      <c r="F261" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A262" s="5">
+      <c r="A262" s="4">
         <f t="shared" si="20"/>
         <v>261</v>
       </c>
-      <c r="B262" s="10">
-        <v>100</v>
-      </c>
-      <c r="C262" s="10">
-        <v>0</v>
-      </c>
-      <c r="E262" s="12">
+      <c r="B262" s="8">
+        <v>100</v>
+      </c>
+      <c r="C262" s="8">
+        <v>0</v>
+      </c>
+      <c r="E262" s="10">
         <f t="shared" si="21"/>
         <v>13785</v>
       </c>
-      <c r="F262" s="13">
+      <c r="F262" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A263" s="5">
+      <c r="A263" s="4">
         <f t="shared" si="20"/>
         <v>262</v>
       </c>
-      <c r="B263" s="10">
-        <v>100</v>
-      </c>
-      <c r="C263" s="10">
-        <v>0</v>
-      </c>
-      <c r="E263" s="12">
+      <c r="B263" s="8">
+        <v>100</v>
+      </c>
+      <c r="C263" s="8">
+        <v>0</v>
+      </c>
+      <c r="E263" s="10">
         <f t="shared" si="21"/>
         <v>13885</v>
       </c>
-      <c r="F263" s="13">
+      <c r="F263" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A264" s="5">
+      <c r="A264" s="4">
         <f t="shared" si="20"/>
         <v>263</v>
       </c>
-      <c r="B264" s="10">
-        <v>100</v>
-      </c>
-      <c r="C264" s="10">
-        <v>0</v>
-      </c>
-      <c r="E264" s="12">
+      <c r="B264" s="8">
+        <v>100</v>
+      </c>
+      <c r="C264" s="8">
+        <v>0</v>
+      </c>
+      <c r="E264" s="10">
         <f t="shared" si="21"/>
         <v>13985</v>
       </c>
-      <c r="F264" s="13">
+      <c r="F264" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A265" s="5">
+      <c r="A265" s="4">
         <f t="shared" si="20"/>
         <v>264</v>
       </c>
-      <c r="B265" s="10">
-        <v>100</v>
-      </c>
-      <c r="C265" s="10">
-        <v>0</v>
-      </c>
-      <c r="E265" s="12">
+      <c r="B265" s="8">
+        <v>100</v>
+      </c>
+      <c r="C265" s="8">
+        <v>0</v>
+      </c>
+      <c r="E265" s="10">
         <f t="shared" si="21"/>
         <v>14085</v>
       </c>
-      <c r="F265" s="13">
+      <c r="F265" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A266" s="5">
+      <c r="A266" s="4">
         <f t="shared" si="20"/>
         <v>265</v>
       </c>
-      <c r="B266" s="10">
-        <v>100</v>
-      </c>
-      <c r="C266" s="10">
-        <v>0</v>
-      </c>
-      <c r="E266" s="12">
+      <c r="B266" s="8">
+        <v>100</v>
+      </c>
+      <c r="C266" s="8">
+        <v>0</v>
+      </c>
+      <c r="E266" s="10">
         <f t="shared" si="21"/>
         <v>14185</v>
       </c>
-      <c r="F266" s="13">
+      <c r="F266" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A267" s="5">
+      <c r="A267" s="4">
         <f t="shared" si="20"/>
         <v>266</v>
       </c>
-      <c r="B267" s="10">
-        <v>100</v>
-      </c>
-      <c r="C267" s="10">
-        <v>0</v>
-      </c>
-      <c r="E267" s="12">
+      <c r="B267" s="8">
+        <v>100</v>
+      </c>
+      <c r="C267" s="8">
+        <v>0</v>
+      </c>
+      <c r="E267" s="10">
         <f t="shared" si="21"/>
         <v>14285</v>
       </c>
-      <c r="F267" s="13">
+      <c r="F267" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A268" s="5">
+      <c r="A268" s="4">
         <f t="shared" si="20"/>
         <v>267</v>
       </c>
-      <c r="B268" s="10">
-        <v>100</v>
-      </c>
-      <c r="C268" s="10">
-        <v>0</v>
-      </c>
-      <c r="E268" s="12">
+      <c r="B268" s="8">
+        <v>100</v>
+      </c>
+      <c r="C268" s="8">
+        <v>0</v>
+      </c>
+      <c r="E268" s="10">
         <f t="shared" si="21"/>
         <v>14385</v>
       </c>
-      <c r="F268" s="13">
+      <c r="F268" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A269" s="5">
+      <c r="A269" s="4">
         <f t="shared" si="20"/>
         <v>268</v>
       </c>
-      <c r="B269" s="10">
-        <v>100</v>
-      </c>
-      <c r="C269" s="10">
-        <v>0</v>
-      </c>
-      <c r="E269" s="12">
+      <c r="B269" s="8">
+        <v>100</v>
+      </c>
+      <c r="C269" s="8">
+        <v>0</v>
+      </c>
+      <c r="E269" s="10">
         <f t="shared" si="21"/>
         <v>14485</v>
       </c>
-      <c r="F269" s="13">
+      <c r="F269" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A270" s="5">
+      <c r="A270" s="4">
         <f t="shared" si="20"/>
         <v>269</v>
       </c>
-      <c r="B270" s="10">
-        <v>100</v>
-      </c>
-      <c r="C270" s="10">
-        <v>0</v>
-      </c>
-      <c r="E270" s="12">
+      <c r="B270" s="8">
+        <v>100</v>
+      </c>
+      <c r="C270" s="8">
+        <v>0</v>
+      </c>
+      <c r="E270" s="10">
         <f t="shared" si="21"/>
         <v>14585</v>
       </c>
-      <c r="F270" s="13">
+      <c r="F270" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A271" s="5">
+      <c r="A271" s="4">
         <f t="shared" si="20"/>
         <v>270</v>
       </c>
-      <c r="B271" s="10">
-        <v>100</v>
-      </c>
-      <c r="C271" s="10">
-        <v>0</v>
-      </c>
-      <c r="E271" s="12">
+      <c r="B271" s="8">
+        <v>100</v>
+      </c>
+      <c r="C271" s="8">
+        <v>0</v>
+      </c>
+      <c r="E271" s="10">
         <f t="shared" si="21"/>
         <v>14685</v>
       </c>
-      <c r="F271" s="13">
+      <c r="F271" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A272" s="5">
+      <c r="A272" s="4">
         <f t="shared" si="20"/>
         <v>271</v>
       </c>
-      <c r="B272" s="10">
-        <v>100</v>
-      </c>
-      <c r="C272" s="10">
-        <v>0</v>
-      </c>
-      <c r="E272" s="12">
+      <c r="B272" s="8">
+        <v>100</v>
+      </c>
+      <c r="C272" s="8">
+        <v>0</v>
+      </c>
+      <c r="E272" s="10">
         <f t="shared" si="21"/>
         <v>14785</v>
       </c>
-      <c r="F272" s="13">
+      <c r="F272" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A273" s="5">
+      <c r="A273" s="4">
         <f t="shared" si="20"/>
         <v>272</v>
       </c>
-      <c r="B273" s="10">
-        <v>100</v>
-      </c>
-      <c r="C273" s="10">
-        <v>0</v>
-      </c>
-      <c r="E273" s="12">
+      <c r="B273" s="8">
+        <v>100</v>
+      </c>
+      <c r="C273" s="8">
+        <v>0</v>
+      </c>
+      <c r="E273" s="10">
         <f t="shared" si="21"/>
         <v>14885</v>
       </c>
-      <c r="F273" s="13">
+      <c r="F273" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A274" s="5">
+      <c r="A274" s="4">
         <f t="shared" si="20"/>
         <v>273</v>
       </c>
-      <c r="B274" s="10">
-        <v>100</v>
-      </c>
-      <c r="C274" s="10">
-        <v>0</v>
-      </c>
-      <c r="E274" s="12">
+      <c r="B274" s="8">
+        <v>100</v>
+      </c>
+      <c r="C274" s="8">
+        <v>0</v>
+      </c>
+      <c r="E274" s="10">
         <f t="shared" si="21"/>
         <v>14985</v>
       </c>
-      <c r="F274" s="13">
+      <c r="F274" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A275" s="5">
+      <c r="A275" s="4">
         <f t="shared" si="20"/>
         <v>274</v>
       </c>
-      <c r="B275" s="10">
-        <v>100</v>
-      </c>
-      <c r="C275" s="10">
-        <v>0</v>
-      </c>
-      <c r="E275" s="12">
+      <c r="B275" s="8">
+        <v>100</v>
+      </c>
+      <c r="C275" s="8">
+        <v>0</v>
+      </c>
+      <c r="E275" s="10">
         <f t="shared" si="21"/>
         <v>15085</v>
       </c>
-      <c r="F275" s="13">
+      <c r="F275" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A276" s="5">
+      <c r="A276" s="4">
         <f t="shared" si="20"/>
         <v>275</v>
       </c>
-      <c r="B276" s="10">
-        <v>100</v>
-      </c>
-      <c r="C276" s="10">
-        <v>0</v>
-      </c>
-      <c r="E276" s="12">
+      <c r="B276" s="8">
+        <v>100</v>
+      </c>
+      <c r="C276" s="8">
+        <v>0</v>
+      </c>
+      <c r="E276" s="10">
         <f t="shared" si="21"/>
         <v>15185</v>
       </c>
-      <c r="F276" s="13">
+      <c r="F276" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A277" s="5">
+      <c r="A277" s="4">
         <f t="shared" si="20"/>
         <v>276</v>
       </c>
-      <c r="B277" s="10">
-        <v>100</v>
-      </c>
-      <c r="C277" s="10">
-        <v>0</v>
-      </c>
-      <c r="E277" s="12">
+      <c r="B277" s="8">
+        <v>100</v>
+      </c>
+      <c r="C277" s="8">
+        <v>0</v>
+      </c>
+      <c r="E277" s="10">
         <f t="shared" si="21"/>
         <v>15285</v>
       </c>
-      <c r="F277" s="13">
+      <c r="F277" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A278" s="5">
+      <c r="A278" s="4">
         <f t="shared" si="20"/>
         <v>277</v>
       </c>
-      <c r="B278" s="10">
-        <v>100</v>
-      </c>
-      <c r="C278" s="10">
-        <v>0</v>
-      </c>
-      <c r="E278" s="12">
+      <c r="B278" s="8">
+        <v>100</v>
+      </c>
+      <c r="C278" s="8">
+        <v>0</v>
+      </c>
+      <c r="E278" s="10">
         <f t="shared" si="21"/>
         <v>15385</v>
       </c>
-      <c r="F278" s="13">
+      <c r="F278" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A279" s="5">
+      <c r="A279" s="4">
         <f t="shared" si="20"/>
         <v>278</v>
       </c>
-      <c r="B279" s="10">
-        <v>100</v>
-      </c>
-      <c r="C279" s="10">
-        <v>0</v>
-      </c>
-      <c r="E279" s="12">
+      <c r="B279" s="8">
+        <v>100</v>
+      </c>
+      <c r="C279" s="8">
+        <v>0</v>
+      </c>
+      <c r="E279" s="10">
         <f t="shared" si="21"/>
         <v>15485</v>
       </c>
-      <c r="F279" s="13">
+      <c r="F279" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A280" s="5">
+      <c r="A280" s="4">
         <f t="shared" si="20"/>
         <v>279</v>
       </c>
-      <c r="B280" s="10">
-        <v>100</v>
-      </c>
-      <c r="C280" s="10">
-        <v>0</v>
-      </c>
-      <c r="E280" s="12">
+      <c r="B280" s="8">
+        <v>100</v>
+      </c>
+      <c r="C280" s="8">
+        <v>0</v>
+      </c>
+      <c r="E280" s="10">
         <f t="shared" si="21"/>
         <v>15585</v>
       </c>
-      <c r="F280" s="13">
+      <c r="F280" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A281" s="5">
+      <c r="A281" s="4">
         <f t="shared" si="20"/>
         <v>280</v>
       </c>
-      <c r="B281" s="10">
-        <v>100</v>
-      </c>
-      <c r="C281" s="10">
-        <v>0</v>
-      </c>
-      <c r="E281" s="12">
+      <c r="B281" s="8">
+        <v>100</v>
+      </c>
+      <c r="C281" s="8">
+        <v>0</v>
+      </c>
+      <c r="E281" s="10">
         <f t="shared" si="21"/>
         <v>15685</v>
       </c>
-      <c r="F281" s="13">
+      <c r="F281" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A282" s="5">
+      <c r="A282" s="4">
         <f t="shared" si="20"/>
         <v>281</v>
       </c>
-      <c r="B282" s="10">
-        <v>100</v>
-      </c>
-      <c r="C282" s="10">
-        <v>0</v>
-      </c>
-      <c r="E282" s="12">
+      <c r="B282" s="8">
+        <v>100</v>
+      </c>
+      <c r="C282" s="8">
+        <v>0</v>
+      </c>
+      <c r="E282" s="10">
         <f t="shared" si="21"/>
         <v>15785</v>
       </c>
-      <c r="F282" s="13">
+      <c r="F282" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A283" s="5">
+      <c r="A283" s="4">
         <f t="shared" si="20"/>
         <v>282</v>
       </c>
-      <c r="B283" s="10">
-        <v>100</v>
-      </c>
-      <c r="C283" s="10">
-        <v>0</v>
-      </c>
-      <c r="E283" s="12">
+      <c r="B283" s="8">
+        <v>100</v>
+      </c>
+      <c r="C283" s="8">
+        <v>0</v>
+      </c>
+      <c r="E283" s="10">
         <f t="shared" si="21"/>
         <v>15885</v>
       </c>
-      <c r="F283" s="13">
+      <c r="F283" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A284" s="5">
+      <c r="A284" s="4">
         <f t="shared" si="20"/>
         <v>283</v>
       </c>
-      <c r="B284" s="10">
-        <v>100</v>
-      </c>
-      <c r="C284" s="10">
-        <v>0</v>
-      </c>
-      <c r="E284" s="12">
+      <c r="B284" s="8">
+        <v>100</v>
+      </c>
+      <c r="C284" s="8">
+        <v>0</v>
+      </c>
+      <c r="E284" s="10">
         <f t="shared" si="21"/>
         <v>15985</v>
       </c>
-      <c r="F284" s="13">
+      <c r="F284" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A285" s="5">
+      <c r="A285" s="4">
         <f t="shared" si="20"/>
         <v>284</v>
       </c>
-      <c r="B285" s="10">
-        <v>100</v>
-      </c>
-      <c r="C285" s="10">
-        <v>0</v>
-      </c>
-      <c r="E285" s="12">
+      <c r="B285" s="8">
+        <v>100</v>
+      </c>
+      <c r="C285" s="8">
+        <v>0</v>
+      </c>
+      <c r="E285" s="10">
         <f t="shared" si="21"/>
         <v>16085</v>
       </c>
-      <c r="F285" s="13">
+      <c r="F285" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A286" s="5">
-        <f t="shared" ref="A286:B301" si="23">A285+1</f>
+      <c r="A286" s="4">
+        <f t="shared" ref="A286:A301" si="23">A285+1</f>
         <v>285</v>
       </c>
-      <c r="B286" s="10">
-        <v>100</v>
-      </c>
-      <c r="C286" s="10">
-        <v>0</v>
-      </c>
-      <c r="E286" s="12">
+      <c r="B286" s="8">
+        <v>100</v>
+      </c>
+      <c r="C286" s="8">
+        <v>0</v>
+      </c>
+      <c r="E286" s="10">
         <f t="shared" si="21"/>
         <v>16185</v>
       </c>
-      <c r="F286" s="13">
+      <c r="F286" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A287" s="5">
+      <c r="A287" s="4">
         <f t="shared" si="23"/>
         <v>286</v>
       </c>
-      <c r="B287" s="10">
-        <v>100</v>
-      </c>
-      <c r="C287" s="10">
-        <v>0</v>
-      </c>
-      <c r="E287" s="12">
+      <c r="B287" s="8">
+        <v>100</v>
+      </c>
+      <c r="C287" s="8">
+        <v>0</v>
+      </c>
+      <c r="E287" s="10">
         <f t="shared" si="21"/>
         <v>16285</v>
       </c>
-      <c r="F287" s="13">
+      <c r="F287" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A288" s="5">
+      <c r="A288" s="4">
         <f t="shared" si="23"/>
         <v>287</v>
       </c>
-      <c r="B288" s="10">
-        <v>100</v>
-      </c>
-      <c r="C288" s="10">
-        <v>0</v>
-      </c>
-      <c r="E288" s="12">
+      <c r="B288" s="8">
+        <v>100</v>
+      </c>
+      <c r="C288" s="8">
+        <v>0</v>
+      </c>
+      <c r="E288" s="10">
         <f t="shared" si="21"/>
         <v>16385</v>
       </c>
-      <c r="F288" s="13">
+      <c r="F288" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A289" s="5">
+      <c r="A289" s="4">
         <f t="shared" si="23"/>
         <v>288</v>
       </c>
-      <c r="B289" s="10">
-        <v>100</v>
-      </c>
-      <c r="C289" s="10">
-        <v>0</v>
-      </c>
-      <c r="E289" s="12">
+      <c r="B289" s="8">
+        <v>100</v>
+      </c>
+      <c r="C289" s="8">
+        <v>0</v>
+      </c>
+      <c r="E289" s="10">
         <f t="shared" si="21"/>
         <v>16485</v>
       </c>
-      <c r="F289" s="13">
+      <c r="F289" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A290" s="5">
+      <c r="A290" s="4">
         <f t="shared" si="23"/>
         <v>289</v>
       </c>
-      <c r="B290" s="10">
-        <v>100</v>
-      </c>
-      <c r="C290" s="10">
-        <v>0</v>
-      </c>
-      <c r="E290" s="12">
+      <c r="B290" s="8">
+        <v>100</v>
+      </c>
+      <c r="C290" s="8">
+        <v>0</v>
+      </c>
+      <c r="E290" s="10">
         <f t="shared" si="21"/>
         <v>16585</v>
       </c>
-      <c r="F290" s="13">
+      <c r="F290" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A291" s="5">
+      <c r="A291" s="4">
         <f t="shared" si="23"/>
         <v>290</v>
       </c>
-      <c r="B291" s="10">
-        <v>100</v>
-      </c>
-      <c r="C291" s="10">
-        <v>0</v>
-      </c>
-      <c r="E291" s="12">
+      <c r="B291" s="8">
+        <v>100</v>
+      </c>
+      <c r="C291" s="8">
+        <v>0</v>
+      </c>
+      <c r="E291" s="10">
         <f t="shared" si="21"/>
         <v>16685</v>
       </c>
-      <c r="F291" s="13">
+      <c r="F291" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A292" s="5">
+      <c r="A292" s="4">
         <f t="shared" si="23"/>
         <v>291</v>
       </c>
-      <c r="B292" s="10">
-        <v>100</v>
-      </c>
-      <c r="C292" s="10">
-        <v>0</v>
-      </c>
-      <c r="E292" s="12">
+      <c r="B292" s="8">
+        <v>100</v>
+      </c>
+      <c r="C292" s="8">
+        <v>0</v>
+      </c>
+      <c r="E292" s="10">
         <f t="shared" si="21"/>
         <v>16785</v>
       </c>
-      <c r="F292" s="13">
+      <c r="F292" s="11">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A293" s="5">
+      <c r="A293" s="4">
         <f t="shared" si="23"/>
         <v>292</v>
       </c>
-      <c r="B293" s="10">
-        <v>100</v>
-      </c>
-      <c r="C293" s="10">
-        <v>0</v>
-      </c>
-      <c r="E293" s="12">
+      <c r="B293" s="8">
+        <v>100</v>
+      </c>
+      <c r="C293" s="8">
+        <v>0</v>
+      </c>
+      <c r="E293" s="10">
         <f t="shared" ref="E293:E301" si="24">E292+B293</f>
         <v>16885</v>
       </c>
-      <c r="F293" s="13">
+      <c r="F293" s="11">
         <f t="shared" ref="F293:F301" si="25">B293-B292</f>
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A294" s="5">
+      <c r="A294" s="4">
         <f t="shared" si="23"/>
         <v>293</v>
       </c>
-      <c r="B294" s="10">
-        <v>100</v>
-      </c>
-      <c r="C294" s="10">
-        <v>0</v>
-      </c>
-      <c r="E294" s="12">
+      <c r="B294" s="8">
+        <v>100</v>
+      </c>
+      <c r="C294" s="8">
+        <v>0</v>
+      </c>
+      <c r="E294" s="10">
         <f t="shared" si="24"/>
         <v>16985</v>
       </c>
-      <c r="F294" s="13">
+      <c r="F294" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A295" s="5">
+      <c r="A295" s="4">
         <f t="shared" si="23"/>
         <v>294</v>
       </c>
-      <c r="B295" s="10">
-        <v>100</v>
-      </c>
-      <c r="C295" s="10">
-        <v>0</v>
-      </c>
-      <c r="E295" s="12">
+      <c r="B295" s="8">
+        <v>100</v>
+      </c>
+      <c r="C295" s="8">
+        <v>0</v>
+      </c>
+      <c r="E295" s="10">
         <f t="shared" si="24"/>
         <v>17085</v>
       </c>
-      <c r="F295" s="13">
+      <c r="F295" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A296" s="5">
+      <c r="A296" s="4">
         <f t="shared" si="23"/>
         <v>295</v>
       </c>
-      <c r="B296" s="10">
-        <v>100</v>
-      </c>
-      <c r="C296" s="10">
-        <v>0</v>
-      </c>
-      <c r="E296" s="12">
+      <c r="B296" s="8">
+        <v>100</v>
+      </c>
+      <c r="C296" s="8">
+        <v>0</v>
+      </c>
+      <c r="E296" s="10">
         <f t="shared" si="24"/>
         <v>17185</v>
       </c>
-      <c r="F296" s="13">
+      <c r="F296" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A297" s="5">
+      <c r="A297" s="4">
         <f t="shared" si="23"/>
         <v>296</v>
       </c>
-      <c r="B297" s="10">
-        <v>100</v>
-      </c>
-      <c r="C297" s="10">
-        <v>0</v>
-      </c>
-      <c r="E297" s="12">
+      <c r="B297" s="8">
+        <v>100</v>
+      </c>
+      <c r="C297" s="8">
+        <v>0</v>
+      </c>
+      <c r="E297" s="10">
         <f t="shared" si="24"/>
         <v>17285</v>
       </c>
-      <c r="F297" s="13">
+      <c r="F297" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A298" s="5">
+      <c r="A298" s="4">
         <f t="shared" si="23"/>
         <v>297</v>
       </c>
-      <c r="B298" s="10">
-        <v>100</v>
-      </c>
-      <c r="C298" s="10">
-        <v>0</v>
-      </c>
-      <c r="E298" s="12">
+      <c r="B298" s="8">
+        <v>100</v>
+      </c>
+      <c r="C298" s="8">
+        <v>0</v>
+      </c>
+      <c r="E298" s="10">
         <f t="shared" si="24"/>
         <v>17385</v>
       </c>
-      <c r="F298" s="13">
+      <c r="F298" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A299" s="5">
+      <c r="A299" s="4">
         <f t="shared" si="23"/>
         <v>298</v>
       </c>
-      <c r="B299" s="10">
-        <v>100</v>
-      </c>
-      <c r="C299" s="10">
-        <v>0</v>
-      </c>
-      <c r="E299" s="12">
+      <c r="B299" s="8">
+        <v>100</v>
+      </c>
+      <c r="C299" s="8">
+        <v>0</v>
+      </c>
+      <c r="E299" s="10">
         <f t="shared" si="24"/>
         <v>17485</v>
       </c>
-      <c r="F299" s="13">
+      <c r="F299" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A300" s="5">
+      <c r="A300" s="4">
         <f t="shared" si="23"/>
         <v>299</v>
       </c>
-      <c r="B300" s="10">
-        <v>100</v>
-      </c>
-      <c r="C300" s="10">
-        <v>0</v>
-      </c>
-      <c r="E300" s="12">
+      <c r="B300" s="8">
+        <v>100</v>
+      </c>
+      <c r="C300" s="8">
+        <v>0</v>
+      </c>
+      <c r="E300" s="10">
         <f t="shared" si="24"/>
         <v>17585</v>
       </c>
-      <c r="F300" s="13">
+      <c r="F300" s="11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A301" s="5">
+      <c r="A301" s="4">
         <f t="shared" si="23"/>
         <v>300</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="3">
         <v>-1</v>
       </c>
-      <c r="C301" s="10">
-        <v>0</v>
-      </c>
-      <c r="E301" s="12">
+      <c r="C301" s="8">
+        <v>0</v>
+      </c>
+      <c r="E301" s="10">
         <f t="shared" si="24"/>
         <v>17584</v>
       </c>
-      <c r="F301" s="7">
+      <c r="F301" s="6">
         <f t="shared" si="25"/>
         <v>-101</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A302" s="5"/>
-      <c r="E302" s="12"/>
-      <c r="F302" s="13"/>
+      <c r="A302" s="4"/>
+      <c r="E302" s="10"/>
+      <c r="F302" s="11"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A303" s="5"/>
-      <c r="E303" s="12"/>
-      <c r="F303" s="13"/>
+      <c r="A303" s="4"/>
+      <c r="E303" s="10"/>
+      <c r="F303" s="11"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A304" s="5"/>
-      <c r="E304" s="12"/>
-      <c r="F304" s="13"/>
+      <c r="A304" s="4"/>
+      <c r="E304" s="10"/>
+      <c r="F304" s="11"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A305" s="5"/>
-      <c r="E305" s="12"/>
-      <c r="F305" s="13"/>
+      <c r="A305" s="4"/>
+      <c r="E305" s="10"/>
+      <c r="F305" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/AddressableResource/Data/Excels/LevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/LevelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E04EA6D-B855-4EF1-937D-E76E9650A927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EEF660-A7E8-417B-B00A-AD13DCED384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,45 +33,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>level</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>exp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임1 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임2 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임3 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임4 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임5 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임6 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임7 언락</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 게임 언락</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -531,11 +499,11 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -546,16 +514,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="9">
         <f>B2</f>
         <v>2</v>
       </c>
       <c r="F2" s="6"/>
-      <c r="G2" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
@@ -566,7 +531,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="10">
         <f>E2+B3</f>
@@ -586,7 +551,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" ref="E4:E67" si="1">E3+B4</f>
@@ -627,7 +592,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="1"/>
@@ -636,9 +601,6 @@
       <c r="F6" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -674,7 +636,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" si="1"/>
@@ -737,7 +699,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="1"/>
@@ -746,9 +708,6 @@
       <c r="F11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -824,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="1"/>
@@ -833,9 +792,6 @@
       <c r="F15" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -859,7 +815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -880,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -901,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -922,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -943,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -953,7 +909,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" s="10">
         <f t="shared" si="4"/>
@@ -963,11 +919,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -988,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -998,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="4"/>
@@ -1008,11 +961,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1033,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1043,7 +993,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E25" s="10">
         <f t="shared" si="4"/>
@@ -1053,11 +1003,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1078,7 +1025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1088,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E27" s="10">
         <f t="shared" si="4"/>
@@ -1098,11 +1045,8 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1123,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1144,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1165,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1186,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
